--- a/analysis/comparison_results_EUS_costs.xlsx
+++ b/analysis/comparison_results_EUS_costs.xlsx
@@ -16,24 +16,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>EUS</t>
   </si>
   <si>
+    <t xml:space="preserve">Zwickl Bernhard</t>
+  </si>
+  <si>
+    <t>noins</t>
+  </si>
+  <si>
     <t>ins20</t>
   </si>
   <si>
-    <t>noins</t>
+    <t>ins40</t>
+  </si>
+  <si>
+    <t>ins60</t>
+  </si>
+  <si>
+    <t>ins80</t>
   </si>
   <si>
     <t xml:space="preserve">noins M_theta=75</t>
   </si>
   <si>
-    <t>ins80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zwickl Bernhard</t>
+    <t xml:space="preserve">ins20 M_theta=75</t>
   </si>
   <si>
     <t>Concept</t>
@@ -96,10 +105,10 @@
     <t xml:space="preserve">Onshore pipelines CAPEX</t>
   </si>
   <si>
+    <t xml:space="preserve">Onshore pipeline insulation </t>
+  </si>
+  <si>
     <t xml:space="preserve">Onshore pipelines OPEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onshore pipelines insulation</t>
   </si>
   <si>
     <t xml:space="preserve">Offshore pipelines CAPEX</t>
@@ -198,17 +207,26 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -710,713 +728,1161 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="36.921875"/>
-    <col bestFit="1" min="2" max="2" width="17.8515625"/>
-    <col bestFit="1" min="3" max="3" width="12.57421875"/>
-    <col bestFit="1" min="4" max="4" width="16.421875"/>
-    <col bestFit="1" min="5" max="5" width="12.50390625"/>
-    <col bestFit="1" min="6" max="6" width="14.28125"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="14.79296875"/>
+    <col customWidth="1" min="3" max="3" width="3.28125"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="12.04296875"/>
+    <col bestFit="1" min="5" max="8" width="12.04296875"/>
+    <col customWidth="1" min="9" max="9" width="4.28125"/>
+    <col bestFit="1" min="10" max="10" width="16.421875"/>
+    <col bestFit="1" min="11" max="11" width="16.22265625"/>
+    <col bestFit="1" min="12" max="12" width="12.50390625"/>
+    <col min="13" max="13" width="12.50390625"/>
+    <col bestFit="1" min="14" max="14" width="14.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1"/>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4"/>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3">
+      <c r="A3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5">
+        <v>69597.543222625303</v>
+      </c>
+      <c r="E3" s="5">
         <v>69597.543222625289</v>
       </c>
-      <c r="C3" s="3">
-        <v>69597.543222625303</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="F3" s="5">
+        <v>69634.329084374185</v>
+      </c>
+      <c r="G3" s="5">
+        <v>69634.329084374462</v>
+      </c>
+      <c r="H3" s="5">
+        <v>69597.54322262542</v>
+      </c>
+      <c r="J3" s="5">
         <v>69392.390164436889</v>
       </c>
-      <c r="E3" s="3">
-        <v>69597.54322262542</v>
-      </c>
+      <c r="K3" s="5">
+        <v>69391.693142625372</v>
+      </c>
+      <c r="M3" s="6"/>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="E4" s="5">
         <v>4060.9494799999989</v>
       </c>
-      <c r="C4" s="3">
+      <c r="F4" s="5">
+        <v>4060.9494799999779</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4060.9494800000039</v>
+      </c>
+      <c r="H4" s="5">
         <v>4060.9494800000002</v>
       </c>
-      <c r="D4" s="3">
+      <c r="J4" s="5">
         <v>4060.9494799999861</v>
       </c>
-      <c r="E4" s="3">
-        <v>4060.9494800000002</v>
-      </c>
+      <c r="K4" s="5">
+        <v>4060.9494799999961</v>
+      </c>
+      <c r="M4" s="6"/>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="A5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5">
+        <v>2822.479555469386</v>
+      </c>
+      <c r="E5" s="5">
         <v>3172.428797102089</v>
       </c>
-      <c r="C5" s="3">
-        <v>2822.479555469386</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="F5" s="5">
+        <v>3210.316269888182</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3570.539649473827</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3585.656305035935</v>
+      </c>
+      <c r="J5" s="5">
         <v>2754.4067292287959</v>
       </c>
-      <c r="E5" s="3">
-        <v>3585.656305035935</v>
-      </c>
+      <c r="K5" s="5">
+        <v>2728.6918029066019</v>
+      </c>
+      <c r="M5" s="6"/>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="A6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5">
+        <v>98.422962059999989</v>
+      </c>
+      <c r="E6" s="5">
         <v>165.10938333999991</v>
       </c>
-      <c r="C6" s="3">
-        <v>98.422962059999989</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="F6" s="5">
+        <v>148.9714454999999</v>
+      </c>
+      <c r="G6" s="5">
         <v>148.97144549999999</v>
       </c>
-      <c r="E6" s="3">
+      <c r="H6" s="5">
         <v>148.9714455000001</v>
       </c>
+      <c r="J6" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="K6" s="5">
+        <v>165.10938333999891</v>
+      </c>
+      <c r="M6" s="6"/>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3">
+      <c r="A7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5">
         <v>23586.962899999999</v>
       </c>
-      <c r="C7" s="3">
+      <c r="E7" s="5">
         <v>23586.962899999999</v>
       </c>
-      <c r="D7" s="3">
+      <c r="F7" s="5">
+        <v>24049.61923</v>
+      </c>
+      <c r="G7" s="5">
+        <v>24054.558690000002</v>
+      </c>
+      <c r="H7" s="5">
+        <v>23774.429339999999</v>
+      </c>
+      <c r="J7" s="5">
         <v>23723.679469999999</v>
       </c>
-      <c r="E7" s="3">
-        <v>23774.429339999999</v>
-      </c>
+      <c r="K7" s="5">
+        <v>23679.195970000001</v>
+      </c>
+      <c r="M7" s="6"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5">
+        <v>940.61582583106713</v>
+      </c>
+      <c r="E8" s="5">
         <v>756.61017611282034</v>
       </c>
-      <c r="C8" s="3">
-        <v>940.61582583106713</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="F8" s="5">
+        <v>650.00889925084607</v>
+      </c>
+      <c r="G8" s="5">
+        <v>730.0148860209132</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1143.9975968240331</v>
+      </c>
+      <c r="J8" s="5">
         <v>960.25576080048108</v>
       </c>
-      <c r="E8" s="3">
-        <v>1143.9975968240331</v>
-      </c>
+      <c r="K8" s="5">
+        <v>804.70709756845656</v>
+      </c>
+      <c r="M8" s="6"/>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3">
+      <c r="A9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5">
+        <v>861.29550492504598</v>
+      </c>
+      <c r="E9" s="5">
         <v>959.55380296238513</v>
       </c>
-      <c r="C9" s="3">
-        <v>861.29550492504598</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="F9" s="5">
+        <v>862.45703766490078</v>
+      </c>
+      <c r="G9" s="5">
+        <v>967.71333735433677</v>
+      </c>
+      <c r="H9" s="5">
+        <v>974.80145458214008</v>
+      </c>
+      <c r="J9" s="5">
         <v>776.20692015063798</v>
       </c>
-      <c r="E9" s="3">
-        <v>974.80145458214008</v>
-      </c>
+      <c r="K9" s="5">
+        <v>800.2757575545179</v>
+      </c>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
         <v>149.2337224143092</v>
       </c>
-      <c r="C10" s="3">
+      <c r="F10" s="5">
+        <v>212.57460395924869</v>
+      </c>
+      <c r="G10" s="5">
+        <v>309.17249442743878</v>
+      </c>
+      <c r="H10" s="5">
+        <v>307.37163604812002</v>
+      </c>
+      <c r="J10" s="5">
         <v>0</v>
       </c>
-      <c r="D10" s="3">
+      <c r="K10" s="5">
+        <v>0.5828006912</v>
+      </c>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5">
+        <v>35.417730949999999</v>
+      </c>
+      <c r="E11" s="5">
+        <v>55.639340949999998</v>
+      </c>
+      <c r="F11" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="G11" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="H11" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="J11" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="K11" s="5">
+        <v>55.639340949999998</v>
+      </c>
+      <c r="M11" s="6"/>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5">
+        <v>1585.91461</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1585.91461</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1637.56744</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1638.1152</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1606.8459499999999</v>
+      </c>
+      <c r="J12" s="5">
+        <v>1601.1893399999999</v>
+      </c>
+      <c r="K12" s="5">
+        <v>1596.2213999999999</v>
+      </c>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5">
+        <v>46.212072067103257</v>
+      </c>
+      <c r="E13" s="5">
+        <v>36.562164955427981</v>
+      </c>
+      <c r="F13" s="5">
+        <v>28.0167534975525</v>
+      </c>
+      <c r="G13" s="5">
+        <v>29.412129022385631</v>
+      </c>
+      <c r="H13" s="5">
+        <v>59.589611248039077</v>
+      </c>
+      <c r="J13" s="5">
+        <v>48.290297872142027</v>
+      </c>
+      <c r="K13" s="5">
+        <v>33.7948929984911</v>
+      </c>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5">
+        <v>10339.488788988891</v>
+      </c>
+      <c r="E14" s="5">
+        <v>10339.488788988891</v>
+      </c>
+      <c r="F14" s="5">
+        <v>10344.95345049641</v>
+      </c>
+      <c r="G14" s="5">
+        <v>10344.95345049645</v>
+      </c>
+      <c r="H14" s="5">
+        <v>10339.488788988911</v>
+      </c>
+      <c r="J14" s="5">
+        <v>10309.01481623552</v>
+      </c>
+      <c r="K14" s="5">
+        <v>10308.9042769889</v>
+      </c>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5">
+        <v>288.30227135991117</v>
+      </c>
+      <c r="E15" s="5">
+        <v>274.29023135991338</v>
+      </c>
+      <c r="F15" s="5">
+        <v>227.0376128161314</v>
+      </c>
+      <c r="G15" s="5">
+        <v>218.2520210880229</v>
+      </c>
+      <c r="H15" s="5">
+        <v>430.23048014211258</v>
+      </c>
+      <c r="J15" s="5">
+        <v>341.73291724526467</v>
+      </c>
+      <c r="K15" s="5">
+        <v>250.42085335991359</v>
+      </c>
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5">
         <v>0</v>
       </c>
-      <c r="E10" s="3">
-        <v>307.37163604812002</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="A11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="3">
-        <v>55.639340949999998</v>
-      </c>
-      <c r="C11" s="3">
-        <v>35.417730949999999</v>
-      </c>
-      <c r="D11" s="3">
-        <v>46.970104149999997</v>
-      </c>
-      <c r="E11" s="3">
-        <v>46.970104149999997</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1585.91461</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1585.91461</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1601.1893399999999</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1606.8459499999999</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="3">
-        <v>36.562164955427981</v>
-      </c>
-      <c r="C13" s="3">
-        <v>46.212072067103257</v>
-      </c>
-      <c r="D13" s="3">
-        <v>48.290297872142027</v>
-      </c>
-      <c r="E13" s="3">
-        <v>59.589611248039077</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="3">
-        <v>10339.488788988891</v>
-      </c>
-      <c r="C14" s="3">
-        <v>10339.488788988891</v>
-      </c>
-      <c r="D14" s="3">
-        <v>10309.01481623552</v>
-      </c>
-      <c r="E14" s="3">
-        <v>10339.488788988911</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25">
-      <c r="A15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="3">
-        <v>274.29023135991338</v>
-      </c>
-      <c r="C15" s="3">
-        <v>288.30227135991117</v>
-      </c>
-      <c r="D15" s="3">
-        <v>341.73291724526467</v>
-      </c>
-      <c r="E15" s="3">
-        <v>430.23048014211258</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="3">
+      <c r="E16" s="5">
         <v>0</v>
       </c>
-      <c r="C16" s="3">
+      <c r="F16" s="5">
         <v>0</v>
       </c>
-      <c r="D16" s="3">
+      <c r="G16" s="5">
         <v>0</v>
       </c>
-      <c r="E16" s="3">
+      <c r="H16" s="5">
         <v>0</v>
       </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="6"/>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="3">
+      <c r="A17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5">
+        <v>92623.050287719947</v>
+      </c>
+      <c r="E17" s="5">
         <v>92623.050287719874</v>
       </c>
-      <c r="C17" s="3">
-        <v>92623.050287719947</v>
-      </c>
-      <c r="D17" s="3">
+      <c r="F17" s="5">
+        <v>92479.201967459187</v>
+      </c>
+      <c r="G17" s="5">
+        <v>92479.201967458517</v>
+      </c>
+      <c r="H17" s="5">
+        <v>92623.05028772002</v>
+      </c>
+      <c r="J17" s="5">
         <v>93090.997181584316</v>
       </c>
-      <c r="E17" s="3">
-        <v>92623.05028772002</v>
-      </c>
+      <c r="K17" s="5">
+        <v>92922.050927719931</v>
+      </c>
+      <c r="M17" s="6"/>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="3">
+      <c r="A18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5">
+        <v>-30343.488367293889</v>
+      </c>
+      <c r="E18" s="5">
         <v>-30343.48836729394</v>
       </c>
-      <c r="C18" s="3">
-        <v>-30343.488367293889</v>
-      </c>
-      <c r="D18" s="3">
+      <c r="F18" s="5">
+        <v>-30393.76092033066</v>
+      </c>
+      <c r="G18" s="5">
+        <v>-30393.760920330689</v>
+      </c>
+      <c r="H18" s="5">
+        <v>-30343.488367293881</v>
+      </c>
+      <c r="J18" s="5">
         <v>-30063.153022915041</v>
       </c>
-      <c r="E18" s="3">
-        <v>-30343.488367293881</v>
-      </c>
+      <c r="K18" s="5">
+        <v>-30062.161487294001</v>
+      </c>
+      <c r="M18" s="6"/>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="3">
+      <c r="A19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5">
+        <v>176543.16684470279</v>
+      </c>
+      <c r="E19" s="5">
         <v>176870.61481882271</v>
       </c>
-      <c r="C19" s="3">
-        <v>176543.16684470279</v>
-      </c>
-      <c r="D19" s="3">
+      <c r="F19" s="5">
+        <v>176986.63785476671</v>
+      </c>
+      <c r="G19" s="5">
+        <v>177530.22052460819</v>
+      </c>
+      <c r="H19" s="5">
+        <v>178049.0356995227</v>
+      </c>
+      <c r="J19" s="5">
         <v>177191.90160428901</v>
       </c>
-      <c r="E19" s="3">
-        <v>178049.0356995227</v>
-      </c>
+      <c r="K19" s="5">
+        <v>176735.4928387182</v>
+      </c>
+      <c r="M19" s="6"/>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="D20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="D21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="D22" s="5"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" ht="14.25">
       <c r="A23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="4">
-        <f>B5/1000</f>
+        <v>28</v>
+      </c>
+      <c r="B23">
+        <v>2.1499999999999999</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="8">
+        <f>D5/1000</f>
+        <v>2.822479555469386</v>
+      </c>
+      <c r="E23" s="9">
+        <f>E5/1000</f>
         <v>3.1724287971020888</v>
       </c>
-      <c r="C23" s="4">
-        <f>C5/1000</f>
-        <v>2.822479555469386</v>
-      </c>
-      <c r="D23" s="4">
-        <f>D5/1000</f>
+      <c r="F23" s="9">
+        <f>F5/1000</f>
+        <v>3.2103162698881822</v>
+      </c>
+      <c r="G23" s="9">
+        <f>G5/1000</f>
+        <v>3.5705396494738268</v>
+      </c>
+      <c r="H23" s="9">
+        <f>H5/1000</f>
+        <v>3.5856563050359349</v>
+      </c>
+      <c r="J23" s="9">
+        <f>J5/1000</f>
         <v>2.7544067292287959</v>
       </c>
-      <c r="E23" s="4">
-        <f>E5/1000</f>
-        <v>3.5856563050359349</v>
-      </c>
-      <c r="F23">
-        <v>2.1499999999999999</v>
-      </c>
+      <c r="K23" s="9">
+        <f>K5/1000</f>
+        <v>2.7286918029066021</v>
+      </c>
+      <c r="M23" s="8"/>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="4">
-        <f>B9/1000</f>
-        <v>0.95955380296238513</v>
-      </c>
-      <c r="C24" s="4">
-        <f>C9/1000</f>
-        <v>0.86129550492504603</v>
-      </c>
-      <c r="D24" s="4">
-        <f>D9/1000</f>
-        <v>0.77620692015063797</v>
-      </c>
-      <c r="E24" s="4">
-        <f>E9/1000</f>
-        <v>0.97480145458214007</v>
-      </c>
-      <c r="F24">
-        <v>0.57999999999999996</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B24" s="9">
+        <f>B10/1000</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="8">
+        <f>D10/1000</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <f>E10/1000</f>
+        <v>0.14923372241430921</v>
+      </c>
+      <c r="F24" s="9">
+        <f>F10/1000</f>
+        <v>0.21257460395924868</v>
+      </c>
+      <c r="G24" s="9">
+        <f>G10/1000</f>
+        <v>0.30917249442743877</v>
+      </c>
+      <c r="H24" s="9">
+        <f>H10/1000</f>
+        <v>0.30737163604812001</v>
+      </c>
+      <c r="J24" s="9">
+        <f>J10/1000</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
+        <f>K10/1000</f>
+        <v>5.8280069119999998e-04</v>
+      </c>
+      <c r="M24" s="9"/>
     </row>
     <row r="25" ht="14.25">
       <c r="A25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="4">
-        <f>B10/1000</f>
-        <v>0.14923372241430921</v>
-      </c>
-      <c r="C25" s="4">
-        <f>C10/1000</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="4">
-        <f>D10/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="4">
-        <f>E10/1000</f>
-        <v>0.30737163604812001</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B25">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="8">
+        <f>D9/1000</f>
+        <v>0.86129550492504603</v>
+      </c>
+      <c r="E25" s="9">
+        <f>E9/1000</f>
+        <v>0.95955380296238513</v>
+      </c>
+      <c r="F25" s="9">
+        <f>F9/1000</f>
+        <v>0.86245703766490078</v>
+      </c>
+      <c r="G25" s="9">
+        <f>G9/1000</f>
+        <v>0.96771333735433673</v>
+      </c>
+      <c r="H25" s="9">
+        <f>H9/1000</f>
+        <v>0.97480145458214007</v>
+      </c>
+      <c r="J25" s="9">
+        <f>J9/1000</f>
+        <v>0.77620692015063797</v>
+      </c>
+      <c r="K25" s="9">
+        <f>K9/1000</f>
+        <v>0.80027575755451785</v>
+      </c>
+      <c r="M25" s="8"/>
     </row>
     <row r="26" ht="14.25">
       <c r="A26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="4">
-        <f>B6/1000</f>
+        <v>31</v>
+      </c>
+      <c r="B26">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8">
+        <f>D6/1000</f>
+        <v>9.8422962059999994e-02</v>
+      </c>
+      <c r="E26" s="9">
+        <f>E6/1000</f>
         <v>0.16510938333999992</v>
       </c>
-      <c r="C26" s="4">
-        <f>C6/1000</f>
-        <v>9.8422962059999994e-02</v>
-      </c>
-      <c r="D26" s="4">
-        <f>D6/1000</f>
+      <c r="F26" s="9">
+        <f>F6/1000</f>
+        <v>0.14897144549999991</v>
+      </c>
+      <c r="G26" s="9">
+        <f>G6/1000</f>
         <v>0.14897144549999999</v>
       </c>
-      <c r="E26" s="4">
-        <f>E6/1000</f>
+      <c r="H26" s="9">
+        <f>H6/1000</f>
         <v>0.1489714455000001</v>
       </c>
-      <c r="F26">
-        <v>0.14000000000000001</v>
-      </c>
+      <c r="J26" s="9">
+        <f>J6/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="K26" s="9">
+        <f>K6/1000</f>
+        <v>0.16510938333999892</v>
+      </c>
+      <c r="M26" s="8"/>
     </row>
     <row r="27" ht="14.25">
       <c r="A27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="4">
-        <f>B11/1000</f>
+        <v>32</v>
+      </c>
+      <c r="B27">
+        <v>5.0000000000000003e-02</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="8">
+        <f>D11/1000</f>
+        <v>3.5417730949999997e-02</v>
+      </c>
+      <c r="E27" s="9">
+        <f>E11/1000</f>
         <v>5.5639340949999998e-02</v>
       </c>
-      <c r="C27" s="4">
-        <f>C11/1000</f>
-        <v>3.5417730949999997e-02</v>
-      </c>
-      <c r="D27" s="4">
-        <f>D11/1000</f>
+      <c r="F27" s="9">
+        <f>F11/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="E27" s="4">
-        <f>E11/1000</f>
+      <c r="G27" s="9">
+        <f>G11/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="F27">
-        <v>5.0000000000000003e-02</v>
-      </c>
+      <c r="H27" s="9">
+        <f>H11/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="J27" s="9">
+        <f>J11/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="K27" s="9">
+        <f>K11/1000</f>
+        <v>5.5639340949999998e-02</v>
+      </c>
+      <c r="M27" s="8"/>
     </row>
     <row r="28" ht="14.25">
       <c r="A28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="4">
-        <f>B7/1000</f>
+        <v>33</v>
+      </c>
+      <c r="B28">
+        <v>23.57</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="8">
+        <f>D7/1000</f>
         <v>23.5869629</v>
       </c>
-      <c r="C28" s="4">
-        <f>C7/1000</f>
+      <c r="E28" s="9">
+        <f>E7/1000</f>
         <v>23.5869629</v>
       </c>
-      <c r="D28" s="4">
-        <f>D7/1000</f>
+      <c r="F28" s="9">
+        <f>F7/1000</f>
+        <v>24.049619230000001</v>
+      </c>
+      <c r="G28" s="9">
+        <f>G7/1000</f>
+        <v>24.05455869</v>
+      </c>
+      <c r="H28" s="9">
+        <f>H7/1000</f>
+        <v>23.774429339999998</v>
+      </c>
+      <c r="J28" s="9">
+        <f>J7/1000</f>
         <v>23.72367947</v>
       </c>
-      <c r="E28" s="4">
-        <f>E7/1000</f>
-        <v>23.774429339999998</v>
-      </c>
-      <c r="F28">
-        <v>23.57</v>
-      </c>
+      <c r="K28" s="9">
+        <f>K7/1000</f>
+        <v>23.679195970000002</v>
+      </c>
+      <c r="M28" s="8"/>
     </row>
     <row r="29" ht="14.25">
       <c r="A29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="4">
-        <f>B12/1000</f>
+        <v>34</v>
+      </c>
+      <c r="B29">
+        <v>1.5800000000000001</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="8">
+        <f>D12/1000</f>
         <v>1.5859146100000001</v>
       </c>
-      <c r="C29" s="4">
-        <f>C12/1000</f>
+      <c r="E29" s="9">
+        <f>E12/1000</f>
         <v>1.5859146100000001</v>
       </c>
-      <c r="D29" s="4">
-        <f>D12/1000</f>
+      <c r="F29" s="9">
+        <f>F12/1000</f>
+        <v>1.63756744</v>
+      </c>
+      <c r="G29" s="9">
+        <f>G12/1000</f>
+        <v>1.6381151999999999</v>
+      </c>
+      <c r="H29" s="9">
+        <f>H12/1000</f>
+        <v>1.6068459499999999</v>
+      </c>
+      <c r="J29" s="9">
+        <f>J12/1000</f>
         <v>1.6011893399999999</v>
       </c>
-      <c r="E29" s="4">
-        <f>E12/1000</f>
-        <v>1.6068459499999999</v>
-      </c>
-      <c r="F29">
-        <v>1.5800000000000001</v>
-      </c>
+      <c r="K29" s="9">
+        <f>K12/1000</f>
+        <v>1.5962213999999999</v>
+      </c>
+      <c r="M29" s="8"/>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="4">
-        <f>B14/1000</f>
+        <v>35</v>
+      </c>
+      <c r="B30">
+        <v>10.57</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8">
+        <f>D14/1000</f>
         <v>10.339488788988891</v>
       </c>
-      <c r="C30" s="4">
-        <f>C14/1000</f>
+      <c r="E30" s="9">
+        <f>E14/1000</f>
         <v>10.339488788988891</v>
       </c>
-      <c r="D30" s="4">
-        <f>D14/1000</f>
+      <c r="F30" s="9">
+        <f>F14/1000</f>
+        <v>10.34495345049641</v>
+      </c>
+      <c r="G30" s="9">
+        <f>G14/1000</f>
+        <v>10.344953450496451</v>
+      </c>
+      <c r="H30" s="9">
+        <f>H14/1000</f>
+        <v>10.339488788988911</v>
+      </c>
+      <c r="J30" s="9">
+        <f>J14/1000</f>
         <v>10.30901481623552</v>
       </c>
-      <c r="E30" s="4">
-        <f>E14/1000</f>
-        <v>10.339488788988911</v>
-      </c>
-      <c r="F30">
-        <v>10.57</v>
-      </c>
+      <c r="K30" s="9">
+        <f>K14/1000</f>
+        <v>10.308904276988899</v>
+      </c>
+      <c r="M30" s="8"/>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="4">
-        <f>B8/1000</f>
+        <v>36</v>
+      </c>
+      <c r="B31">
+        <v>0.62</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="8">
+        <f>D8/1000</f>
+        <v>0.94061582583106718</v>
+      </c>
+      <c r="E31" s="9">
+        <f>E8/1000</f>
         <v>0.75661017611282033</v>
       </c>
-      <c r="C31" s="4">
-        <f>C8/1000</f>
-        <v>0.94061582583106718</v>
-      </c>
-      <c r="D31" s="4">
-        <f>D8/1000</f>
+      <c r="F31" s="9">
+        <f>F8/1000</f>
+        <v>0.65000889925084604</v>
+      </c>
+      <c r="G31" s="9">
+        <f>G8/1000</f>
+        <v>0.73001488602091325</v>
+      </c>
+      <c r="H31" s="9">
+        <f>H8/1000</f>
+        <v>1.143997596824033</v>
+      </c>
+      <c r="J31" s="9">
+        <f>J8/1000</f>
         <v>0.96025576080048114</v>
       </c>
-      <c r="E31" s="4">
-        <f>E8/1000</f>
-        <v>1.143997596824033</v>
-      </c>
-      <c r="F31">
-        <v>0.62</v>
-      </c>
+      <c r="K31" s="9">
+        <f>K8/1000</f>
+        <v>0.8047070975684566</v>
+      </c>
+      <c r="M31" s="8"/>
     </row>
     <row r="32" ht="14.25">
       <c r="A32" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="4">
-        <f>B13/1000</f>
+        <v>37</v>
+      </c>
+      <c r="B32">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="8">
+        <f>D13/1000</f>
+        <v>4.621207206710326e-02</v>
+      </c>
+      <c r="E32" s="9">
+        <f>E13/1000</f>
         <v>3.6562164955427981e-02</v>
       </c>
-      <c r="C32" s="4">
-        <f>C13/1000</f>
-        <v>4.621207206710326e-02</v>
-      </c>
-      <c r="D32" s="4">
-        <f>D13/1000</f>
+      <c r="F32" s="9">
+        <f>F13/1000</f>
+        <v>2.8016753497552501e-02</v>
+      </c>
+      <c r="G32" s="9">
+        <f>G13/1000</f>
+        <v>2.941212902238563e-02</v>
+      </c>
+      <c r="H32" s="9">
+        <f>H13/1000</f>
+        <v>5.9589611248039076e-02</v>
+      </c>
+      <c r="J32" s="9">
+        <f>J13/1000</f>
         <v>4.8290297872142028e-02</v>
       </c>
-      <c r="E32" s="4">
-        <f>E13/1000</f>
-        <v>5.9589611248039076e-02</v>
-      </c>
-      <c r="F32">
-        <v>2.9999999999999999e-02</v>
-      </c>
+      <c r="K32" s="9">
+        <f>K13/1000</f>
+        <v>3.3794892998491102e-02</v>
+      </c>
+      <c r="M32" s="8"/>
     </row>
     <row r="33" ht="14.25">
       <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="4">
-        <f>B15/1000</f>
+        <v>38</v>
+      </c>
+      <c r="B33">
+        <v>0.22</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="8">
+        <f>D15/1000</f>
+        <v>0.28830227135991116</v>
+      </c>
+      <c r="E33" s="9">
+        <f>E15/1000</f>
         <v>0.27429023135991337</v>
       </c>
-      <c r="C33" s="4">
-        <f>C15/1000</f>
-        <v>0.28830227135991116</v>
-      </c>
-      <c r="D33" s="4">
-        <f>D15/1000</f>
+      <c r="F33" s="9">
+        <f>F15/1000</f>
+        <v>0.22703761281613141</v>
+      </c>
+      <c r="G33" s="9">
+        <f>G15/1000</f>
+        <v>0.21825202108802291</v>
+      </c>
+      <c r="H33" s="9">
+        <f>H15/1000</f>
+        <v>0.43023048014211257</v>
+      </c>
+      <c r="J33" s="9">
+        <f>J15/1000</f>
         <v>0.34173291724526467</v>
       </c>
-      <c r="E33" s="4">
-        <f>E15/1000</f>
-        <v>0.43023048014211257</v>
-      </c>
-      <c r="F33">
-        <v>0.22</v>
-      </c>
+      <c r="K33" s="9">
+        <f>K15/1000</f>
+        <v>0.2504208533599136</v>
+      </c>
+      <c r="M33" s="8"/>
     </row>
     <row r="34" ht="14.25">
       <c r="A34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="4">
-        <f>B4/1000</f>
+        <v>39</v>
+      </c>
+      <c r="B34">
+        <v>4.1799999999999997</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8">
+        <f>D4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="E34" s="9">
+        <f>E4/1000</f>
         <v>4.0609494799999988</v>
       </c>
-      <c r="C34" s="4">
-        <f>C4/1000</f>
+      <c r="F34" s="9">
+        <f>F4/1000</f>
+        <v>4.0609494799999784</v>
+      </c>
+      <c r="G34" s="9">
+        <f>G4/1000</f>
+        <v>4.0609494800000041</v>
+      </c>
+      <c r="H34" s="9">
+        <f>H4/1000</f>
         <v>4.0609494800000006</v>
       </c>
-      <c r="D34" s="4">
-        <f>D4/1000</f>
+      <c r="J34" s="9">
+        <f>J4/1000</f>
         <v>4.0609494799999863</v>
       </c>
-      <c r="E34" s="4">
-        <f>E4/1000</f>
-        <v>4.0609494800000006</v>
-      </c>
-      <c r="F34">
-        <v>4.1799999999999997</v>
-      </c>
+      <c r="K34" s="9">
+        <f>K4/1000</f>
+        <v>4.0609494799999961</v>
+      </c>
+      <c r="M34" s="8"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="M35" s="8"/>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="4">
+        <v>40</v>
+      </c>
+      <c r="B36" s="9">
         <f>SUM(B23:B34)</f>
+        <v>43.689999999999998</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="8">
+        <f>SUM(D23:D34)</f>
+        <v>44.666061701651401</v>
+      </c>
+      <c r="E36" s="9">
+        <f>SUM(E23:E34)</f>
         <v>45.142743398185836</v>
       </c>
-      <c r="C36" s="4">
-        <f>SUM(C23:C34)</f>
-        <v>44.666061701651401</v>
-      </c>
-      <c r="D36" s="4">
-        <f>SUM(D23:D34)</f>
+      <c r="F36" s="9">
+        <f>SUM(F23:F34)</f>
+        <v>45.479442327223254</v>
+      </c>
+      <c r="G36" s="9">
+        <f>SUM(G23:G34)</f>
+        <v>46.119622887533374</v>
+      </c>
+      <c r="H36" s="9">
+        <f>SUM(H23:H34)</f>
+        <v>46.479302192519285</v>
+      </c>
+      <c r="J36" s="9">
+        <f>SUM(J23:J34)</f>
         <v>44.771667281182829</v>
       </c>
-      <c r="E36" s="4">
-        <f>SUM(E23:E34)</f>
-        <v>46.479302192519285</v>
-      </c>
-      <c r="F36" s="4">
-        <f>SUM(F23:F34)</f>
-        <v>43.689999999999998</v>
-      </c>
+      <c r="K36" s="9">
+        <f>SUM(K23:K34)</f>
+        <v>44.484493056358076</v>
+      </c>
+      <c r="M36" s="9"/>
     </row>
     <row r="37" ht="14.25">
       <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="4">
-        <f>B18/1000</f>
+        <v>41</v>
+      </c>
+      <c r="B37" s="9">
+        <v>-30.59</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="8">
+        <f>D18/1000</f>
+        <v>-30.34348836729389</v>
+      </c>
+      <c r="E37" s="9">
+        <f>E18/1000</f>
         <v>-30.34348836729394</v>
       </c>
-      <c r="C37" s="4">
-        <f>C18/1000</f>
-        <v>-30.34348836729389</v>
-      </c>
-      <c r="D37" s="4">
-        <f>D18/1000</f>
+      <c r="F37" s="9">
+        <f>F18/1000</f>
+        <v>-30.39376092033066</v>
+      </c>
+      <c r="G37" s="9">
+        <f>G18/1000</f>
+        <v>-30.393760920330688</v>
+      </c>
+      <c r="H37" s="9">
+        <f>H18/1000</f>
+        <v>-30.34348836729388</v>
+      </c>
+      <c r="J37" s="9">
+        <f>J18/1000</f>
         <v>-30.063153022915042</v>
       </c>
-      <c r="E37" s="4">
-        <f>E18/1000</f>
-        <v>-30.34348836729388</v>
-      </c>
-      <c r="F37" s="4">
-        <v>-30.59</v>
-      </c>
+      <c r="K37" s="9">
+        <f>K18/1000</f>
+        <v>-30.062161487294002</v>
+      </c>
+      <c r="M37" s="9"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="B38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="M38" s="9"/>
     </row>
     <row r="39" ht="14.25">
       <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="4">
+        <v>42</v>
+      </c>
+      <c r="B39" s="9">
         <f>SUM(B36:B37)</f>
+        <v>13.099999999999998</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="8">
+        <f>SUM(D36:D37)</f>
+        <v>14.322573334357511</v>
+      </c>
+      <c r="E39" s="9">
+        <f>SUM(E36:E37)</f>
         <v>14.799255030891896</v>
       </c>
-      <c r="C39" s="4">
-        <f>SUM(C36:C37)</f>
-        <v>14.322573334357511</v>
-      </c>
-      <c r="D39" s="4">
-        <f>SUM(D36:D37)</f>
+      <c r="F39" s="9">
+        <f>SUM(F36:F37)</f>
+        <v>15.085681406892594</v>
+      </c>
+      <c r="G39" s="9">
+        <f>SUM(G36:G37)</f>
+        <v>15.725861967202686</v>
+      </c>
+      <c r="H39" s="9">
+        <f>SUM(H36:H37)</f>
+        <v>16.135813825225405</v>
+      </c>
+      <c r="J39" s="9">
+        <f>SUM(J36:J37)</f>
         <v>14.708514258267787</v>
       </c>
-      <c r="E39" s="4">
-        <f>SUM(E36:E37)</f>
-        <v>16.135813825225405</v>
-      </c>
-      <c r="F39" s="4">
-        <f>SUM(F36:F37)</f>
-        <v>13.099999999999998</v>
-      </c>
+      <c r="K39" s="9">
+        <f>SUM(K36:K37)</f>
+        <v>14.422331569064074</v>
+      </c>
+      <c r="M39" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/analysis/comparison_results_EUS_costs.xlsx
+++ b/analysis/comparison_results_EUS_costs.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>EUS</t>
   </si>
@@ -45,6 +45,12 @@
     <t xml:space="preserve">ins20 M_theta=75</t>
   </si>
   <si>
+    <t xml:space="preserve">ins80 M_theta=75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ins20_ 12_08</t>
+  </si>
+  <si>
     <t>Concept</t>
   </si>
   <si>
@@ -60,6 +66,9 @@
     <t xml:space="preserve">CAPEX onshore pipe</t>
   </si>
   <si>
+    <t xml:space="preserve">CAPEX onshore pipe (insulation only)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CAPEX offshore pipe</t>
   </si>
   <si>
@@ -102,10 +111,13 @@
     <t>TOTAL</t>
   </si>
   <si>
+    <t xml:space="preserve">Onshore pipeline insulation CAPEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onshore pipeline insulation OPEX</t>
+  </si>
+  <si>
     <t xml:space="preserve">Onshore pipelines CAPEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onshore pipeline insulation </t>
   </si>
   <si>
     <t xml:space="preserve">Onshore pipelines OPEX</t>
@@ -216,9 +228,6 @@
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -226,6 +235,7 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -732,10 +742,9 @@
     <col customWidth="1" min="3" max="3" width="3.28125"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="12.04296875"/>
     <col bestFit="1" min="5" max="8" width="12.04296875"/>
-    <col customWidth="1" min="9" max="9" width="4.28125"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="12.04296875"/>
     <col bestFit="1" min="10" max="10" width="16.421875"/>
-    <col bestFit="1" min="11" max="11" width="16.22265625"/>
-    <col bestFit="1" min="12" max="12" width="12.50390625"/>
+    <col bestFit="1" min="11" max="12" width="16.22265625"/>
     <col min="13" max="13" width="12.50390625"/>
     <col bestFit="1" min="14" max="14" width="14.28125"/>
   </cols>
@@ -769,1120 +778,1399 @@
       <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="1"/>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5">
+      <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
         <v>69597.543222625303</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>69597.543222625289</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>69634.329084374185</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>69634.329084374462</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>69597.54322262542</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="4">
         <v>69392.390164436889</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="4">
+        <v>69593.258801737524</v>
+      </c>
+      <c r="L3" s="4">
         <v>69391.693142625372</v>
       </c>
-      <c r="M3" s="6"/>
+      <c r="N3" s="4">
+        <v>69593.258801737524</v>
+      </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
         <v>4060.9494800000002</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>4060.9494799999989</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>4060.9494799999779</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>4060.9494800000039</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>4060.9494800000002</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>4060.9494799999861</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
+        <v>4060.9494800000139</v>
+      </c>
+      <c r="L4" s="4">
         <v>4060.9494799999961</v>
       </c>
-      <c r="M4" s="6"/>
+      <c r="N4" s="4">
+        <v>4060.9494800000139</v>
+      </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5">
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
         <v>2822.479555469386</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>3172.428797102089</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>3210.316269888182</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <v>3570.539649473827</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>3585.656305035935</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>2754.4067292287959</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="4">
+        <v>2520.9419442099361</v>
+      </c>
+      <c r="L5" s="4">
         <v>2728.6918029066019</v>
       </c>
-      <c r="M5" s="6"/>
+      <c r="N5" s="4">
+        <v>2520.9419442099361</v>
+      </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5">
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>491.17766999999998</v>
+      </c>
+      <c r="F6" s="4">
+        <v>809.79908999999998</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1105.9221</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1152.8978</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>185.83815000000001</v>
+      </c>
+      <c r="L6">
+        <v>4.4829999999999997</v>
+      </c>
+      <c r="N6" s="4">
+        <v>185.83815000000001</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4">
         <v>98.422962059999989</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E7" s="4">
         <v>165.10938333999991</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F7" s="4">
         <v>148.9714454999999</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G7" s="4">
         <v>148.97144549999999</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H7" s="4">
         <v>148.9714455000001</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J7" s="4">
         <v>148.97144549999999</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K7" s="4">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="L7" s="4">
         <v>165.10938333999891</v>
       </c>
-      <c r="M6" s="6"/>
-    </row>
-    <row r="7" ht="14.25">
-      <c r="A7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5">
+      <c r="N7" s="4">
+        <v>148.97144549999999</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4">
         <v>23586.962899999999</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E8" s="4">
         <v>23586.962899999999</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F8" s="4">
         <v>24049.61923</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G8" s="4">
         <v>24054.558690000002</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H8" s="4">
         <v>23774.429339999999</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J8" s="4">
         <v>23723.679469999999</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K8" s="4">
+        <v>23819.947670000001</v>
+      </c>
+      <c r="L8" s="4">
         <v>23679.195970000001</v>
       </c>
-      <c r="M7" s="6"/>
-    </row>
-    <row r="8" ht="14.25">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5">
+      <c r="N8" s="4">
+        <v>23819.947670000001</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4">
         <v>940.61582583106713</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E9" s="4">
         <v>756.61017611282034</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F9" s="4">
         <v>650.00889925084607</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G9" s="4">
         <v>730.0148860209132</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H9" s="4">
         <v>1143.9975968240331</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J9" s="4">
         <v>960.25576080048108</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K9" s="4">
+        <v>638.30587591942526</v>
+      </c>
+      <c r="L9" s="4">
         <v>804.70709756845656</v>
       </c>
-      <c r="M8" s="6"/>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="A9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5">
+      <c r="N9" s="4">
+        <v>638.30587591942526</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4">
         <v>861.29550492504598</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E10" s="4">
         <v>959.55380296238513</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F10" s="4">
         <v>862.45703766490078</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G10" s="4">
         <v>967.71333735433677</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H10" s="4">
         <v>974.80145458214008</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J10" s="4">
         <v>776.20692015063798</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K10" s="4">
+        <v>706.58427243303038</v>
+      </c>
+      <c r="L10" s="4">
         <v>800.2757575545179</v>
       </c>
-      <c r="M9" s="6"/>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="A10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5">
-        <v>149.2337224143092</v>
-      </c>
-      <c r="F10" s="5">
-        <v>212.57460395924869</v>
-      </c>
-      <c r="G10" s="5">
-        <v>309.17249442743878</v>
-      </c>
-      <c r="H10" s="5">
-        <v>307.37163604812002</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5">
-        <v>0.5828006912</v>
-      </c>
-      <c r="M10" s="6"/>
+      <c r="N10" s="4">
+        <v>706.58427243303038</v>
+      </c>
     </row>
     <row r="11" ht="14.25">
       <c r="A11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5">
+        <v>21</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <v>149.2337224143092</v>
+      </c>
+      <c r="F11" s="4">
+        <v>212.57460395924869</v>
+      </c>
+      <c r="G11" s="4">
+        <v>309.17249442743878</v>
+      </c>
+      <c r="H11" s="4">
+        <v>307.37163604812002</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4">
+        <v>54.851794055020378</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0.5828006912</v>
+      </c>
+      <c r="N11" s="4">
+        <v>185.83815010787461</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4">
         <v>35.417730949999999</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E12" s="4">
         <v>55.639340949999998</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F12" s="4">
         <v>46.970104149999997</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G12" s="4">
         <v>46.970104149999997</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H12" s="4">
         <v>46.970104149999997</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J12" s="4">
         <v>46.970104149999997</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K12" s="4">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="L12" s="4">
         <v>55.639340949999998</v>
       </c>
-      <c r="M11" s="6"/>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5">
+      <c r="N12" s="4">
+        <v>46.970104149999997</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4">
         <v>1585.91461</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E13" s="4">
         <v>1585.91461</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F13" s="4">
         <v>1637.56744</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G13" s="4">
         <v>1638.1152</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H13" s="4">
         <v>1606.8459499999999</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J13" s="4">
         <v>1601.1893399999999</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K13" s="4">
+        <v>1611.9264000000001</v>
+      </c>
+      <c r="L13" s="4">
         <v>1596.2213999999999</v>
       </c>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5">
+      <c r="N13" s="4">
+        <v>1611.9264000000001</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4">
         <v>46.212072067103257</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E14" s="4">
         <v>36.562164955427981</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F14" s="4">
         <v>28.0167534975525</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G14" s="4">
         <v>29.412129022385631</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H14" s="4">
         <v>59.589611248039077</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J14" s="4">
         <v>48.290297872142027</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K14" s="4">
+        <v>27.0567194837393</v>
+      </c>
+      <c r="L14" s="4">
         <v>33.7948929984911</v>
       </c>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5">
+      <c r="N14" s="4">
+        <v>27.0567194837393</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4">
         <v>10339.488788988891</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E15" s="4">
         <v>10339.488788988891</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F15" s="4">
         <v>10344.95345049641</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G15" s="4">
         <v>10344.95345049645</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H15" s="4">
         <v>10339.488788988911</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J15" s="4">
         <v>10309.01481623552</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K15" s="4">
+        <v>10338.8523240865</v>
+      </c>
+      <c r="L15" s="4">
         <v>10308.9042769889</v>
       </c>
-      <c r="M14" s="6"/>
-    </row>
-    <row r="15" ht="14.25">
-      <c r="A15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5">
+      <c r="N15" s="4">
+        <v>10338.8523240865</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4">
         <v>288.30227135991117</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E16" s="4">
         <v>274.29023135991338</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F16" s="4">
         <v>227.0376128161314</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G16" s="4">
         <v>218.2520210880229</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H16" s="4">
         <v>430.23048014211258</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J16" s="4">
         <v>341.73291724526467</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K16" s="4">
+        <v>208.72499015910671</v>
+      </c>
+      <c r="L16" s="4">
         <v>250.42085335991359</v>
       </c>
-      <c r="M15" s="6"/>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5">
+      <c r="N16" s="4">
+        <v>208.72499015910671</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4">
         <v>0</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E17" s="4">
         <v>0</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F17" s="4">
         <v>0</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G17" s="4">
         <v>0</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H17" s="4">
         <v>0</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J17" s="4">
         <v>0</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K17" s="4">
         <v>0</v>
       </c>
-      <c r="M16" s="6"/>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="A17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5">
+      <c r="L17" s="4">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4">
         <v>92623.050287719947</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E18" s="4">
         <v>92623.050287719874</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F18" s="4">
         <v>92479.201967459187</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G18" s="4">
         <v>92479.201967458517</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H18" s="4">
         <v>92623.05028772002</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J18" s="4">
         <v>93090.997181584316</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K18" s="4">
+        <v>92639.804190406634</v>
+      </c>
+      <c r="L18" s="4">
         <v>92922.050927719931</v>
       </c>
-      <c r="M17" s="6"/>
-    </row>
-    <row r="18" ht="14.25">
-      <c r="A18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5">
+      <c r="N18" s="4">
+        <v>92639.804190406634</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4">
         <v>-30343.488367293889</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E19" s="4">
         <v>-30343.48836729394</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F19" s="4">
         <v>-30393.76092033066</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G19" s="4">
         <v>-30393.760920330689</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H19" s="4">
         <v>-30343.488367293881</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J19" s="4">
         <v>-30063.153022915041</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K19" s="4">
+        <v>-30337.633161895152</v>
+      </c>
+      <c r="L19" s="4">
         <v>-30062.161487294001</v>
       </c>
-      <c r="M18" s="6"/>
-    </row>
-    <row r="19" ht="14.25">
-      <c r="A19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5">
+      <c r="N19" s="4">
+        <v>-30337.633161895152</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4">
         <v>176543.16684470279</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E20" s="4">
         <v>176870.61481882271</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F20" s="4">
         <v>176986.63785476671</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G20" s="4">
         <v>177530.22052460819</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H20" s="4">
         <v>178049.0356995227</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J20" s="4">
         <v>177191.90160428901</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K20" s="4">
+        <v>176024.66105619079</v>
+      </c>
+      <c r="L20" s="4">
         <v>176735.4928387182</v>
       </c>
-      <c r="M19" s="6"/>
-    </row>
-    <row r="20" ht="14.25">
-      <c r="D20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="N20" s="4">
+        <v>176024.66105619079</v>
+      </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="D21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="D21" s="4"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="D22" s="5"/>
-      <c r="H22" s="5"/>
+      <c r="D22" s="4"/>
+      <c r="H22" s="4"/>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23">
+      <c r="A23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="6">
+        <v>0</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="7">
+        <f>D6</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <f>E6</f>
+        <v>491.17766999999998</v>
+      </c>
+      <c r="F23" s="8">
+        <f>F6</f>
+        <v>809.79908999999998</v>
+      </c>
+      <c r="G23" s="8">
+        <f>G6</f>
+        <v>1105.9221</v>
+      </c>
+      <c r="H23" s="8">
+        <f>H6</f>
+        <v>1152.8978</v>
+      </c>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8">
+        <f>J6</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="8">
+        <f>K6</f>
+        <v>185.83815000000001</v>
+      </c>
+      <c r="L23" s="8">
+        <f>L6</f>
+        <v>4.4829999999999997</v>
+      </c>
+      <c r="N23" s="8">
+        <f>N6</f>
+        <v>185.83815000000001</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="9">
+        <f>B11/1000</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="7">
+        <f>D11</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="8">
+        <f>E11</f>
+        <v>149.2337224143092</v>
+      </c>
+      <c r="F24" s="8">
+        <f>F11</f>
+        <v>212.57460395924869</v>
+      </c>
+      <c r="G24" s="8">
+        <f>G11</f>
+        <v>309.17249442743878</v>
+      </c>
+      <c r="H24" s="8">
+        <f>H11</f>
+        <v>307.37163604812002</v>
+      </c>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8">
+        <f>J11</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="8">
+        <f>K11</f>
+        <v>54.851794055020378</v>
+      </c>
+      <c r="L24" s="8">
+        <f>L11</f>
+        <v>0.5828006912</v>
+      </c>
+      <c r="N24" s="8">
+        <f>N11</f>
+        <v>185.83815010787461</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26">
         <v>2.1499999999999999</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8">
+      <c r="C26" s="6"/>
+      <c r="D26" s="7">
         <f>D5/1000</f>
         <v>2.822479555469386</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E26" s="9">
         <f>E5/1000</f>
         <v>3.1724287971020888</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F26" s="9">
         <f>F5/1000</f>
         <v>3.2103162698881822</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G26" s="9">
         <f>G5/1000</f>
         <v>3.5705396494738268</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H26" s="9">
         <f>H5/1000</f>
         <v>3.5856563050359349</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J26" s="9">
         <f>J5/1000</f>
         <v>2.7544067292287959</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K26" s="9">
         <f>K5/1000</f>
+        <v>2.5209419442099361</v>
+      </c>
+      <c r="L26" s="9">
+        <f>L5/1000</f>
         <v>2.7286918029066021</v>
       </c>
-      <c r="M23" s="8"/>
-    </row>
-    <row r="24" ht="14.25">
-      <c r="A24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="9">
-        <f>B10/1000</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8">
-        <f>D10/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="9">
-        <f>E10/1000</f>
-        <v>0.14923372241430921</v>
-      </c>
-      <c r="F24" s="9">
-        <f>F10/1000</f>
-        <v>0.21257460395924868</v>
-      </c>
-      <c r="G24" s="9">
-        <f>G10/1000</f>
-        <v>0.30917249442743877</v>
-      </c>
-      <c r="H24" s="9">
-        <f>H10/1000</f>
-        <v>0.30737163604812001</v>
-      </c>
-      <c r="J24" s="9">
-        <f>J10/1000</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="9">
-        <f>K10/1000</f>
-        <v>5.8280069119999998e-04</v>
-      </c>
-      <c r="M24" s="9"/>
-    </row>
-    <row r="25" ht="14.25">
-      <c r="A25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8">
-        <f>D9/1000</f>
-        <v>0.86129550492504603</v>
-      </c>
-      <c r="E25" s="9">
-        <f>E9/1000</f>
-        <v>0.95955380296238513</v>
-      </c>
-      <c r="F25" s="9">
-        <f>F9/1000</f>
-        <v>0.86245703766490078</v>
-      </c>
-      <c r="G25" s="9">
-        <f>G9/1000</f>
-        <v>0.96771333735433673</v>
-      </c>
-      <c r="H25" s="9">
-        <f>H9/1000</f>
-        <v>0.97480145458214007</v>
-      </c>
-      <c r="J25" s="9">
-        <f>J9/1000</f>
-        <v>0.77620692015063797</v>
-      </c>
-      <c r="K25" s="9">
-        <f>K9/1000</f>
-        <v>0.80027575755451785</v>
-      </c>
-      <c r="M25" s="8"/>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="A26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8">
-        <f>D6/1000</f>
-        <v>9.8422962059999994e-02</v>
-      </c>
-      <c r="E26" s="9">
-        <f>E6/1000</f>
-        <v>0.16510938333999992</v>
-      </c>
-      <c r="F26" s="9">
-        <f>F6/1000</f>
-        <v>0.14897144549999991</v>
-      </c>
-      <c r="G26" s="9">
-        <f>G6/1000</f>
-        <v>0.14897144549999999</v>
-      </c>
-      <c r="H26" s="9">
-        <f>H6/1000</f>
-        <v>0.1489714455000001</v>
-      </c>
-      <c r="J26" s="9">
-        <f>J6/1000</f>
-        <v>0.14897144549999999</v>
-      </c>
-      <c r="K26" s="9">
-        <f>K6/1000</f>
-        <v>0.16510938333999892</v>
-      </c>
-      <c r="M26" s="8"/>
+      <c r="N26" s="9">
+        <f>N5/1000</f>
+        <v>2.5209419442099361</v>
+      </c>
     </row>
     <row r="27" ht="14.25">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B27">
-        <v>5.0000000000000003e-02</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8">
-        <f>D11/1000</f>
-        <v>3.5417730949999997e-02</v>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="7">
+        <f>D10/1000</f>
+        <v>0.86129550492504603</v>
       </c>
       <c r="E27" s="9">
-        <f>E11/1000</f>
-        <v>5.5639340949999998e-02</v>
+        <f>E10/1000</f>
+        <v>0.95955380296238513</v>
       </c>
       <c r="F27" s="9">
-        <f>F11/1000</f>
-        <v>4.6970104149999997e-02</v>
+        <f>F10/1000</f>
+        <v>0.86245703766490078</v>
       </c>
       <c r="G27" s="9">
-        <f>G11/1000</f>
-        <v>4.6970104149999997e-02</v>
+        <f>G10/1000</f>
+        <v>0.96771333735433673</v>
       </c>
       <c r="H27" s="9">
-        <f>H11/1000</f>
-        <v>4.6970104149999997e-02</v>
+        <f>H10/1000</f>
+        <v>0.97480145458214007</v>
       </c>
       <c r="J27" s="9">
-        <f>J11/1000</f>
-        <v>4.6970104149999997e-02</v>
+        <f>J10/1000</f>
+        <v>0.77620692015063797</v>
       </c>
       <c r="K27" s="9">
-        <f>K11/1000</f>
-        <v>5.5639340949999998e-02</v>
-      </c>
-      <c r="M27" s="8"/>
+        <f>K10/1000</f>
+        <v>0.70658427243303035</v>
+      </c>
+      <c r="L27" s="9">
+        <f>L10/1000</f>
+        <v>0.80027575755451785</v>
+      </c>
+      <c r="N27" s="9">
+        <f>N10/1000</f>
+        <v>0.70658427243303035</v>
+      </c>
     </row>
     <row r="28" ht="14.25">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28">
-        <v>23.57</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="D28" s="7">
         <f>D7/1000</f>
-        <v>23.5869629</v>
+        <v>9.8422962059999994e-02</v>
       </c>
       <c r="E28" s="9">
         <f>E7/1000</f>
-        <v>23.5869629</v>
+        <v>0.16510938333999992</v>
       </c>
       <c r="F28" s="9">
         <f>F7/1000</f>
-        <v>24.049619230000001</v>
+        <v>0.14897144549999991</v>
       </c>
       <c r="G28" s="9">
         <f>G7/1000</f>
-        <v>24.05455869</v>
+        <v>0.14897144549999999</v>
       </c>
       <c r="H28" s="9">
         <f>H7/1000</f>
-        <v>23.774429339999998</v>
+        <v>0.1489714455000001</v>
       </c>
       <c r="J28" s="9">
         <f>J7/1000</f>
-        <v>23.72367947</v>
+        <v>0.14897144549999999</v>
       </c>
       <c r="K28" s="9">
         <f>K7/1000</f>
-        <v>23.679195970000002</v>
-      </c>
-      <c r="M28" s="8"/>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="L28" s="9">
+        <f>L7/1000</f>
+        <v>0.16510938333999892</v>
+      </c>
+      <c r="N28" s="9">
+        <f>N7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
     </row>
     <row r="29" ht="14.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29">
-        <v>1.5800000000000001</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8">
+        <v>5.0000000000000003e-02</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="7">
         <f>D12/1000</f>
-        <v>1.5859146100000001</v>
+        <v>3.5417730949999997e-02</v>
       </c>
       <c r="E29" s="9">
         <f>E12/1000</f>
-        <v>1.5859146100000001</v>
+        <v>5.5639340949999998e-02</v>
       </c>
       <c r="F29" s="9">
         <f>F12/1000</f>
-        <v>1.63756744</v>
+        <v>4.6970104149999997e-02</v>
       </c>
       <c r="G29" s="9">
         <f>G12/1000</f>
-        <v>1.6381151999999999</v>
+        <v>4.6970104149999997e-02</v>
       </c>
       <c r="H29" s="9">
         <f>H12/1000</f>
-        <v>1.6068459499999999</v>
+        <v>4.6970104149999997e-02</v>
       </c>
       <c r="J29" s="9">
         <f>J12/1000</f>
-        <v>1.6011893399999999</v>
+        <v>4.6970104149999997e-02</v>
       </c>
       <c r="K29" s="9">
         <f>K12/1000</f>
-        <v>1.5962213999999999</v>
-      </c>
-      <c r="M29" s="8"/>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="L29" s="9">
+        <f>L12/1000</f>
+        <v>5.5639340949999998e-02</v>
+      </c>
+      <c r="N29" s="9">
+        <f>N12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30">
-        <v>10.57</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8">
-        <f>D14/1000</f>
-        <v>10.339488788988891</v>
+        <v>23.57</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="7">
+        <f>D8/1000</f>
+        <v>23.5869629</v>
       </c>
       <c r="E30" s="9">
-        <f>E14/1000</f>
-        <v>10.339488788988891</v>
+        <f>E8/1000</f>
+        <v>23.5869629</v>
       </c>
       <c r="F30" s="9">
-        <f>F14/1000</f>
-        <v>10.34495345049641</v>
+        <f>F8/1000</f>
+        <v>24.049619230000001</v>
       </c>
       <c r="G30" s="9">
-        <f>G14/1000</f>
-        <v>10.344953450496451</v>
+        <f>G8/1000</f>
+        <v>24.05455869</v>
       </c>
       <c r="H30" s="9">
-        <f>H14/1000</f>
-        <v>10.339488788988911</v>
+        <f>H8/1000</f>
+        <v>23.774429339999998</v>
       </c>
       <c r="J30" s="9">
-        <f>J14/1000</f>
-        <v>10.30901481623552</v>
+        <f>J8/1000</f>
+        <v>23.72367947</v>
       </c>
       <c r="K30" s="9">
-        <f>K14/1000</f>
-        <v>10.308904276988899</v>
-      </c>
-      <c r="M30" s="8"/>
+        <f>K8/1000</f>
+        <v>23.819947670000001</v>
+      </c>
+      <c r="L30" s="9">
+        <f>L8/1000</f>
+        <v>23.679195970000002</v>
+      </c>
+      <c r="N30" s="9">
+        <f>N8/1000</f>
+        <v>23.819947670000001</v>
+      </c>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B31">
-        <v>0.62</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8">
-        <f>D8/1000</f>
-        <v>0.94061582583106718</v>
+        <v>1.5800000000000001</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="7">
+        <f>D13/1000</f>
+        <v>1.5859146100000001</v>
       </c>
       <c r="E31" s="9">
-        <f>E8/1000</f>
-        <v>0.75661017611282033</v>
+        <f>E13/1000</f>
+        <v>1.5859146100000001</v>
       </c>
       <c r="F31" s="9">
-        <f>F8/1000</f>
-        <v>0.65000889925084604</v>
+        <f>F13/1000</f>
+        <v>1.63756744</v>
       </c>
       <c r="G31" s="9">
-        <f>G8/1000</f>
-        <v>0.73001488602091325</v>
+        <f>G13/1000</f>
+        <v>1.6381151999999999</v>
       </c>
       <c r="H31" s="9">
-        <f>H8/1000</f>
-        <v>1.143997596824033</v>
+        <f>H13/1000</f>
+        <v>1.6068459499999999</v>
       </c>
       <c r="J31" s="9">
-        <f>J8/1000</f>
-        <v>0.96025576080048114</v>
+        <f>J13/1000</f>
+        <v>1.6011893399999999</v>
       </c>
       <c r="K31" s="9">
-        <f>K8/1000</f>
-        <v>0.8047070975684566</v>
-      </c>
-      <c r="M31" s="8"/>
+        <f>K13/1000</f>
+        <v>1.6119264</v>
+      </c>
+      <c r="L31" s="9">
+        <f>L13/1000</f>
+        <v>1.5962213999999999</v>
+      </c>
+      <c r="N31" s="9">
+        <f>N13/1000</f>
+        <v>1.6119264</v>
+      </c>
     </row>
     <row r="32" ht="14.25">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32">
-        <v>2.9999999999999999e-02</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8">
-        <f>D13/1000</f>
-        <v>4.621207206710326e-02</v>
+        <v>10.57</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="7">
+        <f>D15/1000</f>
+        <v>10.339488788988891</v>
       </c>
       <c r="E32" s="9">
-        <f>E13/1000</f>
-        <v>3.6562164955427981e-02</v>
+        <f>E15/1000</f>
+        <v>10.339488788988891</v>
       </c>
       <c r="F32" s="9">
-        <f>F13/1000</f>
-        <v>2.8016753497552501e-02</v>
+        <f>F15/1000</f>
+        <v>10.34495345049641</v>
       </c>
       <c r="G32" s="9">
-        <f>G13/1000</f>
-        <v>2.941212902238563e-02</v>
+        <f>G15/1000</f>
+        <v>10.344953450496451</v>
       </c>
       <c r="H32" s="9">
-        <f>H13/1000</f>
-        <v>5.9589611248039076e-02</v>
+        <f>H15/1000</f>
+        <v>10.339488788988911</v>
       </c>
       <c r="J32" s="9">
-        <f>J13/1000</f>
-        <v>4.8290297872142028e-02</v>
+        <f>J15/1000</f>
+        <v>10.30901481623552</v>
       </c>
       <c r="K32" s="9">
-        <f>K13/1000</f>
-        <v>3.3794892998491102e-02</v>
-      </c>
-      <c r="M32" s="8"/>
+        <f>K15/1000</f>
+        <v>10.338852324086499</v>
+      </c>
+      <c r="L32" s="9">
+        <f>L15/1000</f>
+        <v>10.308904276988899</v>
+      </c>
+      <c r="N32" s="9">
+        <f>N15/1000</f>
+        <v>10.338852324086499</v>
+      </c>
     </row>
     <row r="33" ht="14.25">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B33">
-        <v>0.22</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8">
-        <f>D15/1000</f>
-        <v>0.28830227135991116</v>
+        <v>0.62</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="7">
+        <f>D9/1000</f>
+        <v>0.94061582583106718</v>
       </c>
       <c r="E33" s="9">
-        <f>E15/1000</f>
-        <v>0.27429023135991337</v>
+        <f>E9/1000</f>
+        <v>0.75661017611282033</v>
       </c>
       <c r="F33" s="9">
-        <f>F15/1000</f>
-        <v>0.22703761281613141</v>
+        <f>F9/1000</f>
+        <v>0.65000889925084604</v>
       </c>
       <c r="G33" s="9">
-        <f>G15/1000</f>
-        <v>0.21825202108802291</v>
+        <f>G9/1000</f>
+        <v>0.73001488602091325</v>
       </c>
       <c r="H33" s="9">
-        <f>H15/1000</f>
-        <v>0.43023048014211257</v>
+        <f>H9/1000</f>
+        <v>1.143997596824033</v>
       </c>
       <c r="J33" s="9">
-        <f>J15/1000</f>
-        <v>0.34173291724526467</v>
+        <f>J9/1000</f>
+        <v>0.96025576080048114</v>
       </c>
       <c r="K33" s="9">
-        <f>K15/1000</f>
-        <v>0.2504208533599136</v>
-      </c>
-      <c r="M33" s="8"/>
+        <f>K9/1000</f>
+        <v>0.63830587591942523</v>
+      </c>
+      <c r="L33" s="9">
+        <f>L9/1000</f>
+        <v>0.8047070975684566</v>
+      </c>
+      <c r="N33" s="9">
+        <f>N9/1000</f>
+        <v>0.63830587591942523</v>
+      </c>
     </row>
     <row r="34" ht="14.25">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B34">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="7">
+        <f>D14/1000</f>
+        <v>4.621207206710326e-02</v>
+      </c>
+      <c r="E34" s="9">
+        <f>E14/1000</f>
+        <v>3.6562164955427981e-02</v>
+      </c>
+      <c r="F34" s="9">
+        <f>F14/1000</f>
+        <v>2.8016753497552501e-02</v>
+      </c>
+      <c r="G34" s="9">
+        <f>G14/1000</f>
+        <v>2.941212902238563e-02</v>
+      </c>
+      <c r="H34" s="9">
+        <f>H14/1000</f>
+        <v>5.9589611248039076e-02</v>
+      </c>
+      <c r="J34" s="9">
+        <f>J14/1000</f>
+        <v>4.8290297872142028e-02</v>
+      </c>
+      <c r="K34" s="9">
+        <f>K14/1000</f>
+        <v>2.7056719483739302e-02</v>
+      </c>
+      <c r="L34" s="9">
+        <f>L14/1000</f>
+        <v>3.3794892998491102e-02</v>
+      </c>
+      <c r="N34" s="9">
+        <f>N14/1000</f>
+        <v>2.7056719483739302e-02</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35">
+        <v>0.22</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="7">
+        <f>D16/1000</f>
+        <v>0.28830227135991116</v>
+      </c>
+      <c r="E35" s="9">
+        <f>E16/1000</f>
+        <v>0.27429023135991337</v>
+      </c>
+      <c r="F35" s="9">
+        <f>F16/1000</f>
+        <v>0.22703761281613141</v>
+      </c>
+      <c r="G35" s="9">
+        <f>G16/1000</f>
+        <v>0.21825202108802291</v>
+      </c>
+      <c r="H35" s="9">
+        <f>H16/1000</f>
+        <v>0.43023048014211257</v>
+      </c>
+      <c r="J35" s="9">
+        <f>J16/1000</f>
+        <v>0.34173291724526467</v>
+      </c>
+      <c r="K35" s="9">
+        <f>K16/1000</f>
+        <v>0.2087249901591067</v>
+      </c>
+      <c r="L35" s="9">
+        <f>L16/1000</f>
+        <v>0.2504208533599136</v>
+      </c>
+      <c r="N35" s="9">
+        <f>N16/1000</f>
+        <v>0.2087249901591067</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36">
         <v>4.1799999999999997</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8">
+      <c r="C36" s="6"/>
+      <c r="D36" s="7">
         <f>D4/1000</f>
         <v>4.0609494800000006</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E36" s="9">
         <f>E4/1000</f>
         <v>4.0609494799999988</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F36" s="9">
         <f>F4/1000</f>
         <v>4.0609494799999784</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G36" s="9">
         <f>G4/1000</f>
         <v>4.0609494800000041</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H36" s="9">
         <f>H4/1000</f>
         <v>4.0609494800000006</v>
       </c>
-      <c r="J34" s="9">
+      <c r="J36" s="9">
         <f>J4/1000</f>
         <v>4.0609494799999863</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K36" s="9">
         <f>K4/1000</f>
+        <v>4.0609494800000139</v>
+      </c>
+      <c r="L36" s="9">
+        <f>L4/1000</f>
         <v>4.0609494799999961</v>
       </c>
-      <c r="M34" s="8"/>
-    </row>
-    <row r="35" ht="14.25">
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="M35" s="8"/>
-    </row>
-    <row r="36" ht="14.25">
-      <c r="A36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="9">
-        <f>SUM(B23:B34)</f>
+      <c r="N36" s="9">
+        <f>N4/1000</f>
+        <v>4.0609494800000139</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="N37" s="9"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="8">
+        <f>SUM(B26:B36)</f>
         <v>43.689999999999998</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8">
-        <f>SUM(D23:D34)</f>
+      <c r="C38" s="8"/>
+      <c r="D38" s="7">
+        <f>SUM(D26:D36)</f>
         <v>44.666061701651401</v>
       </c>
-      <c r="E36" s="9">
-        <f>SUM(E23:E34)</f>
-        <v>45.142743398185836</v>
-      </c>
-      <c r="F36" s="9">
-        <f>SUM(F23:F34)</f>
-        <v>45.479442327223254</v>
-      </c>
-      <c r="G36" s="9">
-        <f>SUM(G23:G34)</f>
-        <v>46.119622887533374</v>
-      </c>
-      <c r="H36" s="9">
-        <f>SUM(H23:H34)</f>
-        <v>46.479302192519285</v>
-      </c>
-      <c r="J36" s="9">
-        <f>SUM(J23:J34)</f>
+      <c r="E38" s="8">
+        <f>SUM(E26:E36)</f>
+        <v>44.99350967577152</v>
+      </c>
+      <c r="F38" s="8">
+        <f>SUM(F26:F36)</f>
+        <v>45.266867723264006</v>
+      </c>
+      <c r="G38" s="8">
+        <f>SUM(G26:G36)</f>
+        <v>45.810450393105931</v>
+      </c>
+      <c r="H38" s="8">
+        <f>SUM(H26:H36)</f>
+        <v>46.171930556471168</v>
+      </c>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8">
+        <f>SUM(J26:J36)</f>
         <v>44.771667281182829</v>
       </c>
-      <c r="K36" s="9">
-        <f>SUM(K23:K34)</f>
-        <v>44.484493056358076</v>
-      </c>
-      <c r="M36" s="9"/>
-    </row>
-    <row r="37" ht="14.25">
-      <c r="A37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="9">
-        <v>-30.59</v>
-      </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8">
-        <f>D18/1000</f>
-        <v>-30.34348836729389</v>
-      </c>
-      <c r="E37" s="9">
-        <f>E18/1000</f>
-        <v>-30.34348836729394</v>
-      </c>
-      <c r="F37" s="9">
-        <f>F18/1000</f>
-        <v>-30.39376092033066</v>
-      </c>
-      <c r="G37" s="9">
-        <f>G18/1000</f>
-        <v>-30.393760920330688</v>
-      </c>
-      <c r="H37" s="9">
-        <f>H18/1000</f>
-        <v>-30.34348836729388</v>
-      </c>
-      <c r="J37" s="9">
-        <f>J18/1000</f>
-        <v>-30.063153022915042</v>
-      </c>
-      <c r="K37" s="9">
-        <f>K18/1000</f>
-        <v>-30.062161487294002</v>
-      </c>
-      <c r="M37" s="9"/>
-    </row>
-    <row r="38" ht="14.25">
-      <c r="B38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="M38" s="9"/>
+      <c r="K38" s="8">
+        <f>SUM(K26:K36)</f>
+        <v>44.129231225941751</v>
+      </c>
+      <c r="L38" s="8">
+        <f>SUM(L26:L36)</f>
+        <v>44.483910255666878</v>
+      </c>
+      <c r="N38" s="8">
+        <f>SUM(N26:N36)</f>
+        <v>44.129231225941751</v>
+      </c>
     </row>
     <row r="39" ht="14.25">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B39" s="9">
-        <f>SUM(B36:B37)</f>
+        <v>-30.59</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="7">
+        <f>D19/1000</f>
+        <v>-30.34348836729389</v>
+      </c>
+      <c r="E39" s="9">
+        <f>E19/1000</f>
+        <v>-30.34348836729394</v>
+      </c>
+      <c r="F39" s="9">
+        <f>F19/1000</f>
+        <v>-30.39376092033066</v>
+      </c>
+      <c r="G39" s="9">
+        <f>G19/1000</f>
+        <v>-30.393760920330688</v>
+      </c>
+      <c r="H39" s="9">
+        <f>H19/1000</f>
+        <v>-30.34348836729388</v>
+      </c>
+      <c r="J39" s="9">
+        <f>J19/1000</f>
+        <v>-30.063153022915042</v>
+      </c>
+      <c r="K39" s="9">
+        <f>K19/1000</f>
+        <v>-30.337633161895152</v>
+      </c>
+      <c r="L39" s="9">
+        <f>L19/1000</f>
+        <v>-30.062161487294002</v>
+      </c>
+      <c r="N39" s="9">
+        <f>N19/1000</f>
+        <v>-30.337633161895152</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="B40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="N40" s="9"/>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="9">
+        <f>SUM(B38:B39)</f>
         <v>13.099999999999998</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8">
-        <f>SUM(D36:D37)</f>
+      <c r="C41" s="6"/>
+      <c r="D41" s="7">
+        <f>SUM(D38:D39)</f>
         <v>14.322573334357511</v>
       </c>
-      <c r="E39" s="9">
-        <f>SUM(E36:E37)</f>
-        <v>14.799255030891896</v>
-      </c>
-      <c r="F39" s="9">
-        <f>SUM(F36:F37)</f>
-        <v>15.085681406892594</v>
-      </c>
-      <c r="G39" s="9">
-        <f>SUM(G36:G37)</f>
-        <v>15.725861967202686</v>
-      </c>
-      <c r="H39" s="9">
-        <f>SUM(H36:H37)</f>
-        <v>16.135813825225405</v>
-      </c>
-      <c r="J39" s="9">
-        <f>SUM(J36:J37)</f>
+      <c r="E41" s="9">
+        <f>SUM(E38:E39)</f>
+        <v>14.65002130847758</v>
+      </c>
+      <c r="F41" s="9">
+        <f>SUM(F38:F39)</f>
+        <v>14.873106802933346</v>
+      </c>
+      <c r="G41" s="9">
+        <f>SUM(G38:G39)</f>
+        <v>15.416689472775243</v>
+      </c>
+      <c r="H41" s="9">
+        <f>SUM(H38:H39)</f>
+        <v>15.828442189177288</v>
+      </c>
+      <c r="J41" s="9">
+        <f>SUM(J38:J39)</f>
         <v>14.708514258267787</v>
       </c>
-      <c r="K39" s="9">
-        <f>SUM(K36:K37)</f>
-        <v>14.422331569064074</v>
-      </c>
-      <c r="M39" s="9"/>
+      <c r="K41" s="9">
+        <f>SUM(K38:K39)</f>
+        <v>13.7915980640466</v>
+      </c>
+      <c r="L41" s="9">
+        <f>SUM(L38:L39)</f>
+        <v>14.421748768372876</v>
+      </c>
+      <c r="N41" s="9">
+        <f>SUM(N38:N39)</f>
+        <v>13.7915980640466</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/analysis/comparison_results_EUS_costs.xlsx
+++ b/analysis/comparison_results_EUS_costs.xlsx
@@ -950,7 +950,7 @@
         <v>4.4829999999999997</v>
       </c>
       <c r="N6" s="4">
-        <v>185.83815000000001</v>
+        <v>185.83815010787461</v>
       </c>
     </row>
     <row r="7" ht="14.25">
@@ -1115,7 +1115,7 @@
         <v>0.5828006912</v>
       </c>
       <c r="N11" s="4">
-        <v>185.83815010787461</v>
+        <v>54.851794055020378</v>
       </c>
     </row>
     <row r="12" ht="14.25">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="N23" s="8">
         <f>N6</f>
-        <v>185.83815000000001</v>
+        <v>185.83815010787461</v>
       </c>
     </row>
     <row r="24" ht="14.25">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="N24" s="8">
         <f>N11</f>
-        <v>185.83815010787461</v>
+        <v>54.851794055020378</v>
       </c>
     </row>
     <row r="26" ht="14.25">

--- a/analysis/comparison_results_EUS_costs.xlsx
+++ b/analysis/comparison_results_EUS_costs.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>EUS</t>
   </si>
   <si>
-    <t xml:space="preserve">Zwickl Bernhard</t>
+    <t>Pau</t>
   </si>
   <si>
     <t>noins</t>
@@ -49,6 +49,33 @@
   </si>
   <si>
     <t xml:space="preserve">ins20_ 12_08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noins 45°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ins20 45°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ins40 45°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ins60 45°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ins80 45°C</t>
+  </si>
+  <si>
+    <t>ins20%</t>
+  </si>
+  <si>
+    <t>ins40%</t>
+  </si>
+  <si>
+    <t>ins60%</t>
+  </si>
+  <si>
+    <t>ins80%</t>
   </si>
   <si>
     <t>Concept</t>
@@ -184,12 +211,18 @@
       <b/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="5"/>
+        <bgColor indexed="5"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -219,12 +252,11 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -238,6 +270,10 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -738,22 +774,26 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="36.921875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="14.79296875"/>
-    <col customWidth="1" min="3" max="3" width="3.28125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="12.04296875"/>
-    <col bestFit="1" min="5" max="8" width="12.04296875"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="12.04296875"/>
-    <col bestFit="1" min="10" max="10" width="16.421875"/>
-    <col bestFit="1" min="11" max="12" width="16.22265625"/>
-    <col min="13" max="13" width="12.50390625"/>
-    <col bestFit="1" min="14" max="14" width="14.28125"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="6.93359375"/>
+    <col customWidth="1" min="3" max="3" width="4.7109375"/>
+    <col customWidth="1" min="4" max="4" width="12.04296875"/>
+    <col customWidth="1" min="5" max="8" width="9.140625"/>
+    <col customWidth="1" min="9" max="9" width="4.140625"/>
+    <col customWidth="1" min="10" max="12" width="9.140625"/>
+    <col customWidth="1" min="13" max="13" width="4.7109375"/>
+    <col customWidth="1" min="14" max="14" width="9.140625"/>
+    <col customWidth="1" min="15" max="15" width="3.7109375"/>
+    <col bestFit="1" customWidth="1" min="16" max="16" width="9.79296875"/>
+    <col bestFit="1" min="17" max="18" width="12.04296875"/>
+    <col bestFit="1" min="19" max="20" width="9.59375"/>
+    <col customWidth="1" min="22" max="22" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
@@ -781,1395 +821,2534 @@
       <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>12</v>
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4">
+      <c r="A3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
         <v>69597.543222625303</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>69597.543222625289</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>69634.329084374185</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>69634.329084374462</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="3">
         <v>69597.54322262542</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="3">
         <v>69392.390164436889</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="3">
         <v>69593.258801737524</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="3">
         <v>69391.693142625372</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="3">
         <v>69593.258801737524</v>
       </c>
+      <c r="P3" s="3">
+        <v>69607.316629999783</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>69612.092578749347</v>
+      </c>
+      <c r="R3" s="3">
+        <v>69634.329084374505</v>
+      </c>
+      <c r="S3" s="3">
+        <v>69634.329084374622</v>
+      </c>
+      <c r="V3" s="3">
+        <v>69607.316630000118</v>
+      </c>
+      <c r="W3" s="3">
+        <v>69597.543222625274</v>
+      </c>
+      <c r="X3" s="3">
+        <v>69391.693142625401</v>
+      </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
+      <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
         <v>4060.9494800000002</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>4060.9494799999989</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>4060.9494799999779</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>4060.9494800000039</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <v>4060.9494800000002</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>4060.9494799999861</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="3">
         <v>4060.9494800000139</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <v>4060.9494799999961</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="3">
         <v>4060.9494800000139</v>
       </c>
+      <c r="P4" s="3">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>4060.949480000002</v>
+      </c>
+      <c r="R4" s="3">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="S4" s="3">
+        <v>4060.949479999987</v>
+      </c>
+      <c r="V4" s="3">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="W4" s="3">
+        <v>4060.949480000002</v>
+      </c>
+      <c r="X4" s="3">
+        <v>4060.9494800000002</v>
+      </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4">
+      <c r="A5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
         <v>2822.479555469386</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>3172.428797102089</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>3210.316269888182</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>3570.539649473827</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="3">
         <v>3585.656305035935</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>2754.4067292287959</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="3">
         <v>2520.9419442099361</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>2728.6918029066019</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="3">
         <v>2520.9419442099361</v>
       </c>
+      <c r="P5" s="3">
+        <v>3035.4719047544108</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>2473.4636952706069</v>
+      </c>
+      <c r="R5" s="3">
+        <v>2810.9045367664571</v>
+      </c>
+      <c r="S5" s="3">
+        <v>2763.7644747940608</v>
+      </c>
+      <c r="V5" s="3">
+        <v>3011.7763737611531</v>
+      </c>
+      <c r="W5" s="3">
+        <v>2491.3570058783462</v>
+      </c>
+      <c r="X5" s="3">
+        <v>2940.315261938953</v>
+      </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
         <v>491.17766999999998</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>809.79908999999998</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>1105.9221</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="3">
         <v>1152.8978</v>
       </c>
-      <c r="J6" s="4">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4">
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
         <v>185.83815000000001</v>
       </c>
       <c r="L6">
         <v>4.4829999999999997</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="3">
         <v>185.83815010787461</v>
       </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>210.4018810091365</v>
+      </c>
+      <c r="R6" s="3">
+        <v>406.13277811148492</v>
+      </c>
+      <c r="S6" s="3">
+        <v>459.23456850371412</v>
+      </c>
+      <c r="V6" s="3">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3">
+        <v>203.41004422359791</v>
+      </c>
+      <c r="X6" s="3">
+        <v>440.69461639348378</v>
+      </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3">
         <v>98.422962059999989</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>165.10938333999991</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>148.9714454999999</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>148.97144549999999</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="3">
         <v>148.9714455000001</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="3">
         <v>148.97144549999999</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="3">
         <v>148.97144549999999</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="3">
         <v>165.10938333999891</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N7" s="3">
         <v>148.97144549999999</v>
       </c>
+      <c r="P7" s="3">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>165.10938333999999</v>
+      </c>
+      <c r="R7" s="3">
+        <v>148.9714454999997</v>
+      </c>
+      <c r="S7" s="3">
+        <v>165.10938333999999</v>
+      </c>
+      <c r="V7" s="3">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="W7" s="3">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="X7" s="3">
+        <v>165.10938333999999</v>
+      </c>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4">
+      <c r="A8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
         <v>23586.962899999999</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>23586.962899999999</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>24049.61923</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>24054.558690000002</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="3">
         <v>23774.429339999999</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>23723.679469999999</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="3">
         <v>23819.947670000001</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="3">
         <v>23679.195970000001</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N8" s="3">
         <v>23819.947670000001</v>
       </c>
+      <c r="P8" s="3">
+        <v>23831.502369999998</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>24005.356090000001</v>
+      </c>
+      <c r="R8" s="3">
+        <v>23831.502369999998</v>
+      </c>
+      <c r="S8" s="3">
+        <v>24050.87442</v>
+      </c>
+      <c r="V8" s="3">
+        <v>23819.947670000001</v>
+      </c>
+      <c r="W8" s="3">
+        <v>23926.322779999999</v>
+      </c>
+      <c r="X8" s="3">
+        <v>23679.195970000001</v>
+      </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4">
+      <c r="A9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3">
         <v>940.61582583106713</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>756.61017611282034</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>650.00889925084607</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>730.0148860209132</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="3">
         <v>1143.9975968240331</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="3">
         <v>960.25576080048108</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="3">
         <v>638.30587591942526</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="3">
         <v>804.70709756845656</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9" s="3">
         <v>638.30587591942526</v>
       </c>
+      <c r="P9" s="3">
+        <v>1005.98814195919</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>700.79319852844105</v>
+      </c>
+      <c r="R9" s="3">
+        <v>640.87292339114379</v>
+      </c>
+      <c r="S9" s="3">
+        <v>714.12149683434768</v>
+      </c>
+      <c r="V9" s="3">
+        <v>1024.471405513181</v>
+      </c>
+      <c r="W9" s="3">
+        <v>726.569981355952</v>
+      </c>
+      <c r="X9" s="3">
+        <v>672.74187858881464</v>
+      </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4">
+      <c r="A10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3">
         <v>861.29550492504598</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>959.55380296238513</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>862.45703766490078</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="3">
         <v>967.71333735433677</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="3">
         <v>974.80145458214008</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="3">
         <v>776.20692015063798</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="3">
         <v>706.58427243303038</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="3">
         <v>800.2757575545179</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N10" s="3">
         <v>706.58427243303038</v>
       </c>
+      <c r="P10" s="3">
+        <v>799.41261835164994</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>676.67633230917636</v>
+      </c>
+      <c r="R10" s="3">
+        <v>759.33901395087673</v>
+      </c>
+      <c r="S10" s="3">
+        <v>766.89135089267393</v>
+      </c>
+      <c r="V10" s="3">
+        <v>808.72542709314394</v>
+      </c>
+      <c r="W10" s="3">
+        <v>696.5245112513079</v>
+      </c>
+      <c r="X10" s="3">
+        <v>836.65331059579796</v>
+      </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="A11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
         <v>149.2337224143092</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>212.57460395924869</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="3">
         <v>309.17249442743878</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="3">
         <v>307.37163604812002</v>
       </c>
-      <c r="J11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4">
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
         <v>54.851794055020378</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="3">
         <v>0.5828006912</v>
       </c>
-      <c r="N11" s="4">
+      <c r="N11" s="3">
         <v>54.851794055020378</v>
       </c>
+      <c r="P11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>53.737659732956381</v>
+      </c>
+      <c r="R11" s="3">
+        <v>107.5648752189488</v>
+      </c>
+      <c r="S11" s="3">
+        <v>128.50129163889599</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0</v>
+      </c>
+      <c r="W11" s="3">
+        <v>63.142957502529988</v>
+      </c>
+      <c r="X11" s="3">
+        <v>128.79124610002</v>
+      </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4">
+      <c r="A12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3">
         <v>35.417730949999999</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>55.639340949999998</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>46.970104149999997</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="3">
         <v>46.970104149999997</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="3">
         <v>46.970104149999997</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="3">
         <v>46.970104149999997</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="3">
         <v>46.970104149999997</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="3">
         <v>55.639340949999998</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N12" s="3">
         <v>46.970104149999997</v>
       </c>
+      <c r="P12" s="3">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>55.639340949999998</v>
+      </c>
+      <c r="R12" s="3">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="S12" s="3">
+        <v>55.639340949999998</v>
+      </c>
+      <c r="V12" s="3">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="W12" s="3">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="X12" s="3">
+        <v>55.639340949999998</v>
+      </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4">
+      <c r="A13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3">
         <v>1585.91461</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>1585.91461</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <v>1637.56744</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="3">
         <v>1638.1152</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="3">
         <v>1606.8459499999999</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="3">
         <v>1601.1893399999999</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="3">
         <v>1611.9264000000001</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="3">
         <v>1596.2213999999999</v>
       </c>
-      <c r="N13" s="4">
+      <c r="N13" s="3">
         <v>1611.9264000000001</v>
       </c>
+      <c r="P13" s="3">
+        <v>1613.2147199999999</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>1632.6251999999999</v>
+      </c>
+      <c r="R13" s="3">
+        <v>1613.2147199999999</v>
+      </c>
+      <c r="S13" s="3">
+        <v>1637.7056500000001</v>
+      </c>
+      <c r="V13" s="3">
+        <v>1611.9264000000001</v>
+      </c>
+      <c r="W13" s="3">
+        <v>1623.80045</v>
+      </c>
+      <c r="X13" s="3">
+        <v>1596.2213999999999</v>
+      </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4">
+      <c r="A14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3">
         <v>46.212072067103257</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <v>36.562164955427981</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="3">
         <v>28.0167534975525</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="3">
         <v>29.412129022385631</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="3">
         <v>59.589611248039077</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="3">
         <v>48.290297872142027</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="3">
         <v>27.0567194837393</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="3">
         <v>33.7948929984911</v>
       </c>
-      <c r="N14" s="4">
+      <c r="N14" s="3">
         <v>27.0567194837393</v>
       </c>
+      <c r="P14" s="3">
+        <v>42.188342550647633</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>32.164074349346528</v>
+      </c>
+      <c r="R14" s="3">
+        <v>25.807109992933011</v>
+      </c>
+      <c r="S14" s="3">
+        <v>33.074541389620833</v>
+      </c>
+      <c r="V14" s="3">
+        <v>44.940613976118541</v>
+      </c>
+      <c r="W14" s="3">
+        <v>34.900366947641352</v>
+      </c>
+      <c r="X14" s="3">
+        <v>29.188099345928421</v>
+      </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4">
+      <c r="A15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3">
         <v>10339.488788988891</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="3">
         <v>10339.488788988891</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="3">
         <v>10344.95345049641</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="3">
         <v>10344.95345049645</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="3">
         <v>10339.488788988911</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="3">
         <v>10309.01481623552</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="3">
         <v>10338.8523240865</v>
       </c>
-      <c r="L15" s="4">
+      <c r="L15" s="3">
         <v>10308.9042769889</v>
       </c>
-      <c r="N15" s="4">
+      <c r="N15" s="3">
         <v>10338.8523240865</v>
       </c>
+      <c r="P15" s="3">
+        <v>10340.94066099997</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>10341.650143992971</v>
+      </c>
+      <c r="R15" s="3">
+        <v>10344.953450496459</v>
+      </c>
+      <c r="S15" s="3">
+        <v>10344.953450496479</v>
+      </c>
+      <c r="V15" s="3">
+        <v>10340.940661000021</v>
+      </c>
+      <c r="W15" s="3">
+        <v>10339.488788988891</v>
+      </c>
+      <c r="X15" s="3">
+        <v>10308.9042769889</v>
+      </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4">
+      <c r="A16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3">
         <v>288.30227135991117</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
         <v>274.29023135991338</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="3">
         <v>227.0376128161314</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="3">
         <v>218.2520210880229</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="3">
         <v>430.23048014211258</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="3">
         <v>341.73291724526467</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="3">
         <v>208.72499015910671</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L16" s="3">
         <v>250.42085335991359</v>
       </c>
-      <c r="N16" s="4">
+      <c r="N16" s="3">
         <v>208.72499015910671</v>
       </c>
+      <c r="P16" s="3">
+        <v>259.85669432135552</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>255.70237149609181</v>
+      </c>
+      <c r="R16" s="3">
+        <v>215.83602108801921</v>
+      </c>
+      <c r="S16" s="3">
+        <v>271.29140108260452</v>
+      </c>
+      <c r="V16" s="3">
+        <v>289.0632183213545</v>
+      </c>
+      <c r="W16" s="3">
+        <v>272.74804135991099</v>
+      </c>
+      <c r="X16" s="3">
+        <v>244.76081335991179</v>
+      </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4">
-        <v>0</v>
-      </c>
-      <c r="N17" s="4">
+      <c r="A17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4">
+      <c r="A18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3">
         <v>92623.050287719947</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="3">
         <v>92623.050287719874</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="3">
         <v>92479.201967459187</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="3">
         <v>92479.201967458517</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="3">
         <v>92623.05028772002</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="3">
         <v>93090.997181584316</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="3">
         <v>92639.804190406634</v>
       </c>
-      <c r="L18" s="4">
+      <c r="L18" s="3">
         <v>92922.050927719931</v>
       </c>
-      <c r="N18" s="4">
+      <c r="N18" s="3">
         <v>92639.804190406634</v>
       </c>
+      <c r="P18" s="3">
+        <v>92584.832120000006</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>92566.156134917474</v>
+      </c>
+      <c r="R18" s="3">
+        <v>92479.201967458532</v>
+      </c>
+      <c r="S18" s="3">
+        <v>92479.201967459085</v>
+      </c>
+      <c r="V18" s="3">
+        <v>92584.832120000006</v>
+      </c>
+      <c r="W18" s="3">
+        <v>92623.050287719991</v>
+      </c>
+      <c r="X18" s="3">
+        <v>92922.050927719858</v>
+      </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4">
+      <c r="A19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3">
         <v>-30343.488367293889</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="3">
         <v>-30343.48836729394</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="3">
         <v>-30393.76092033066</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="3">
         <v>-30393.760920330689</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="3">
         <v>-30343.488367293881</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="3">
         <v>-30063.153022915041</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="3">
         <v>-30337.633161895152</v>
       </c>
-      <c r="L19" s="4">
+      <c r="L19" s="3">
         <v>-30062.161487294001</v>
       </c>
-      <c r="N19" s="4">
+      <c r="N19" s="3">
         <v>-30337.633161895152</v>
       </c>
+      <c r="P19" s="3">
+        <v>-30356.844969999998</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>-30363.371910661281</v>
+      </c>
+      <c r="R19" s="3">
+        <v>-30393.760920330729</v>
+      </c>
+      <c r="S19" s="3">
+        <v>-30393.760920330689</v>
+      </c>
+      <c r="V19" s="3">
+        <v>-30356.844969999991</v>
+      </c>
+      <c r="W19" s="3">
+        <v>-30343.48836729387</v>
+      </c>
+      <c r="X19" s="3">
+        <v>-30062.161487293939</v>
+      </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4">
+      <c r="A20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3">
         <v>176543.16684470279</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
         <v>176870.61481882271</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="3">
         <v>176986.63785476671</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>177530.22052460819</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="3">
         <v>178049.0356995227</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="3">
         <v>177191.90160428901</v>
       </c>
-      <c r="K20" s="4">
+      <c r="K20" s="3">
         <v>176024.66105619079</v>
       </c>
-      <c r="L20" s="4">
+      <c r="L20" s="3">
         <v>176735.4928387182</v>
       </c>
-      <c r="N20" s="4">
+      <c r="N20" s="3">
         <v>176024.66105619079</v>
       </c>
+      <c r="P20" s="3">
+        <v>177020.770262587</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>176215.00611324221</v>
+      </c>
+      <c r="R20" s="3">
+        <v>176219.09130683821</v>
+      </c>
+      <c r="S20" s="3">
+        <v>176584.14512128281</v>
+      </c>
+      <c r="V20" s="3">
+        <v>177043.9865793151</v>
+      </c>
+      <c r="W20" s="3">
+        <v>176245.70809848339</v>
+      </c>
+      <c r="X20" s="3">
+        <v>176841.2617981596</v>
+      </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="D21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="D21" s="3"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="D22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="D22" s="3"/>
+      <c r="H22" s="3"/>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="6">
-        <v>0</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7">
+      <c r="A23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="5">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="6">
         <f>D6</f>
         <v>0</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="7">
         <f>E6</f>
         <v>491.17766999999998</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="7">
         <f>F6</f>
         <v>809.79908999999998</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="7">
         <f>G6</f>
         <v>1105.9221</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="7">
         <f>H6</f>
         <v>1152.8978</v>
       </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8">
+      <c r="I23" s="7"/>
+      <c r="J23" s="7">
         <f>J6</f>
         <v>0</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="7">
         <f>K6</f>
         <v>185.83815000000001</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="7">
         <f>L6</f>
         <v>4.4829999999999997</v>
       </c>
-      <c r="N23" s="8">
+      <c r="N23" s="7">
         <f>N6</f>
         <v>185.83815010787461</v>
       </c>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7">
+        <f>P6</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="7">
+        <f>Q6</f>
+        <v>210.4018810091365</v>
+      </c>
+      <c r="R23" s="7">
+        <f>R6</f>
+        <v>406.13277811148492</v>
+      </c>
+      <c r="S23" s="7">
+        <f>S6</f>
+        <v>459.23456850371412</v>
+      </c>
+      <c r="T23" s="7">
+        <f>T6</f>
+        <v>0</v>
+      </c>
+      <c r="U23" s="7">
+        <f>U6</f>
+        <v>0</v>
+      </c>
+      <c r="V23" s="7">
+        <f>V6</f>
+        <v>0</v>
+      </c>
+      <c r="W23" s="7">
+        <f>W6</f>
+        <v>203.41004422359791</v>
+      </c>
+      <c r="X23" s="7">
+        <f>X6</f>
+        <v>440.69461639348378</v>
+      </c>
+      <c r="Y23" s="7">
+        <f>Y6</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="9">
+        <v>41</v>
+      </c>
+      <c r="B24" s="8">
         <f>B11/1000</f>
         <v>0</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7">
+      <c r="C24" s="5"/>
+      <c r="D24" s="6">
         <f>D11</f>
         <v>0</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="7">
         <f>E11</f>
         <v>149.2337224143092</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="7">
         <f>F11</f>
         <v>212.57460395924869</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="7">
         <f>G11</f>
         <v>309.17249442743878</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="7">
         <f>H11</f>
         <v>307.37163604812002</v>
       </c>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8">
+      <c r="I24" s="7"/>
+      <c r="J24" s="7">
         <f>J11</f>
         <v>0</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="7">
         <f>K11</f>
         <v>54.851794055020378</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="7">
         <f>L11</f>
         <v>0.5828006912</v>
       </c>
-      <c r="N24" s="8">
+      <c r="N24" s="7">
         <f>N11</f>
         <v>54.851794055020378</v>
       </c>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="A26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26">
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24" s="7">
+        <f>P11</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="7">
+        <f>Q11</f>
+        <v>53.737659732956381</v>
+      </c>
+      <c r="R24" s="7">
+        <f>R11</f>
+        <v>107.5648752189488</v>
+      </c>
+      <c r="S24" s="7">
+        <f>S11</f>
+        <v>128.50129163889599</v>
+      </c>
+      <c r="T24" s="7">
+        <f>T11</f>
+        <v>0</v>
+      </c>
+      <c r="U24" s="7">
+        <f>U11</f>
+        <v>0</v>
+      </c>
+      <c r="V24" s="7">
+        <f>V11</f>
+        <v>0</v>
+      </c>
+      <c r="W24" s="7">
+        <f>W11</f>
+        <v>63.142957502529988</v>
+      </c>
+      <c r="X24" s="7">
+        <f>X11</f>
+        <v>128.79124610002</v>
+      </c>
+      <c r="Y24" s="7">
+        <f>Y11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" s="9" customFormat="1" ht="14.25">
+      <c r="A26" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="9">
         <v>2.1499999999999999</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7">
+      <c r="C26" s="10"/>
+      <c r="D26" s="11">
         <f>D5/1000</f>
         <v>2.822479555469386</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="12">
         <f>E5/1000</f>
         <v>3.1724287971020888</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="12">
         <f>F5/1000</f>
         <v>3.2103162698881822</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="12">
         <f>G5/1000</f>
         <v>3.5705396494738268</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="12">
         <f>H5/1000</f>
         <v>3.5856563050359349</v>
       </c>
-      <c r="J26" s="9">
+      <c r="I26" s="9"/>
+      <c r="J26" s="12">
         <f>J5/1000</f>
         <v>2.7544067292287959</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="12">
         <f>K5/1000</f>
         <v>2.5209419442099361</v>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="12">
         <f>L5/1000</f>
         <v>2.7286918029066021</v>
       </c>
-      <c r="N26" s="9">
+      <c r="M26" s="9"/>
+      <c r="N26" s="12">
         <f>N5/1000</f>
         <v>2.5209419442099361</v>
       </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26" s="12">
+        <f>P5/1000</f>
+        <v>3.0354719047544108</v>
+      </c>
+      <c r="Q26" s="12">
+        <f>Q5/1000</f>
+        <v>2.4734636952706071</v>
+      </c>
+      <c r="R26" s="12">
+        <f>R5/1000</f>
+        <v>2.8109045367664569</v>
+      </c>
+      <c r="S26" s="12">
+        <f>S5/1000</f>
+        <v>2.7637644747940606</v>
+      </c>
+      <c r="T26" s="12">
+        <f>T5/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U26" s="12">
+        <f>U5/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V26" s="12">
+        <f>V5/1000</f>
+        <v>3.0117763737611529</v>
+      </c>
+      <c r="W26" s="12">
+        <f>W5/1000</f>
+        <v>2.4913570058783461</v>
+      </c>
+      <c r="X26" s="12">
+        <f>X5/1000</f>
+        <v>2.9403152619389528</v>
+      </c>
+      <c r="Y26" s="12">
+        <f>Y5/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" ht="14.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B27">
         <v>0.57999999999999996</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7">
+      <c r="C27" s="5"/>
+      <c r="D27" s="6">
         <f>D10/1000</f>
         <v>0.86129550492504603</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="8">
         <f>E10/1000</f>
         <v>0.95955380296238513</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="8">
         <f>F10/1000</f>
         <v>0.86245703766490078</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="8">
         <f>G10/1000</f>
         <v>0.96771333735433673</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="8">
         <f>H10/1000</f>
         <v>0.97480145458214007</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="8">
         <f>J10/1000</f>
         <v>0.77620692015063797</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="8">
         <f>K10/1000</f>
         <v>0.70658427243303035</v>
       </c>
-      <c r="L27" s="9">
+      <c r="L27" s="8">
         <f>L10/1000</f>
         <v>0.80027575755451785</v>
       </c>
-      <c r="N27" s="9">
+      <c r="N27" s="8">
         <f>N10/1000</f>
         <v>0.70658427243303035</v>
       </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27" s="8">
+        <f>P10/1000</f>
+        <v>0.7994126183516499</v>
+      </c>
+      <c r="Q27" s="8">
+        <f>Q10/1000</f>
+        <v>0.67667633230917634</v>
+      </c>
+      <c r="R27" s="8">
+        <f>R10/1000</f>
+        <v>0.75933901395087677</v>
+      </c>
+      <c r="S27" s="8">
+        <f>S10/1000</f>
+        <v>0.76689135089267391</v>
+      </c>
+      <c r="T27" s="8">
+        <f>T10/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U27" s="8">
+        <f>U10/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V27" s="8">
+        <f>V10/1000</f>
+        <v>0.80872542709314399</v>
+      </c>
+      <c r="W27" s="8">
+        <f>W10/1000</f>
+        <v>0.69652451125130788</v>
+      </c>
+      <c r="X27" s="8">
+        <f>X10/1000</f>
+        <v>0.83665331059579795</v>
+      </c>
+      <c r="Y27" s="8">
+        <f>Y10/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" ht="14.25">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B28">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7">
+      <c r="C28" s="5"/>
+      <c r="D28" s="6">
         <f>D7/1000</f>
         <v>9.8422962059999994e-02</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="8">
         <f>E7/1000</f>
         <v>0.16510938333999992</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="8">
         <f>F7/1000</f>
         <v>0.14897144549999991</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="8">
         <f>G7/1000</f>
         <v>0.14897144549999999</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="8">
         <f>H7/1000</f>
         <v>0.1489714455000001</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="8">
         <f>J7/1000</f>
         <v>0.14897144549999999</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="8">
         <f>K7/1000</f>
         <v>0.14897144549999999</v>
       </c>
-      <c r="L28" s="9">
+      <c r="L28" s="8">
         <f>L7/1000</f>
         <v>0.16510938333999892</v>
       </c>
-      <c r="N28" s="9">
+      <c r="N28" s="8">
         <f>N7/1000</f>
         <v>0.14897144549999999</v>
       </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28" s="8">
+        <f>P7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="Q28" s="8">
+        <f>Q7/1000</f>
+        <v>0.16510938334</v>
+      </c>
+      <c r="R28" s="8">
+        <f>R7/1000</f>
+        <v>0.14897144549999972</v>
+      </c>
+      <c r="S28" s="8">
+        <f>S7/1000</f>
+        <v>0.16510938334</v>
+      </c>
+      <c r="T28" s="8">
+        <f>T7/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U28" s="8">
+        <f>U7/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V28" s="8">
+        <f>V7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="W28" s="8">
+        <f>W7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="X28" s="8">
+        <f>X7/1000</f>
+        <v>0.16510938334</v>
+      </c>
+      <c r="Y28" s="8">
+        <f>Y7/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" ht="14.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B29">
         <v>5.0000000000000003e-02</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7">
+      <c r="C29" s="5"/>
+      <c r="D29" s="6">
         <f>D12/1000</f>
         <v>3.5417730949999997e-02</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="8">
         <f>E12/1000</f>
         <v>5.5639340949999998e-02</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="8">
         <f>F12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="8">
         <f>G12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="8">
         <f>H12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="8">
         <f>J12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="8">
         <f>K12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="8">
         <f>L12/1000</f>
         <v>5.5639340949999998e-02</v>
       </c>
-      <c r="N29" s="9">
+      <c r="N29" s="8">
         <f>N12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29" s="8">
+        <f>P12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="Q29" s="8">
+        <f>Q12/1000</f>
+        <v>5.5639340949999998e-02</v>
+      </c>
+      <c r="R29" s="8">
+        <f>R12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="S29" s="8">
+        <f>S12/1000</f>
+        <v>5.5639340949999998e-02</v>
+      </c>
+      <c r="T29" s="8">
+        <f>T12/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U29" s="8">
+        <f>U12/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V29" s="8">
+        <f>V12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="W29" s="8">
+        <f>W12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="X29" s="8">
+        <f>X12/1000</f>
+        <v>5.5639340949999998e-02</v>
+      </c>
+      <c r="Y29" s="8">
+        <f>Y12/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B30">
         <v>23.57</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7">
+      <c r="C30" s="5"/>
+      <c r="D30" s="6">
         <f>D8/1000</f>
         <v>23.5869629</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="8">
         <f>E8/1000</f>
         <v>23.5869629</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="8">
         <f>F8/1000</f>
         <v>24.049619230000001</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="8">
         <f>G8/1000</f>
         <v>24.05455869</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="8">
         <f>H8/1000</f>
         <v>23.774429339999998</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="8">
         <f>J8/1000</f>
         <v>23.72367947</v>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="8">
         <f>K8/1000</f>
         <v>23.819947670000001</v>
       </c>
-      <c r="L30" s="9">
+      <c r="L30" s="8">
         <f>L8/1000</f>
         <v>23.679195970000002</v>
       </c>
-      <c r="N30" s="9">
+      <c r="N30" s="8">
         <f>N8/1000</f>
         <v>23.819947670000001</v>
       </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30" s="8">
+        <f>P8/1000</f>
+        <v>23.831502369999999</v>
+      </c>
+      <c r="Q30" s="8">
+        <f>Q8/1000</f>
+        <v>24.005356089999999</v>
+      </c>
+      <c r="R30" s="8">
+        <f>R8/1000</f>
+        <v>23.831502369999999</v>
+      </c>
+      <c r="S30" s="8">
+        <f>S8/1000</f>
+        <v>24.05087442</v>
+      </c>
+      <c r="T30" s="8">
+        <f>T8/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U30" s="8">
+        <f>U8/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V30" s="8">
+        <f>V8/1000</f>
+        <v>23.819947670000001</v>
+      </c>
+      <c r="W30" s="8">
+        <f>W8/1000</f>
+        <v>23.92632278</v>
+      </c>
+      <c r="X30" s="8">
+        <f>X8/1000</f>
+        <v>23.679195970000002</v>
+      </c>
+      <c r="Y30" s="8">
+        <f>Y8/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B31">
         <v>1.5800000000000001</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7">
+      <c r="C31" s="5"/>
+      <c r="D31" s="6">
         <f>D13/1000</f>
         <v>1.5859146100000001</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="8">
         <f>E13/1000</f>
         <v>1.5859146100000001</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="8">
         <f>F13/1000</f>
         <v>1.63756744</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="8">
         <f>G13/1000</f>
         <v>1.6381151999999999</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="8">
         <f>H13/1000</f>
         <v>1.6068459499999999</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="8">
         <f>J13/1000</f>
         <v>1.6011893399999999</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="8">
         <f>K13/1000</f>
         <v>1.6119264</v>
       </c>
-      <c r="L31" s="9">
+      <c r="L31" s="8">
         <f>L13/1000</f>
         <v>1.5962213999999999</v>
       </c>
-      <c r="N31" s="9">
+      <c r="N31" s="8">
         <f>N13/1000</f>
         <v>1.6119264</v>
       </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31" s="8">
+        <f>P13/1000</f>
+        <v>1.61321472</v>
+      </c>
+      <c r="Q31" s="8">
+        <f>Q13/1000</f>
+        <v>1.6326251999999999</v>
+      </c>
+      <c r="R31" s="8">
+        <f>R13/1000</f>
+        <v>1.61321472</v>
+      </c>
+      <c r="S31" s="8">
+        <f>S13/1000</f>
+        <v>1.63770565</v>
+      </c>
+      <c r="T31" s="8">
+        <f>T13/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U31" s="8">
+        <f>U13/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V31" s="8">
+        <f>V13/1000</f>
+        <v>1.6119264</v>
+      </c>
+      <c r="W31" s="8">
+        <f>W13/1000</f>
+        <v>1.6238004500000001</v>
+      </c>
+      <c r="X31" s="8">
+        <f>X13/1000</f>
+        <v>1.5962213999999999</v>
+      </c>
+      <c r="Y31" s="8">
+        <f>Y13/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" ht="14.25">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B32">
         <v>10.57</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7">
+      <c r="C32" s="5"/>
+      <c r="D32" s="6">
         <f>D15/1000</f>
         <v>10.339488788988891</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="8">
         <f>E15/1000</f>
         <v>10.339488788988891</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="8">
         <f>F15/1000</f>
         <v>10.34495345049641</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="8">
         <f>G15/1000</f>
         <v>10.344953450496451</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="8">
         <f>H15/1000</f>
         <v>10.339488788988911</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="8">
         <f>J15/1000</f>
         <v>10.30901481623552</v>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="8">
         <f>K15/1000</f>
         <v>10.338852324086499</v>
       </c>
-      <c r="L32" s="9">
+      <c r="L32" s="8">
         <f>L15/1000</f>
         <v>10.308904276988899</v>
       </c>
-      <c r="N32" s="9">
+      <c r="N32" s="8">
         <f>N15/1000</f>
         <v>10.338852324086499</v>
       </c>
-    </row>
-    <row r="33" ht="14.25">
-      <c r="A33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33">
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32" s="8">
+        <f>P15/1000</f>
+        <v>10.340940660999969</v>
+      </c>
+      <c r="Q32" s="8">
+        <f>Q15/1000</f>
+        <v>10.34165014399297</v>
+      </c>
+      <c r="R32" s="8">
+        <f>R15/1000</f>
+        <v>10.34495345049646</v>
+      </c>
+      <c r="S32" s="8">
+        <f>S15/1000</f>
+        <v>10.34495345049648</v>
+      </c>
+      <c r="T32" s="8">
+        <f>T15/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U32" s="8">
+        <f>U15/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V32" s="8">
+        <f>V15/1000</f>
+        <v>10.340940661000021</v>
+      </c>
+      <c r="W32" s="8">
+        <f>W15/1000</f>
+        <v>10.339488788988891</v>
+      </c>
+      <c r="X32" s="8">
+        <f>X15/1000</f>
+        <v>10.308904276988899</v>
+      </c>
+      <c r="Y32" s="8">
+        <f>Y15/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" s="9" customFormat="1" ht="14.25">
+      <c r="A33" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="9">
         <v>0.62</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7">
+      <c r="C33" s="10"/>
+      <c r="D33" s="11">
         <f>D9/1000</f>
         <v>0.94061582583106718</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="12">
         <f>E9/1000</f>
         <v>0.75661017611282033</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="12">
         <f>F9/1000</f>
         <v>0.65000889925084604</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="12">
         <f>G9/1000</f>
         <v>0.73001488602091325</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="12">
         <f>H9/1000</f>
         <v>1.143997596824033</v>
       </c>
-      <c r="J33" s="9">
+      <c r="I33" s="9"/>
+      <c r="J33" s="12">
         <f>J9/1000</f>
         <v>0.96025576080048114</v>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="12">
         <f>K9/1000</f>
         <v>0.63830587591942523</v>
       </c>
-      <c r="L33" s="9">
+      <c r="L33" s="12">
         <f>L9/1000</f>
         <v>0.8047070975684566</v>
       </c>
-      <c r="N33" s="9">
+      <c r="M33" s="9"/>
+      <c r="N33" s="12">
         <f>N9/1000</f>
         <v>0.63830587591942523</v>
       </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33" s="12">
+        <f>P9/1000</f>
+        <v>1.0059881419591901</v>
+      </c>
+      <c r="Q33" s="12">
+        <f>Q9/1000</f>
+        <v>0.70079319852844102</v>
+      </c>
+      <c r="R33" s="12">
+        <f>R9/1000</f>
+        <v>0.64087292339114377</v>
+      </c>
+      <c r="S33" s="12">
+        <f>S9/1000</f>
+        <v>0.71412149683434767</v>
+      </c>
+      <c r="T33" s="12">
+        <f>T9/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U33" s="12">
+        <f>U9/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V33" s="12">
+        <f>V9/1000</f>
+        <v>1.0244714055131809</v>
+      </c>
+      <c r="W33" s="12">
+        <f>W9/1000</f>
+        <v>0.72656998135595197</v>
+      </c>
+      <c r="X33" s="12">
+        <f>X9/1000</f>
+        <v>0.67274187858881462</v>
+      </c>
+      <c r="Y33" s="12">
+        <f>Y9/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" ht="14.25">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B34">
         <v>2.9999999999999999e-02</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7">
+      <c r="C34" s="5"/>
+      <c r="D34" s="6">
         <f>D14/1000</f>
         <v>4.621207206710326e-02</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="8">
         <f>E14/1000</f>
         <v>3.6562164955427981e-02</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="8">
         <f>F14/1000</f>
         <v>2.8016753497552501e-02</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="8">
         <f>G14/1000</f>
         <v>2.941212902238563e-02</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="8">
         <f>H14/1000</f>
         <v>5.9589611248039076e-02</v>
       </c>
-      <c r="J34" s="9">
+      <c r="J34" s="8">
         <f>J14/1000</f>
         <v>4.8290297872142028e-02</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="8">
         <f>K14/1000</f>
         <v>2.7056719483739302e-02</v>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="8">
         <f>L14/1000</f>
         <v>3.3794892998491102e-02</v>
       </c>
-      <c r="N34" s="9">
+      <c r="N34" s="8">
         <f>N14/1000</f>
         <v>2.7056719483739302e-02</v>
       </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34" s="8">
+        <f>P14/1000</f>
+        <v>4.2188342550647635e-02</v>
+      </c>
+      <c r="Q34" s="8">
+        <f>Q14/1000</f>
+        <v>3.2164074349346525e-02</v>
+      </c>
+      <c r="R34" s="8">
+        <f>R14/1000</f>
+        <v>2.5807109992933012e-02</v>
+      </c>
+      <c r="S34" s="8">
+        <f>S14/1000</f>
+        <v>3.3074541389620835e-02</v>
+      </c>
+      <c r="T34" s="8">
+        <f>T14/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U34" s="8">
+        <f>U14/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V34" s="8">
+        <f>V14/1000</f>
+        <v>4.4940613976118544e-02</v>
+      </c>
+      <c r="W34" s="8">
+        <f>W14/1000</f>
+        <v>3.4900366947641349e-02</v>
+      </c>
+      <c r="X34" s="8">
+        <f>X14/1000</f>
+        <v>2.918809934592842e-02</v>
+      </c>
+      <c r="Y34" s="8">
+        <f>Y14/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" ht="14.25">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B35">
         <v>0.22</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7">
+      <c r="C35" s="5"/>
+      <c r="D35" s="6">
         <f>D16/1000</f>
         <v>0.28830227135991116</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="8">
         <f>E16/1000</f>
         <v>0.27429023135991337</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="8">
         <f>F16/1000</f>
         <v>0.22703761281613141</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="8">
         <f>G16/1000</f>
         <v>0.21825202108802291</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="8">
         <f>H16/1000</f>
         <v>0.43023048014211257</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="8">
         <f>J16/1000</f>
         <v>0.34173291724526467</v>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="8">
         <f>K16/1000</f>
         <v>0.2087249901591067</v>
       </c>
-      <c r="L35" s="9">
+      <c r="L35" s="8">
         <f>L16/1000</f>
         <v>0.2504208533599136</v>
       </c>
-      <c r="N35" s="9">
+      <c r="N35" s="8">
         <f>N16/1000</f>
         <v>0.2087249901591067</v>
       </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35" s="8">
+        <f>P16/1000</f>
+        <v>0.2598566943213555</v>
+      </c>
+      <c r="Q35" s="8">
+        <f>Q16/1000</f>
+        <v>0.25570237149609182</v>
+      </c>
+      <c r="R35" s="8">
+        <f>R16/1000</f>
+        <v>0.21583602108801922</v>
+      </c>
+      <c r="S35" s="8">
+        <f>S16/1000</f>
+        <v>0.27129140108260452</v>
+      </c>
+      <c r="T35" s="8">
+        <f>T16/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U35" s="8">
+        <f>U16/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V35" s="8">
+        <f>V16/1000</f>
+        <v>0.28906321832135451</v>
+      </c>
+      <c r="W35" s="8">
+        <f>W16/1000</f>
+        <v>0.27274804135991099</v>
+      </c>
+      <c r="X35" s="8">
+        <f>X16/1000</f>
+        <v>0.24476081335991179</v>
+      </c>
+      <c r="Y35" s="8">
+        <f>Y16/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B36">
         <v>4.1799999999999997</v>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="7">
+      <c r="C36" s="5"/>
+      <c r="D36" s="6">
         <f>D4/1000</f>
         <v>4.0609494800000006</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="8">
         <f>E4/1000</f>
         <v>4.0609494799999988</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="8">
         <f>F4/1000</f>
         <v>4.0609494799999784</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="8">
         <f>G4/1000</f>
         <v>4.0609494800000041</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="8">
         <f>H4/1000</f>
         <v>4.0609494800000006</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="8">
         <f>J4/1000</f>
         <v>4.0609494799999863</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="8">
         <f>K4/1000</f>
         <v>4.0609494800000139</v>
       </c>
-      <c r="L36" s="9">
+      <c r="L36" s="8">
         <f>L4/1000</f>
         <v>4.0609494799999961</v>
       </c>
-      <c r="N36" s="9">
+      <c r="N36" s="8">
         <f>N4/1000</f>
         <v>4.0609494800000139</v>
       </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36" s="8">
+        <f>P4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="Q36" s="8">
+        <f>Q4/1000</f>
+        <v>4.0609494800000023</v>
+      </c>
+      <c r="R36" s="8">
+        <f>R4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="S36" s="8">
+        <f>S4/1000</f>
+        <v>4.0609494799999872</v>
+      </c>
+      <c r="T36" s="8">
+        <f>T4/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U36" s="8">
+        <f>U4/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V36" s="8">
+        <f>V4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="W36" s="8">
+        <f>W4/1000</f>
+        <v>4.0609494800000023</v>
+      </c>
+      <c r="X36" s="8">
+        <f>X4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="Y36" s="8">
+        <f>Y4/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="N37" s="9"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="P37" s="8"/>
+      <c r="Q37" s="8"/>
+      <c r="R37" s="8"/>
+      <c r="S37" s="8"/>
+      <c r="T37" s="8"/>
+      <c r="U37" s="8"/>
+      <c r="V37" s="8"/>
+      <c r="W37" s="8"/>
+      <c r="X37" s="8"/>
+      <c r="Y37" s="8"/>
     </row>
     <row r="38" ht="14.25">
       <c r="A38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="8">
+        <v>53</v>
+      </c>
+      <c r="B38" s="7">
         <f>SUM(B26:B36)</f>
         <v>43.689999999999998</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="7">
+      <c r="C38" s="7"/>
+      <c r="D38" s="6">
         <f>SUM(D26:D36)</f>
         <v>44.666061701651401</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="7">
         <f>SUM(E26:E36)</f>
         <v>44.99350967577152</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="7">
         <f>SUM(F26:F36)</f>
         <v>45.266867723264006</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="7">
         <f>SUM(G26:G36)</f>
         <v>45.810450393105931</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="7">
         <f>SUM(H26:H36)</f>
         <v>46.171930556471168</v>
       </c>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8">
+      <c r="I38" s="7"/>
+      <c r="J38" s="7">
         <f>SUM(J26:J36)</f>
         <v>44.771667281182829</v>
       </c>
-      <c r="K38" s="8">
+      <c r="K38" s="7">
         <f>SUM(K26:K36)</f>
         <v>44.129231225941751</v>
       </c>
-      <c r="L38" s="8">
+      <c r="L38" s="7">
         <f>SUM(L26:L36)</f>
         <v>44.483910255666878</v>
       </c>
-      <c r="N38" s="8">
+      <c r="N38" s="7">
         <f>SUM(N26:N36)</f>
         <v>44.129231225941751</v>
       </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38" s="7">
+        <f>SUM(P26:P36)</f>
+        <v>45.185466482587223</v>
+      </c>
+      <c r="Q38" s="7">
+        <f>SUM(Q26:Q36)</f>
+        <v>44.400129310236643</v>
+      </c>
+      <c r="R38" s="7">
+        <f>SUM(R26:R36)</f>
+        <v>44.499321175335879</v>
+      </c>
+      <c r="S38" s="7">
+        <f>SUM(S26:S36)</f>
+        <v>44.864374989779776</v>
+      </c>
+      <c r="T38" s="7">
+        <f>SUM(T26:T36)</f>
+        <v>0</v>
+      </c>
+      <c r="U38" s="7">
+        <f>SUM(U26:U36)</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="7">
+        <f>SUM(V26:V36)</f>
+        <v>45.208682799314971</v>
+      </c>
+      <c r="W38" s="7">
+        <f>SUM(W26:W36)</f>
+        <v>44.368602955432053</v>
+      </c>
+      <c r="X38" s="7">
+        <f>SUM(X26:X36)</f>
+        <v>44.589679215108305</v>
+      </c>
+      <c r="Y38" s="7">
+        <f>SUM(Y26:Y36)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="39" ht="14.25">
       <c r="A39" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="9">
+        <v>54</v>
+      </c>
+      <c r="B39" s="8">
         <v>-30.59</v>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7">
+      <c r="C39" s="5"/>
+      <c r="D39" s="6">
         <f>D19/1000</f>
         <v>-30.34348836729389</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="8">
         <f>E19/1000</f>
         <v>-30.34348836729394</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="8">
         <f>F19/1000</f>
         <v>-30.39376092033066</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="8">
         <f>G19/1000</f>
         <v>-30.393760920330688</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="8">
         <f>H19/1000</f>
         <v>-30.34348836729388</v>
       </c>
-      <c r="J39" s="9">
+      <c r="J39" s="8">
         <f>J19/1000</f>
         <v>-30.063153022915042</v>
       </c>
-      <c r="K39" s="9">
+      <c r="K39" s="8">
         <f>K19/1000</f>
         <v>-30.337633161895152</v>
       </c>
-      <c r="L39" s="9">
+      <c r="L39" s="8">
         <f>L19/1000</f>
         <v>-30.062161487294002</v>
       </c>
-      <c r="N39" s="9">
+      <c r="N39" s="8">
         <f>N19/1000</f>
         <v>-30.337633161895152</v>
       </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39" s="8">
+        <f>P19/1000</f>
+        <v>-30.356844969999997</v>
+      </c>
+      <c r="Q39" s="8">
+        <f>Q19/1000</f>
+        <v>-30.363371910661282</v>
+      </c>
+      <c r="R39" s="8">
+        <f>R19/1000</f>
+        <v>-30.393760920330728</v>
+      </c>
+      <c r="S39" s="8">
+        <f>S19/1000</f>
+        <v>-30.393760920330688</v>
+      </c>
+      <c r="T39" s="8">
+        <f>T19/1000</f>
+        <v>0</v>
+      </c>
+      <c r="U39" s="8">
+        <f>U19/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="8">
+        <f>V19/1000</f>
+        <v>-30.35684496999999</v>
+      </c>
+      <c r="W39" s="8">
+        <f>W19/1000</f>
+        <v>-30.343488367293869</v>
+      </c>
+      <c r="X39" s="8">
+        <f>X19/1000</f>
+        <v>-30.062161487293938</v>
+      </c>
+      <c r="Y39" s="8">
+        <f>Y19/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" ht="14.25">
-      <c r="B40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="N40" s="9"/>
+      <c r="B40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="P40" s="8"/>
+      <c r="Q40" s="8"/>
+      <c r="R40" s="8"/>
+      <c r="S40" s="8"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="8"/>
+      <c r="V40" s="8"/>
+      <c r="W40" s="8"/>
+      <c r="X40" s="8"/>
+      <c r="Y40" s="8"/>
     </row>
     <row r="41" ht="14.25">
       <c r="A41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="9">
+        <v>55</v>
+      </c>
+      <c r="B41" s="8">
         <f>SUM(B38:B39)</f>
         <v>13.099999999999998</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7">
+      <c r="C41" s="5"/>
+      <c r="D41" s="6">
         <f>SUM(D38:D39)</f>
         <v>14.322573334357511</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="8">
         <f>SUM(E38:E39)</f>
         <v>14.65002130847758</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="8">
         <f>SUM(F38:F39)</f>
         <v>14.873106802933346</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="8">
         <f>SUM(G38:G39)</f>
         <v>15.416689472775243</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="8">
         <f>SUM(H38:H39)</f>
         <v>15.828442189177288</v>
       </c>
-      <c r="J41" s="9">
+      <c r="J41" s="8">
         <f>SUM(J38:J39)</f>
         <v>14.708514258267787</v>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="8">
         <f>SUM(K38:K39)</f>
         <v>13.7915980640466</v>
       </c>
-      <c r="L41" s="9">
+      <c r="L41" s="8">
         <f>SUM(L38:L39)</f>
         <v>14.421748768372876</v>
       </c>
-      <c r="N41" s="9">
+      <c r="N41" s="8">
         <f>SUM(N38:N39)</f>
         <v>13.7915980640466</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41" s="8">
+        <f>SUM(P38:P39)</f>
+        <v>14.828621512587226</v>
+      </c>
+      <c r="Q41" s="8">
+        <f>SUM(Q38:Q39)</f>
+        <v>14.036757399575361</v>
+      </c>
+      <c r="R41" s="8">
+        <f>SUM(R38:R39)</f>
+        <v>14.105560255005152</v>
+      </c>
+      <c r="S41" s="8">
+        <f>SUM(S38:S39)</f>
+        <v>14.470614069449088</v>
+      </c>
+      <c r="T41" s="8">
+        <f>SUM(T38:T39)</f>
+        <v>0</v>
+      </c>
+      <c r="U41" s="8">
+        <f>SUM(U38:U39)</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="8">
+        <f>SUM(V38:V39)</f>
+        <v>14.851837829314981</v>
+      </c>
+      <c r="W41" s="8">
+        <f>SUM(W38:W39)</f>
+        <v>14.025114588138184</v>
+      </c>
+      <c r="X41" s="8">
+        <f>SUM(X38:X39)</f>
+        <v>14.527517727814367</v>
+      </c>
+      <c r="Y41" s="8">
+        <f>SUM(Y38:Y39)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/comparison_results_EUS_costs.xlsx
+++ b/analysis/comparison_results_EUS_costs.xlsx
@@ -3,10 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="all" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="noins" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="sCO2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="liq" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sCO2 vs liq" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -16,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>EUS</t>
   </si>
@@ -63,9 +67,6 @@
     <t xml:space="preserve">ins60 45°C</t>
   </si>
   <si>
-    <t xml:space="preserve">ins80 45°C</t>
-  </si>
-  <si>
     <t>ins20%</t>
   </si>
   <si>
@@ -76,6 +77,33 @@
   </si>
   <si>
     <t>ins80%</t>
+  </si>
+  <si>
+    <t>ins100%</t>
+  </si>
+  <si>
+    <t>ins150%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liq noins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liq ins20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liq ins40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liq ins60%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liq ins80%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liq ins100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liq ins150%</t>
   </si>
   <si>
     <t>Concept</t>
@@ -185,6 +213,12 @@
   <si>
     <t xml:space="preserve">Net cost</t>
   </si>
+  <si>
+    <t xml:space="preserve">sCO2 noins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total length km</t>
+  </si>
 </sst>
 </file>
 
@@ -225,12 +259,40 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left style="none"/>
       <right style="none"/>
       <top style="none"/>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -248,11 +310,55 @@
       </bottom>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -260,20 +366,33 @@
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
+    <xf fontId="2" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="1" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -780,13 +899,16 @@
     <col customWidth="1" min="5" max="8" width="9.140625"/>
     <col customWidth="1" min="9" max="9" width="4.140625"/>
     <col customWidth="1" min="10" max="12" width="9.140625"/>
-    <col customWidth="1" min="13" max="13" width="4.7109375"/>
+    <col customWidth="1" min="13" max="13" width="3.8515625"/>
     <col customWidth="1" min="14" max="14" width="9.140625"/>
     <col customWidth="1" min="15" max="15" width="3.7109375"/>
     <col bestFit="1" customWidth="1" min="16" max="16" width="9.79296875"/>
     <col bestFit="1" min="17" max="18" width="12.04296875"/>
-    <col bestFit="1" min="19" max="20" width="9.59375"/>
-    <col customWidth="1" min="22" max="22" width="9.140625"/>
+    <col bestFit="1" min="19" max="19" width="9.59375"/>
+    <col customWidth="1" min="20" max="20" width="4.421875"/>
+    <col customWidth="1" min="21" max="21" width="9.140625"/>
+    <col customWidth="1" min="28" max="28" width="3.421875"/>
+    <col bestFit="1" min="35" max="35" width="10.3125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -836,11 +958,12 @@
       <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="1"/>
+      <c r="U1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>2</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>16</v>
@@ -854,1053 +977,1533 @@
       <c r="Z1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3">
+      <c r="A3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5">
         <v>69597.543222625303</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="5">
         <v>69597.543222625289</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="5">
         <v>69634.329084374185</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="5">
         <v>69634.329084374462</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="5">
         <v>69597.54322262542</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="5">
         <v>69392.390164436889</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="5">
         <v>69593.258801737524</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="5">
         <v>69391.693142625372</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="5">
         <v>69593.258801737524</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="5">
         <v>69607.316629999783</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="5">
         <v>69612.092578749347</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="5">
         <v>69634.329084374505</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="5">
         <v>69634.329084374622</v>
       </c>
-      <c r="V3" s="3">
+      <c r="U3" s="5">
         <v>69607.316630000118</v>
       </c>
-      <c r="W3" s="3">
+      <c r="V3" s="5">
         <v>69597.543222625274</v>
       </c>
-      <c r="X3" s="3">
+      <c r="W3" s="5">
         <v>69391.693142625401</v>
       </c>
+      <c r="X3" s="5">
+        <v>69599.622444599387</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>69532.139366398915</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>69603.132085613208</v>
+      </c>
+      <c r="AA3" s="5">
+        <v>69438.499605969642</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>69593.258801737393</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>69406.223870696296</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>69597.54322262507</v>
+      </c>
+      <c r="AF3" s="5">
+        <v>69634.329084374709</v>
+      </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3">
+      <c r="A4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5">
         <v>4060.9494800000002</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="5">
         <v>4060.9494799999989</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="5">
         <v>4060.9494799999779</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="5">
         <v>4060.9494800000039</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="5">
         <v>4060.9494800000002</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="5">
         <v>4060.9494799999861</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="5">
         <v>4060.9494800000139</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="5">
         <v>4060.9494799999961</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="5">
         <v>4060.9494800000139</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="5">
         <v>4060.9494800000002</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="5">
         <v>4060.949480000002</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="5">
         <v>4060.9494800000002</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="5">
         <v>4060.949479999987</v>
       </c>
-      <c r="V4" s="3">
+      <c r="U4" s="5">
         <v>4060.9494800000002</v>
       </c>
-      <c r="W4" s="3">
+      <c r="V4" s="5">
         <v>4060.949480000002</v>
       </c>
-      <c r="X4" s="3">
+      <c r="W4" s="5">
         <v>4060.9494800000002</v>
       </c>
+      <c r="X4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>4060.9494799999939</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>4060.9494799999889</v>
+      </c>
+      <c r="AA4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="AC4" s="5">
+        <v>4060.9494799999879</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>4060.9494799999952</v>
+      </c>
+      <c r="AE4" s="5">
+        <v>4060.9494799999861</v>
+      </c>
+      <c r="AF4" s="5">
+        <v>4060.9494800000011</v>
+      </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3">
+      <c r="A5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5">
         <v>2822.479555469386</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="5">
         <v>3172.428797102089</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="5">
         <v>3210.316269888182</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="5">
         <v>3570.539649473827</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="5">
         <v>3585.656305035935</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="5">
         <v>2754.4067292287959</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="5">
         <v>2520.9419442099361</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="5">
         <v>2728.6918029066019</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="5">
         <v>2520.9419442099361</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="5">
         <v>3035.4719047544108</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="5">
         <v>2473.4636952706069</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="5">
         <v>2810.9045367664571</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="5">
         <v>2763.7644747940608</v>
       </c>
-      <c r="V5" s="3">
+      <c r="U5" s="5">
         <v>3011.7763737611531</v>
       </c>
-      <c r="W5" s="3">
+      <c r="V5" s="5">
         <v>2491.3570058783462</v>
       </c>
-      <c r="X5" s="3">
+      <c r="W5" s="5">
         <v>2940.315261938953</v>
       </c>
+      <c r="X5" s="5">
+        <v>2699.1899078522679</v>
+      </c>
+      <c r="Y5" s="5">
+        <v>3004.409742667825</v>
+      </c>
+      <c r="Z5" s="5">
+        <v>3033.681652187734</v>
+      </c>
+      <c r="AA5" s="5">
+        <v>2958.4751029840372</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>2542.3794783902758</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>2494.4157891952582</v>
+      </c>
+      <c r="AE5" s="5">
+        <v>2513.7389663880131</v>
+      </c>
+      <c r="AF5" s="5">
+        <v>2435.1492104371969</v>
+      </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="A6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
         <v>491.17766999999998</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="5">
         <v>809.79908999999998</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="5">
         <v>1105.9221</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="5">
         <v>1152.8978</v>
       </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3">
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
         <v>185.83815000000001</v>
       </c>
       <c r="L6">
         <v>4.4829999999999997</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="5">
         <v>185.83815010787461</v>
       </c>
-      <c r="P6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3">
+      <c r="P6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5">
         <v>210.4018810091365</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="5">
         <v>406.13277811148492</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="5">
         <v>459.23456850371412</v>
       </c>
-      <c r="V6" s="3">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3">
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5">
         <v>203.41004422359791</v>
       </c>
-      <c r="X6" s="3">
+      <c r="W6" s="5">
         <v>440.69461639348378</v>
       </c>
+      <c r="X6" s="5">
+        <v>261.30101500166052</v>
+      </c>
+      <c r="Y6" s="5">
+        <v>492.09113817889602</v>
+      </c>
+      <c r="Z6" s="5">
+        <v>234.26697045616001</v>
+      </c>
+      <c r="AA6" s="5">
+        <v>165.67485359931001</v>
+      </c>
+      <c r="AC6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="5">
+        <v>96.841142582021973</v>
+      </c>
+      <c r="AE6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="5">
+        <v>30.554145623040011</v>
+      </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3">
+      <c r="A7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5">
         <v>98.422962059999989</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="5">
         <v>165.10938333999991</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="5">
         <v>148.9714454999999</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="5">
         <v>148.97144549999999</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="5">
         <v>148.9714455000001</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="5">
         <v>148.97144549999999</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="5">
         <v>148.97144549999999</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="5">
         <v>165.10938333999891</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="5">
         <v>148.97144549999999</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="5">
         <v>148.97144549999999</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="5">
         <v>165.10938333999999</v>
       </c>
-      <c r="R7" s="3">
+      <c r="R7" s="5">
         <v>148.9714454999997</v>
       </c>
-      <c r="S7" s="3">
+      <c r="S7" s="5">
         <v>165.10938333999999</v>
       </c>
-      <c r="V7" s="3">
+      <c r="U7" s="5">
         <v>148.97144549999999</v>
       </c>
-      <c r="W7" s="3">
+      <c r="V7" s="5">
         <v>148.97144549999999</v>
       </c>
-      <c r="X7" s="3">
+      <c r="W7" s="5">
         <v>165.10938333999999</v>
       </c>
+      <c r="X7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>148.9714454999984</v>
+      </c>
+      <c r="Z7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="AA7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="AE7" s="5">
+        <v>165.10938333999931</v>
+      </c>
+      <c r="AF7" s="5">
+        <v>148.9714454999999</v>
+      </c>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3">
+      <c r="A8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5">
         <v>23586.962899999999</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="5">
         <v>23586.962899999999</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="5">
         <v>24049.61923</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="5">
         <v>24054.558690000002</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="5">
         <v>23774.429339999999</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="5">
         <v>23723.679469999999</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="5">
         <v>23819.947670000001</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="5">
         <v>23679.195970000001</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="5">
         <v>23819.947670000001</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="5">
         <v>23831.502369999998</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="5">
         <v>24005.356090000001</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="5">
         <v>23831.502369999998</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="5">
         <v>24050.87442</v>
       </c>
-      <c r="V8" s="3">
+      <c r="U8" s="5">
         <v>23819.947670000001</v>
       </c>
-      <c r="W8" s="3">
+      <c r="V8" s="5">
         <v>23926.322779999999</v>
       </c>
-      <c r="X8" s="3">
+      <c r="W8" s="5">
         <v>23679.195970000001</v>
       </c>
+      <c r="X8" s="5">
+        <v>23826.562910000001</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>23631.474620000001</v>
+      </c>
+      <c r="Z8" s="5">
+        <v>23774.429339999999</v>
+      </c>
+      <c r="AA8" s="5">
+        <v>23606.99826</v>
+      </c>
+      <c r="AC8" s="5">
+        <v>23774.429339999999</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>23723.679469999999</v>
+      </c>
+      <c r="AE8" s="5">
+        <v>23586.962899999999</v>
+      </c>
+      <c r="AF8" s="5">
+        <v>23826.562910000001</v>
+      </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3">
+      <c r="A9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5">
         <v>940.61582583106713</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="5">
         <v>756.61017611282034</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="5">
         <v>650.00889925084607</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="5">
         <v>730.0148860209132</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="5">
         <v>1143.9975968240331</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="5">
         <v>960.25576080048108</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="5">
         <v>638.30587591942526</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="5">
         <v>804.70709756845656</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="5">
         <v>638.30587591942526</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="5">
         <v>1005.98814195919</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="5">
         <v>700.79319852844105</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="5">
         <v>640.87292339114379</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="5">
         <v>714.12149683434768</v>
       </c>
-      <c r="V9" s="3">
+      <c r="U9" s="5">
         <v>1024.471405513181</v>
       </c>
-      <c r="W9" s="3">
+      <c r="V9" s="5">
         <v>726.569981355952</v>
       </c>
-      <c r="X9" s="3">
+      <c r="W9" s="5">
         <v>672.74187858881464</v>
       </c>
+      <c r="X9" s="5">
+        <v>678.56208479756037</v>
+      </c>
+      <c r="Y9" s="5">
+        <v>777.59004986035484</v>
+      </c>
+      <c r="Z9" s="5">
+        <v>804.70481487888799</v>
+      </c>
+      <c r="AA9" s="5">
+        <v>1080.042504820924</v>
+      </c>
+      <c r="AC9" s="5">
+        <v>672.75459643071383</v>
+      </c>
+      <c r="AD9" s="5">
+        <v>658.84192959465611</v>
+      </c>
+      <c r="AE9" s="5">
+        <v>737.71733283010838</v>
+      </c>
+      <c r="AF9" s="5">
+        <v>725.20134591293049</v>
+      </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5">
         <v>861.29550492504598</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="5">
         <v>959.55380296238513</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="5">
         <v>862.45703766490078</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="5">
         <v>967.71333735433677</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="5">
         <v>974.80145458214008</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="5">
         <v>776.20692015063798</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="5">
         <v>706.58427243303038</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="5">
         <v>800.2757575545179</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="5">
         <v>706.58427243303038</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="5">
         <v>799.41261835164994</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="5">
         <v>676.67633230917636</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="5">
         <v>759.33901395087673</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="5">
         <v>766.89135089267393</v>
       </c>
-      <c r="V10" s="3">
+      <c r="U10" s="5">
         <v>808.72542709314394</v>
       </c>
-      <c r="W10" s="3">
+      <c r="V10" s="5">
         <v>696.5245112513079</v>
       </c>
-      <c r="X10" s="3">
+      <c r="W10" s="5">
         <v>836.65331059579796</v>
       </c>
+      <c r="X10" s="5">
+        <v>696.20053983729599</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>854.95436631219593</v>
+      </c>
+      <c r="Z10" s="5">
+        <v>841.68429764965992</v>
+      </c>
+      <c r="AA10" s="5">
+        <v>824.41561571600096</v>
+      </c>
+      <c r="AC10" s="5">
+        <v>735.50880075495002</v>
+      </c>
+      <c r="AD10" s="5">
+        <v>723.82196580906998</v>
+      </c>
+      <c r="AE10" s="5">
+        <v>741.58780880969596</v>
+      </c>
+      <c r="AF10" s="5">
+        <v>682.981213044024</v>
+      </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
         <v>149.2337224143092</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="5">
         <v>212.57460395924869</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="5">
         <v>309.17249442743878</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="5">
         <v>307.37163604812002</v>
       </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3">
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
         <v>54.851794055020378</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="5">
         <v>0.5828006912</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="5">
         <v>54.851794055020378</v>
       </c>
-      <c r="P11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3">
+      <c r="P11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5">
         <v>53.737659732956381</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="5">
         <v>107.5648752189488</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11" s="5">
         <v>128.50129163889599</v>
       </c>
-      <c r="V11" s="3">
-        <v>0</v>
-      </c>
-      <c r="W11" s="3">
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
         <v>63.142957502529988</v>
       </c>
-      <c r="X11" s="3">
+      <c r="W11" s="5">
         <v>128.79124610002</v>
       </c>
+      <c r="X11" s="5">
+        <v>39.618204026112011</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>123.06288941384</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>46.122297555099998</v>
+      </c>
+      <c r="AA11" s="5">
+        <v>34.749922530525012</v>
+      </c>
+      <c r="AC11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>39.004466488049992</v>
+      </c>
+      <c r="AE11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="5">
+        <v>12.306343296</v>
+      </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5">
         <v>35.417730949999999</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="5">
         <v>55.639340949999998</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="5">
         <v>46.970104149999997</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="5">
         <v>46.970104149999997</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="5">
         <v>46.970104149999997</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="5">
         <v>46.970104149999997</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="5">
         <v>46.970104149999997</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="5">
         <v>55.639340949999998</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="5">
         <v>46.970104149999997</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="5">
         <v>46.970104149999997</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="5">
         <v>55.639340949999998</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="5">
         <v>46.970104149999997</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="5">
         <v>55.639340949999998</v>
       </c>
-      <c r="V12" s="3">
+      <c r="U12" s="5">
         <v>46.970104149999997</v>
       </c>
-      <c r="W12" s="3">
+      <c r="V12" s="5">
         <v>46.970104149999997</v>
       </c>
-      <c r="X12" s="3">
+      <c r="W12" s="5">
         <v>55.639340949999998</v>
       </c>
+      <c r="X12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="AE12" s="5">
+        <v>55.639340949999998</v>
+      </c>
+      <c r="AF12" s="5">
+        <v>46.970104149999997</v>
+      </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3">
+      <c r="A13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5">
         <v>1585.91461</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="5">
         <v>1585.91461</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="5">
         <v>1637.56744</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="5">
         <v>1638.1152</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="5">
         <v>1606.8459499999999</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="5">
         <v>1601.1893399999999</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="5">
         <v>1611.9264000000001</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="5">
         <v>1596.2213999999999</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="5">
         <v>1611.9264000000001</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P13" s="5">
         <v>1613.2147199999999</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q13" s="5">
         <v>1632.6251999999999</v>
       </c>
-      <c r="R13" s="3">
+      <c r="R13" s="5">
         <v>1613.2147199999999</v>
       </c>
-      <c r="S13" s="3">
+      <c r="S13" s="5">
         <v>1637.7056500000001</v>
       </c>
-      <c r="V13" s="3">
+      <c r="U13" s="5">
         <v>1611.9264000000001</v>
       </c>
-      <c r="W13" s="3">
+      <c r="V13" s="5">
         <v>1623.80045</v>
       </c>
-      <c r="X13" s="3">
+      <c r="W13" s="5">
         <v>1596.2213999999999</v>
       </c>
+      <c r="X13" s="5">
+        <v>1612.66696</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>1590.8734099999999</v>
+      </c>
+      <c r="Z13" s="5">
+        <v>1606.8459499999999</v>
+      </c>
+      <c r="AA13" s="5">
+        <v>1588.16291</v>
+      </c>
+      <c r="AC13" s="5">
+        <v>1606.8459499999999</v>
+      </c>
+      <c r="AD13" s="5">
+        <v>1601.1893399999999</v>
+      </c>
+      <c r="AE13" s="5">
+        <v>1585.91461</v>
+      </c>
+      <c r="AF13" s="5">
+        <v>1612.66696</v>
+      </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3">
+      <c r="A14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5">
         <v>46.212072067103257</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="5">
         <v>36.562164955427981</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="5">
         <v>28.0167534975525</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="5">
         <v>29.412129022385631</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="5">
         <v>59.589611248039077</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="5">
         <v>48.290297872142027</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="5">
         <v>27.0567194837393</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="5">
         <v>33.7948929984911</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="5">
         <v>27.0567194837393</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="5">
         <v>42.188342550647633</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="5">
         <v>32.164074349346528</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="5">
         <v>25.807109992933011</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="5">
         <v>33.074541389620833</v>
       </c>
-      <c r="V14" s="3">
+      <c r="U14" s="5">
         <v>44.940613976118541</v>
       </c>
-      <c r="W14" s="3">
+      <c r="V14" s="5">
         <v>34.900366947641352</v>
       </c>
-      <c r="X14" s="3">
+      <c r="W14" s="5">
         <v>29.188099345928421</v>
       </c>
+      <c r="X14" s="5">
+        <v>29.308103597655158</v>
+      </c>
+      <c r="Y14" s="5">
+        <v>39.810106116292182</v>
+      </c>
+      <c r="Z14" s="5">
+        <v>34.090012150156006</v>
+      </c>
+      <c r="AA14" s="5">
+        <v>61.198907395515157</v>
+      </c>
+      <c r="AC14" s="5">
+        <v>26.625943351861551</v>
+      </c>
+      <c r="AD14" s="5">
+        <v>31.554270135409059</v>
+      </c>
+      <c r="AE14" s="5">
+        <v>36.076930372359037</v>
+      </c>
+      <c r="AF14" s="5">
+        <v>34.48622183996001</v>
+      </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3">
+      <c r="A15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5">
         <v>10339.488788988891</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="5">
         <v>10339.488788988891</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="5">
         <v>10344.95345049641</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="5">
         <v>10344.95345049645</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="5">
         <v>10339.488788988911</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="5">
         <v>10309.01481623552</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="5">
         <v>10338.8523240865</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="5">
         <v>10308.9042769889</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="5">
         <v>10338.8523240865</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="5">
         <v>10340.94066099997</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="5">
         <v>10341.650143992971</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="5">
         <v>10344.953450496459</v>
       </c>
-      <c r="S15" s="3">
+      <c r="S15" s="5">
         <v>10344.953450496479</v>
       </c>
-      <c r="V15" s="3">
+      <c r="U15" s="5">
         <v>10340.940661000021</v>
       </c>
-      <c r="W15" s="3">
+      <c r="V15" s="5">
         <v>10339.488788988891</v>
       </c>
-      <c r="X15" s="3">
+      <c r="W15" s="5">
         <v>10308.9042769889</v>
       </c>
+      <c r="X15" s="5">
+        <v>10339.796881386421</v>
+      </c>
+      <c r="Y15" s="5">
+        <v>10329.770524506201</v>
+      </c>
+      <c r="Z15" s="5">
+        <v>10340.319033082371</v>
+      </c>
+      <c r="AA15" s="5">
+        <v>10315.86367440231</v>
+      </c>
+      <c r="AC15" s="5">
+        <v>10338.852324086471</v>
+      </c>
+      <c r="AD15" s="5">
+        <v>10311.069574492059</v>
+      </c>
+      <c r="AE15" s="5">
+        <v>10339.488788988851</v>
+      </c>
+      <c r="AF15" s="5">
+        <v>10344.95345049649</v>
+      </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3">
+      <c r="A16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5">
         <v>288.30227135991117</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="5">
         <v>274.29023135991338</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="5">
         <v>227.0376128161314</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="5">
         <v>218.2520210880229</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="5">
         <v>430.23048014211258</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="5">
         <v>341.73291724526467</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="5">
         <v>208.72499015910671</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="5">
         <v>250.42085335991359</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="5">
         <v>208.72499015910671</v>
       </c>
-      <c r="P16" s="3">
+      <c r="P16" s="5">
         <v>259.85669432135552</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="Q16" s="5">
         <v>255.70237149609181</v>
       </c>
-      <c r="R16" s="3">
+      <c r="R16" s="5">
         <v>215.83602108801921</v>
       </c>
-      <c r="S16" s="3">
+      <c r="S16" s="5">
         <v>271.29140108260452</v>
       </c>
-      <c r="V16" s="3">
+      <c r="U16" s="5">
         <v>289.0632183213545</v>
       </c>
-      <c r="W16" s="3">
+      <c r="V16" s="5">
         <v>272.74804135991099</v>
       </c>
-      <c r="X16" s="3">
+      <c r="W16" s="5">
         <v>244.76081335991179</v>
       </c>
+      <c r="X16" s="5">
+        <v>228.56775681613709</v>
+      </c>
+      <c r="Y16" s="5">
+        <v>286.36727108258782</v>
+      </c>
+      <c r="Z16" s="5">
+        <v>235.18915591713539</v>
+      </c>
+      <c r="AA16" s="5">
+        <v>429.06939878270413</v>
+      </c>
+      <c r="AC16" s="5">
+        <v>227.4956853704592</v>
+      </c>
+      <c r="AD16" s="5">
+        <v>272.44837499370601</v>
+      </c>
+      <c r="AE16" s="5">
+        <v>282.64223135991409</v>
+      </c>
+      <c r="AF16" s="5">
+        <v>229.51373762586601</v>
+      </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="A17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
+      <c r="R17" s="5">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5">
+        <v>0</v>
+      </c>
+      <c r="W17" s="5">
+        <v>0</v>
+      </c>
+      <c r="X17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3">
+      <c r="A18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5">
         <v>92623.050287719947</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="5">
         <v>92623.050287719874</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="5">
         <v>92479.201967459187</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="5">
         <v>92479.201967458517</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="5">
         <v>92623.05028772002</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="5">
         <v>93090.997181584316</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="5">
         <v>92639.804190406634</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="5">
         <v>92922.050927719931</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="5">
         <v>92639.804190406634</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="5">
         <v>92584.832120000006</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="5">
         <v>92566.156134917474</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="5">
         <v>92479.201967458532</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="5">
         <v>92479.201967459085</v>
       </c>
-      <c r="V18" s="3">
+      <c r="U18" s="5">
         <v>92584.832120000006</v>
       </c>
-      <c r="W18" s="3">
+      <c r="V18" s="5">
         <v>92623.050287719991</v>
       </c>
-      <c r="X18" s="3">
+      <c r="W18" s="5">
         <v>92922.050927719858</v>
       </c>
+      <c r="X18" s="5">
+        <v>92522.56579599141</v>
+      </c>
+      <c r="Y18" s="5">
+        <v>92606.881784256359</v>
+      </c>
+      <c r="Z18" s="5">
+        <v>92601.195463209151</v>
+      </c>
+      <c r="AA18" s="5">
+        <v>92828.863940102048</v>
+      </c>
+      <c r="AC18" s="5">
+        <v>92639.804190406896</v>
+      </c>
+      <c r="AD18" s="5">
+        <v>93080.28297062905</v>
+      </c>
+      <c r="AE18" s="5">
+        <v>92623.050287719743</v>
+      </c>
+      <c r="AF18" s="5">
+        <v>92479.201967458706</v>
+      </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3">
+      <c r="A19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5">
         <v>-30343.488367293889</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="5">
         <v>-30343.48836729394</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="5">
         <v>-30393.76092033066</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="5">
         <v>-30393.760920330689</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="5">
         <v>-30343.488367293881</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="5">
         <v>-30063.153022915041</v>
       </c>
-      <c r="K19" s="3">
+      <c r="K19" s="5">
         <v>-30337.633161895152</v>
       </c>
-      <c r="L19" s="3">
+      <c r="L19" s="5">
         <v>-30062.161487294001</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N19" s="5">
         <v>-30337.633161895152</v>
       </c>
-      <c r="P19" s="3">
+      <c r="P19" s="5">
         <v>-30356.844969999998</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="Q19" s="5">
         <v>-30363.371910661281</v>
       </c>
-      <c r="R19" s="3">
+      <c r="R19" s="5">
         <v>-30393.760920330729</v>
       </c>
-      <c r="S19" s="3">
+      <c r="S19" s="5">
         <v>-30393.760920330689</v>
       </c>
-      <c r="V19" s="3">
+      <c r="U19" s="5">
         <v>-30356.844969999991</v>
       </c>
-      <c r="W19" s="3">
+      <c r="V19" s="5">
         <v>-30343.48836729387</v>
       </c>
-      <c r="X19" s="3">
+      <c r="W19" s="5">
         <v>-30062.161487293939</v>
       </c>
+      <c r="X19" s="5">
+        <v>-30346.329111751569</v>
+      </c>
+      <c r="Y19" s="5">
+        <v>-30254.10340311785</v>
+      </c>
+      <c r="Z19" s="5">
+        <v>-30351.126258527838</v>
+      </c>
+      <c r="AA19" s="5">
+        <v>-30126.16563613954</v>
+      </c>
+      <c r="AC19" s="5">
+        <v>-30337.63316189517</v>
+      </c>
+      <c r="AD19" s="5">
+        <v>-30082.054339034021</v>
+      </c>
+      <c r="AE19" s="5">
+        <v>-30343.48836729406</v>
+      </c>
+      <c r="AF19" s="5">
+        <v>-30393.76092033066</v>
+      </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3">
+      <c r="A20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5">
         <v>176543.16684470279</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="5">
         <v>176870.61481882271</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="5">
         <v>176986.63785476671</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="5">
         <v>177530.22052460819</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="5">
         <v>178049.0356995227</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="5">
         <v>177191.90160428901</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="5">
         <v>176024.66105619079</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="5">
         <v>176735.4928387182</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="5">
         <v>176024.66105619079</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="5">
         <v>177020.770262587</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="5">
         <v>176215.00611324221</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="5">
         <v>176219.09130683821</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="5">
         <v>176584.14512128281</v>
       </c>
-      <c r="V20" s="3">
+      <c r="U20" s="5">
         <v>177043.9865793151</v>
       </c>
-      <c r="W20" s="3">
+      <c r="V20" s="5">
         <v>176245.70809848339</v>
       </c>
-      <c r="X20" s="3">
+      <c r="W20" s="5">
         <v>176841.2617981596</v>
       </c>
+      <c r="X20" s="5">
+        <v>176143.60530277659</v>
+      </c>
+      <c r="Y20" s="5">
+        <v>176657.05886773291</v>
+      </c>
+      <c r="Z20" s="5">
+        <v>176781.03657581049</v>
+      </c>
+      <c r="AA20" s="5">
+        <v>177262.31531368359</v>
+      </c>
+      <c r="AC20" s="5">
+        <v>176077.21297828379</v>
+      </c>
+      <c r="AD20" s="5">
+        <v>176478.36424616151</v>
+      </c>
+      <c r="AE20" s="5">
+        <v>175982.93291608969</v>
+      </c>
+      <c r="AF20" s="5">
+        <v>175868.17621050921</v>
+      </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="D21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="D21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="D22" s="3"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" ht="14.25">
-      <c r="A23" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="5">
-        <v>0</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="6">
+      <c r="D22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" s="6" customFormat="1" ht="14.25">
+      <c r="A23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="6">
+        <v>0</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="7">
         <f>D6</f>
         <v>0</v>
       </c>
@@ -1933,6 +2536,7 @@
         <f>L6</f>
         <v>4.4829999999999997</v>
       </c>
+      <c r="M23" s="6"/>
       <c r="N23" s="7">
         <f>N6</f>
         <v>185.83815010787461</v>
@@ -1954,1124 +2558,1593 @@
         <f>S6</f>
         <v>459.23456850371412</v>
       </c>
-      <c r="T23" s="7">
-        <f>T6</f>
-        <v>0</v>
-      </c>
-      <c r="U23" s="7">
+      <c r="T23" s="7"/>
+      <c r="U23" s="8">
         <f>U6</f>
         <v>0</v>
       </c>
-      <c r="V23" s="7">
+      <c r="V23" s="8">
         <f>V6</f>
-        <v>0</v>
-      </c>
-      <c r="W23" s="7">
+        <v>203.41004422359791</v>
+      </c>
+      <c r="W23" s="8">
         <f>W6</f>
-        <v>203.41004422359791</v>
-      </c>
-      <c r="X23" s="7">
+        <v>440.69461639348378</v>
+      </c>
+      <c r="X23" s="8">
         <f>X6</f>
-        <v>440.69461639348378</v>
-      </c>
-      <c r="Y23" s="7">
+        <v>261.30101500166052</v>
+      </c>
+      <c r="Y23" s="8">
         <f>Y6</f>
+        <v>492.09113817889602</v>
+      </c>
+      <c r="Z23" s="8">
+        <f>Z6</f>
+        <v>234.26697045616001</v>
+      </c>
+      <c r="AA23" s="8">
+        <f>AA6</f>
+        <v>165.67485359931001</v>
+      </c>
+      <c r="AB23" s="8"/>
+      <c r="AC23" s="8">
+        <f>AC6</f>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="8">
+        <f>AD6</f>
+        <v>96.841142582021973</v>
+      </c>
+      <c r="AE23" s="8">
+        <f>AE6</f>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="8">
+        <f>AF6</f>
+        <v>30.554145623040011</v>
+      </c>
+      <c r="AG23" s="8">
+        <f>AG6</f>
+        <v>0</v>
+      </c>
+      <c r="AH23" s="8">
+        <f>AH6</f>
+        <v>0</v>
+      </c>
+      <c r="AI23" s="8">
+        <f>AI6</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="8">
+        <v>49</v>
+      </c>
+      <c r="B24" s="9">
         <f>B11/1000</f>
         <v>0</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="6">
+      <c r="C24" s="10"/>
+      <c r="D24" s="9">
         <f>D11</f>
         <v>0</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="9">
         <f>E11</f>
         <v>149.2337224143092</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="9">
         <f>F11</f>
         <v>212.57460395924869</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="9">
         <f>G11</f>
         <v>309.17249442743878</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="9">
         <f>H11</f>
         <v>307.37163604812002</v>
       </c>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7">
+      <c r="I24" s="9"/>
+      <c r="J24" s="9">
         <f>J11</f>
         <v>0</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K24" s="9">
         <f>K11</f>
         <v>54.851794055020378</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L24" s="9">
         <f>L11</f>
         <v>0.5828006912</v>
       </c>
-      <c r="N24" s="7">
+      <c r="N24" s="9">
         <f>N11</f>
         <v>54.851794055020378</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
-      <c r="P24" s="7">
+      <c r="P24" s="9">
         <f>P11</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="Q24" s="9">
         <f>Q11</f>
         <v>53.737659732956381</v>
       </c>
-      <c r="R24" s="7">
+      <c r="R24" s="9">
         <f>R11</f>
         <v>107.5648752189488</v>
       </c>
-      <c r="S24" s="7">
+      <c r="S24" s="9">
         <f>S11</f>
         <v>128.50129163889599</v>
       </c>
-      <c r="T24" s="7">
-        <f>T11</f>
-        <v>0</v>
-      </c>
-      <c r="U24" s="7">
+      <c r="T24" s="9"/>
+      <c r="U24" s="11">
         <f>U11</f>
         <v>0</v>
       </c>
-      <c r="V24" s="7">
+      <c r="V24" s="11">
         <f>V11</f>
-        <v>0</v>
-      </c>
-      <c r="W24" s="7">
+        <v>63.142957502529988</v>
+      </c>
+      <c r="W24" s="11">
         <f>W11</f>
-        <v>63.142957502529988</v>
-      </c>
-      <c r="X24" s="7">
+        <v>128.79124610002</v>
+      </c>
+      <c r="X24" s="11">
         <f>X11</f>
-        <v>128.79124610002</v>
-      </c>
-      <c r="Y24" s="7">
+        <v>39.618204026112011</v>
+      </c>
+      <c r="Y24" s="11">
         <f>Y11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" s="9" customFormat="1" ht="14.25">
-      <c r="A26" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="9">
+        <v>123.06288941384</v>
+      </c>
+      <c r="Z24" s="11">
+        <f>Z11</f>
+        <v>46.122297555099998</v>
+      </c>
+      <c r="AA24" s="11">
+        <f>AA11</f>
+        <v>34.749922530525012</v>
+      </c>
+      <c r="AB24" s="11"/>
+      <c r="AC24" s="11">
+        <f>AC11</f>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="11">
+        <f>AD11</f>
+        <v>39.004466488049992</v>
+      </c>
+      <c r="AE24" s="11">
+        <f>AE11</f>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="11">
+        <f>AF11</f>
+        <v>12.306343296</v>
+      </c>
+      <c r="AG24" s="11">
+        <f>AG11</f>
+        <v>0</v>
+      </c>
+      <c r="AH24" s="11">
+        <f>AH11</f>
+        <v>0</v>
+      </c>
+      <c r="AI24" s="11">
+        <f>AI11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="U25" s="11"/>
+      <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
+      <c r="Z25" s="11"/>
+      <c r="AA25" s="11"/>
+      <c r="AB25" s="11"/>
+      <c r="AC25" s="11"/>
+      <c r="AD25" s="11"/>
+      <c r="AE25" s="11"/>
+      <c r="AF25" s="11"/>
+      <c r="AG25" s="11"/>
+      <c r="AH25" s="11"/>
+      <c r="AI25" s="11"/>
+    </row>
+    <row r="26" s="6" customFormat="1" ht="14.25">
+      <c r="A26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="6">
         <v>2.1499999999999999</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="11">
+      <c r="C26" s="6"/>
+      <c r="D26" s="7">
         <f>D5/1000</f>
         <v>2.822479555469386</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="7">
         <f>E5/1000</f>
         <v>3.1724287971020888</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="7">
         <f>F5/1000</f>
         <v>3.2103162698881822</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="7">
         <f>G5/1000</f>
         <v>3.5705396494738268</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="7">
         <f>H5/1000</f>
         <v>3.5856563050359349</v>
       </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="12">
+      <c r="I26" s="6"/>
+      <c r="J26" s="7">
         <f>J5/1000</f>
         <v>2.7544067292287959</v>
       </c>
-      <c r="K26" s="12">
+      <c r="K26" s="7">
         <f>K5/1000</f>
         <v>2.5209419442099361</v>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="7">
         <f>L5/1000</f>
         <v>2.7286918029066021</v>
       </c>
-      <c r="M26" s="9"/>
-      <c r="N26" s="12">
+      <c r="M26" s="6"/>
+      <c r="N26" s="7">
         <f>N5/1000</f>
         <v>2.5209419442099361</v>
       </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26" s="12">
+      <c r="O26" s="6">
+        <v>0</v>
+      </c>
+      <c r="P26" s="7">
         <f>P5/1000</f>
         <v>3.0354719047544108</v>
       </c>
-      <c r="Q26" s="12">
+      <c r="Q26" s="7">
         <f>Q5/1000</f>
         <v>2.4734636952706071</v>
       </c>
-      <c r="R26" s="12">
+      <c r="R26" s="7">
         <f>R5/1000</f>
         <v>2.8109045367664569</v>
       </c>
-      <c r="S26" s="12">
+      <c r="S26" s="7">
         <f>S5/1000</f>
         <v>2.7637644747940606</v>
       </c>
-      <c r="T26" s="12">
-        <f>T5/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U26" s="12">
+      <c r="T26" s="7"/>
+      <c r="U26" s="8">
         <f>U5/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V26" s="12">
+        <v>3.0117763737611529</v>
+      </c>
+      <c r="V26" s="8">
         <f>V5/1000</f>
-        <v>3.0117763737611529</v>
-      </c>
-      <c r="W26" s="12">
+        <v>2.4913570058783461</v>
+      </c>
+      <c r="W26" s="8">
         <f>W5/1000</f>
-        <v>2.4913570058783461</v>
-      </c>
-      <c r="X26" s="12">
+        <v>2.9403152619389528</v>
+      </c>
+      <c r="X26" s="8">
         <f>X5/1000</f>
-        <v>2.9403152619389528</v>
-      </c>
-      <c r="Y26" s="12">
+        <v>2.6991899078522681</v>
+      </c>
+      <c r="Y26" s="8">
         <f>Y5/1000</f>
+        <v>3.0044097426678249</v>
+      </c>
+      <c r="Z26" s="8">
+        <f>Z5/1000</f>
+        <v>3.0336816521877341</v>
+      </c>
+      <c r="AA26" s="8">
+        <f>AA5/1000</f>
+        <v>2.9584751029840373</v>
+      </c>
+      <c r="AB26" s="8"/>
+      <c r="AC26" s="8">
+        <f>AC5/1000</f>
+        <v>2.5423794783902758</v>
+      </c>
+      <c r="AD26" s="8">
+        <f>AD5/1000</f>
+        <v>2.4944157891952581</v>
+      </c>
+      <c r="AE26" s="8">
+        <f>AE5/1000</f>
+        <v>2.5137389663880132</v>
+      </c>
+      <c r="AF26" s="8">
+        <f>AF5/1000</f>
+        <v>2.435149210437197</v>
+      </c>
+      <c r="AG26" s="8">
+        <f>AG5/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH26" s="8">
+        <f>AH5/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI26" s="8">
+        <f>AI5/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" ht="14.25">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B27">
         <v>0.57999999999999996</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="6">
+      <c r="C27" s="10"/>
+      <c r="D27" s="9">
         <f>D10/1000</f>
         <v>0.86129550492504603</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="9">
         <f>E10/1000</f>
         <v>0.95955380296238513</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="9">
         <f>F10/1000</f>
         <v>0.86245703766490078</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="9">
         <f>G10/1000</f>
         <v>0.96771333735433673</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="9">
         <f>H10/1000</f>
         <v>0.97480145458214007</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="9">
         <f>J10/1000</f>
         <v>0.77620692015063797</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27" s="9">
         <f>K10/1000</f>
         <v>0.70658427243303035</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="9">
         <f>L10/1000</f>
         <v>0.80027575755451785</v>
       </c>
-      <c r="N27" s="8">
+      <c r="N27" s="9">
         <f>N10/1000</f>
         <v>0.70658427243303035</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
-      <c r="P27" s="8">
+      <c r="P27" s="9">
         <f>P10/1000</f>
         <v>0.7994126183516499</v>
       </c>
-      <c r="Q27" s="8">
+      <c r="Q27" s="9">
         <f>Q10/1000</f>
         <v>0.67667633230917634</v>
       </c>
-      <c r="R27" s="8">
+      <c r="R27" s="9">
         <f>R10/1000</f>
         <v>0.75933901395087677</v>
       </c>
-      <c r="S27" s="8">
+      <c r="S27" s="9">
         <f>S10/1000</f>
         <v>0.76689135089267391</v>
       </c>
-      <c r="T27" s="8">
-        <f>T10/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U27" s="8">
+      <c r="T27" s="9"/>
+      <c r="U27" s="11">
         <f>U10/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V27" s="8">
+        <v>0.80872542709314399</v>
+      </c>
+      <c r="V27" s="11">
         <f>V10/1000</f>
-        <v>0.80872542709314399</v>
-      </c>
-      <c r="W27" s="8">
+        <v>0.69652451125130788</v>
+      </c>
+      <c r="W27" s="11">
         <f>W10/1000</f>
-        <v>0.69652451125130788</v>
-      </c>
-      <c r="X27" s="8">
+        <v>0.83665331059579795</v>
+      </c>
+      <c r="X27" s="11">
         <f>X10/1000</f>
-        <v>0.83665331059579795</v>
-      </c>
-      <c r="Y27" s="8">
+        <v>0.69620053983729602</v>
+      </c>
+      <c r="Y27" s="11">
         <f>Y10/1000</f>
+        <v>0.8549543663121959</v>
+      </c>
+      <c r="Z27" s="11">
+        <f>Z10/1000</f>
+        <v>0.84168429764965991</v>
+      </c>
+      <c r="AA27" s="11">
+        <f>AA10/1000</f>
+        <v>0.82441561571600097</v>
+      </c>
+      <c r="AB27" s="11"/>
+      <c r="AC27" s="11">
+        <f>AC10/1000</f>
+        <v>0.73550880075495007</v>
+      </c>
+      <c r="AD27" s="11">
+        <f>AD10/1000</f>
+        <v>0.72382196580906999</v>
+      </c>
+      <c r="AE27" s="11">
+        <f>AE10/1000</f>
+        <v>0.74158780880969599</v>
+      </c>
+      <c r="AF27" s="11">
+        <f>AF10/1000</f>
+        <v>0.68298121304402404</v>
+      </c>
+      <c r="AG27" s="11">
+        <f>AG10/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH27" s="11">
+        <f>AH10/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI27" s="11">
+        <f>AI10/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="14.25">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B28">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="6">
+      <c r="C28" s="10"/>
+      <c r="D28" s="9">
         <f>D7/1000</f>
         <v>9.8422962059999994e-02</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="9">
         <f>E7/1000</f>
         <v>0.16510938333999992</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="9">
         <f>F7/1000</f>
         <v>0.14897144549999991</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="9">
         <f>G7/1000</f>
         <v>0.14897144549999999</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="9">
         <f>H7/1000</f>
         <v>0.1489714455000001</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="9">
         <f>J7/1000</f>
         <v>0.14897144549999999</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="9">
         <f>K7/1000</f>
         <v>0.14897144549999999</v>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="9">
         <f>L7/1000</f>
         <v>0.16510938333999892</v>
       </c>
-      <c r="N28" s="8">
+      <c r="N28" s="9">
         <f>N7/1000</f>
         <v>0.14897144549999999</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
-      <c r="P28" s="8">
+      <c r="P28" s="9">
         <f>P7/1000</f>
         <v>0.14897144549999999</v>
       </c>
-      <c r="Q28" s="8">
+      <c r="Q28" s="9">
         <f>Q7/1000</f>
         <v>0.16510938334</v>
       </c>
-      <c r="R28" s="8">
+      <c r="R28" s="9">
         <f>R7/1000</f>
         <v>0.14897144549999972</v>
       </c>
-      <c r="S28" s="8">
+      <c r="S28" s="9">
         <f>S7/1000</f>
         <v>0.16510938334</v>
       </c>
-      <c r="T28" s="8">
-        <f>T7/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U28" s="8">
+      <c r="T28" s="9"/>
+      <c r="U28" s="11">
         <f>U7/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V28" s="8">
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="V28" s="11">
         <f>V7/1000</f>
         <v>0.14897144549999999</v>
       </c>
-      <c r="W28" s="8">
+      <c r="W28" s="11">
         <f>W7/1000</f>
+        <v>0.16510938334</v>
+      </c>
+      <c r="X28" s="11">
+        <f>X7/1000</f>
         <v>0.14897144549999999</v>
       </c>
-      <c r="X28" s="8">
-        <f>X7/1000</f>
-        <v>0.16510938334</v>
-      </c>
-      <c r="Y28" s="8">
+      <c r="Y28" s="11">
         <f>Y7/1000</f>
+        <v>0.14897144549999838</v>
+      </c>
+      <c r="Z28" s="11">
+        <f>Z7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="AA28" s="11">
+        <f>AA7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="AB28" s="11"/>
+      <c r="AC28" s="11">
+        <f>AC7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="AD28" s="11">
+        <f>AD7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="AE28" s="11">
+        <f>AE7/1000</f>
+        <v>0.1651093833399993</v>
+      </c>
+      <c r="AF28" s="11">
+        <f>AF7/1000</f>
+        <v>0.14897144549999991</v>
+      </c>
+      <c r="AG28" s="11">
+        <f>AG7/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH28" s="11">
+        <f>AH7/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI28" s="11">
+        <f>AI7/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="14.25">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B29">
         <v>5.0000000000000003e-02</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="6">
+      <c r="C29" s="10"/>
+      <c r="D29" s="9">
         <f>D12/1000</f>
         <v>3.5417730949999997e-02</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="9">
         <f>E12/1000</f>
         <v>5.5639340949999998e-02</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="9">
         <f>F12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="9">
         <f>G12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="9">
         <f>H12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="9">
         <f>J12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="9">
         <f>K12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="9">
         <f>L12/1000</f>
         <v>5.5639340949999998e-02</v>
       </c>
-      <c r="N29" s="8">
+      <c r="N29" s="9">
         <f>N12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
-      <c r="P29" s="8">
+      <c r="P29" s="9">
         <f>P12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="Q29" s="8">
+      <c r="Q29" s="9">
         <f>Q12/1000</f>
         <v>5.5639340949999998e-02</v>
       </c>
-      <c r="R29" s="8">
+      <c r="R29" s="9">
         <f>R12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="S29" s="8">
+      <c r="S29" s="9">
         <f>S12/1000</f>
         <v>5.5639340949999998e-02</v>
       </c>
-      <c r="T29" s="8">
-        <f>T12/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U29" s="8">
+      <c r="T29" s="9"/>
+      <c r="U29" s="11">
         <f>U12/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V29" s="8">
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="V29" s="11">
         <f>V12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="W29" s="8">
+      <c r="W29" s="11">
         <f>W12/1000</f>
+        <v>5.5639340949999998e-02</v>
+      </c>
+      <c r="X29" s="11">
+        <f>X12/1000</f>
         <v>4.6970104149999997e-02</v>
       </c>
-      <c r="X29" s="8">
-        <f>X12/1000</f>
+      <c r="Y29" s="11">
+        <f>Y12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="Z29" s="11">
+        <f>Z12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="AA29" s="11">
+        <f>AA12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="AB29" s="11"/>
+      <c r="AC29" s="11">
+        <f>AC12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="AD29" s="11">
+        <f>AD12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="AE29" s="11">
+        <f>AE12/1000</f>
         <v>5.5639340949999998e-02</v>
       </c>
-      <c r="Y29" s="8">
-        <f>Y12/1000</f>
+      <c r="AF29" s="11">
+        <f>AF12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="AG29" s="11">
+        <f>AG12/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH29" s="11">
+        <f>AH12/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI29" s="11">
+        <f>AI12/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B30">
         <v>23.57</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="6">
+      <c r="C30" s="10"/>
+      <c r="D30" s="9">
         <f>D8/1000</f>
         <v>23.5869629</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="9">
         <f>E8/1000</f>
         <v>23.5869629</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="9">
         <f>F8/1000</f>
         <v>24.049619230000001</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="9">
         <f>G8/1000</f>
         <v>24.05455869</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="9">
         <f>H8/1000</f>
         <v>23.774429339999998</v>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="9">
         <f>J8/1000</f>
         <v>23.72367947</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="9">
         <f>K8/1000</f>
         <v>23.819947670000001</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="9">
         <f>L8/1000</f>
         <v>23.679195970000002</v>
       </c>
-      <c r="N30" s="8">
+      <c r="N30" s="9">
         <f>N8/1000</f>
         <v>23.819947670000001</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
-      <c r="P30" s="8">
+      <c r="P30" s="9">
         <f>P8/1000</f>
         <v>23.831502369999999</v>
       </c>
-      <c r="Q30" s="8">
+      <c r="Q30" s="9">
         <f>Q8/1000</f>
         <v>24.005356089999999</v>
       </c>
-      <c r="R30" s="8">
+      <c r="R30" s="9">
         <f>R8/1000</f>
         <v>23.831502369999999</v>
       </c>
-      <c r="S30" s="8">
+      <c r="S30" s="9">
         <f>S8/1000</f>
         <v>24.05087442</v>
       </c>
-      <c r="T30" s="8">
-        <f>T8/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U30" s="8">
+      <c r="T30" s="9"/>
+      <c r="U30" s="11">
         <f>U8/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V30" s="8">
+        <v>23.819947670000001</v>
+      </c>
+      <c r="V30" s="11">
         <f>V8/1000</f>
-        <v>23.819947670000001</v>
-      </c>
-      <c r="W30" s="8">
+        <v>23.92632278</v>
+      </c>
+      <c r="W30" s="11">
         <f>W8/1000</f>
-        <v>23.92632278</v>
-      </c>
-      <c r="X30" s="8">
+        <v>23.679195970000002</v>
+      </c>
+      <c r="X30" s="11">
         <f>X8/1000</f>
-        <v>23.679195970000002</v>
-      </c>
-      <c r="Y30" s="8">
+        <v>23.82656291</v>
+      </c>
+      <c r="Y30" s="11">
         <f>Y8/1000</f>
+        <v>23.631474620000002</v>
+      </c>
+      <c r="Z30" s="11">
+        <f>Z8/1000</f>
+        <v>23.774429339999998</v>
+      </c>
+      <c r="AA30" s="11">
+        <f>AA8/1000</f>
+        <v>23.606998260000001</v>
+      </c>
+      <c r="AB30" s="11"/>
+      <c r="AC30" s="11">
+        <f>AC8/1000</f>
+        <v>23.774429339999998</v>
+      </c>
+      <c r="AD30" s="11">
+        <f>AD8/1000</f>
+        <v>23.72367947</v>
+      </c>
+      <c r="AE30" s="11">
+        <f>AE8/1000</f>
+        <v>23.5869629</v>
+      </c>
+      <c r="AF30" s="11">
+        <f>AF8/1000</f>
+        <v>23.82656291</v>
+      </c>
+      <c r="AG30" s="11">
+        <f>AG8/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH30" s="11">
+        <f>AH8/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI30" s="11">
+        <f>AI8/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B31">
         <v>1.5800000000000001</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="6">
+      <c r="C31" s="10"/>
+      <c r="D31" s="9">
         <f>D13/1000</f>
         <v>1.5859146100000001</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="9">
         <f>E13/1000</f>
         <v>1.5859146100000001</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="9">
         <f>F13/1000</f>
         <v>1.63756744</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="9">
         <f>G13/1000</f>
         <v>1.6381151999999999</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="9">
         <f>H13/1000</f>
         <v>1.6068459499999999</v>
       </c>
-      <c r="J31" s="8">
+      <c r="J31" s="9">
         <f>J13/1000</f>
         <v>1.6011893399999999</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="9">
         <f>K13/1000</f>
         <v>1.6119264</v>
       </c>
-      <c r="L31" s="8">
+      <c r="L31" s="9">
         <f>L13/1000</f>
         <v>1.5962213999999999</v>
       </c>
-      <c r="N31" s="8">
+      <c r="N31" s="9">
         <f>N13/1000</f>
         <v>1.6119264</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
-      <c r="P31" s="8">
+      <c r="P31" s="9">
         <f>P13/1000</f>
         <v>1.61321472</v>
       </c>
-      <c r="Q31" s="8">
+      <c r="Q31" s="9">
         <f>Q13/1000</f>
         <v>1.6326251999999999</v>
       </c>
-      <c r="R31" s="8">
+      <c r="R31" s="9">
         <f>R13/1000</f>
         <v>1.61321472</v>
       </c>
-      <c r="S31" s="8">
+      <c r="S31" s="9">
         <f>S13/1000</f>
         <v>1.63770565</v>
       </c>
-      <c r="T31" s="8">
-        <f>T13/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U31" s="8">
+      <c r="T31" s="9"/>
+      <c r="U31" s="11">
         <f>U13/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V31" s="8">
+        <v>1.6119264</v>
+      </c>
+      <c r="V31" s="11">
         <f>V13/1000</f>
-        <v>1.6119264</v>
-      </c>
-      <c r="W31" s="8">
+        <v>1.6238004500000001</v>
+      </c>
+      <c r="W31" s="11">
         <f>W13/1000</f>
-        <v>1.6238004500000001</v>
-      </c>
-      <c r="X31" s="8">
+        <v>1.5962213999999999</v>
+      </c>
+      <c r="X31" s="11">
         <f>X13/1000</f>
-        <v>1.5962213999999999</v>
-      </c>
-      <c r="Y31" s="8">
+        <v>1.6126669600000001</v>
+      </c>
+      <c r="Y31" s="11">
         <f>Y13/1000</f>
+        <v>1.5908734099999999</v>
+      </c>
+      <c r="Z31" s="11">
+        <f>Z13/1000</f>
+        <v>1.6068459499999999</v>
+      </c>
+      <c r="AA31" s="11">
+        <f>AA13/1000</f>
+        <v>1.5881629100000001</v>
+      </c>
+      <c r="AB31" s="11"/>
+      <c r="AC31" s="11">
+        <f>AC13/1000</f>
+        <v>1.6068459499999999</v>
+      </c>
+      <c r="AD31" s="11">
+        <f>AD13/1000</f>
+        <v>1.6011893399999999</v>
+      </c>
+      <c r="AE31" s="11">
+        <f>AE13/1000</f>
+        <v>1.5859146100000001</v>
+      </c>
+      <c r="AF31" s="11">
+        <f>AF13/1000</f>
+        <v>1.6126669600000001</v>
+      </c>
+      <c r="AG31" s="11">
+        <f>AG13/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH31" s="11">
+        <f>AH13/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI31" s="11">
+        <f>AI13/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="14.25">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B32">
         <v>10.57</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="6">
+      <c r="C32" s="10"/>
+      <c r="D32" s="9">
         <f>D15/1000</f>
         <v>10.339488788988891</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="9">
         <f>E15/1000</f>
         <v>10.339488788988891</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="9">
         <f>F15/1000</f>
         <v>10.34495345049641</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="9">
         <f>G15/1000</f>
         <v>10.344953450496451</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="9">
         <f>H15/1000</f>
         <v>10.339488788988911</v>
       </c>
-      <c r="J32" s="8">
+      <c r="J32" s="9">
         <f>J15/1000</f>
         <v>10.30901481623552</v>
       </c>
-      <c r="K32" s="8">
+      <c r="K32" s="9">
         <f>K15/1000</f>
         <v>10.338852324086499</v>
       </c>
-      <c r="L32" s="8">
+      <c r="L32" s="9">
         <f>L15/1000</f>
         <v>10.308904276988899</v>
       </c>
-      <c r="N32" s="8">
+      <c r="N32" s="9">
         <f>N15/1000</f>
         <v>10.338852324086499</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
-      <c r="P32" s="8">
+      <c r="P32" s="9">
         <f>P15/1000</f>
         <v>10.340940660999969</v>
       </c>
-      <c r="Q32" s="8">
+      <c r="Q32" s="9">
         <f>Q15/1000</f>
         <v>10.34165014399297</v>
       </c>
-      <c r="R32" s="8">
+      <c r="R32" s="9">
         <f>R15/1000</f>
         <v>10.34495345049646</v>
       </c>
-      <c r="S32" s="8">
+      <c r="S32" s="9">
         <f>S15/1000</f>
         <v>10.34495345049648</v>
       </c>
-      <c r="T32" s="8">
-        <f>T15/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U32" s="8">
+      <c r="T32" s="9"/>
+      <c r="U32" s="11">
         <f>U15/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V32" s="8">
+        <v>10.340940661000021</v>
+      </c>
+      <c r="V32" s="11">
         <f>V15/1000</f>
-        <v>10.340940661000021</v>
-      </c>
-      <c r="W32" s="8">
+        <v>10.339488788988891</v>
+      </c>
+      <c r="W32" s="11">
         <f>W15/1000</f>
-        <v>10.339488788988891</v>
-      </c>
-      <c r="X32" s="8">
+        <v>10.308904276988899</v>
+      </c>
+      <c r="X32" s="11">
         <f>X15/1000</f>
-        <v>10.308904276988899</v>
-      </c>
-      <c r="Y32" s="8">
+        <v>10.339796881386421</v>
+      </c>
+      <c r="Y32" s="11">
         <f>Y15/1000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" s="9" customFormat="1" ht="14.25">
-      <c r="A33" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="9">
+        <v>10.3297705245062</v>
+      </c>
+      <c r="Z32" s="11">
+        <f>Z15/1000</f>
+        <v>10.340319033082372</v>
+      </c>
+      <c r="AA32" s="11">
+        <f>AA15/1000</f>
+        <v>10.31586367440231</v>
+      </c>
+      <c r="AB32" s="11"/>
+      <c r="AC32" s="11">
+        <f>AC15/1000</f>
+        <v>10.338852324086471</v>
+      </c>
+      <c r="AD32" s="11">
+        <f>AD15/1000</f>
+        <v>10.311069574492059</v>
+      </c>
+      <c r="AE32" s="11">
+        <f>AE15/1000</f>
+        <v>10.33948878898885</v>
+      </c>
+      <c r="AF32" s="11">
+        <f>AF15/1000</f>
+        <v>10.34495345049649</v>
+      </c>
+      <c r="AG32" s="11">
+        <f>AG15/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH32" s="11">
+        <f>AH15/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI32" s="11">
+        <f>AI15/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" s="6" customFormat="1" ht="14.25">
+      <c r="A33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="6">
         <v>0.62</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="11">
+      <c r="C33" s="6"/>
+      <c r="D33" s="7">
         <f>D9/1000</f>
         <v>0.94061582583106718</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="7">
         <f>E9/1000</f>
         <v>0.75661017611282033</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="7">
         <f>F9/1000</f>
         <v>0.65000889925084604</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="7">
         <f>G9/1000</f>
         <v>0.73001488602091325</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="7">
         <f>H9/1000</f>
         <v>1.143997596824033</v>
       </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="12">
+      <c r="I33" s="6"/>
+      <c r="J33" s="7">
         <f>J9/1000</f>
         <v>0.96025576080048114</v>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="7">
         <f>K9/1000</f>
         <v>0.63830587591942523</v>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="7">
         <f>L9/1000</f>
         <v>0.8047070975684566</v>
       </c>
-      <c r="M33" s="9"/>
-      <c r="N33" s="12">
+      <c r="M33" s="6"/>
+      <c r="N33" s="7">
         <f>N9/1000</f>
         <v>0.63830587591942523</v>
       </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33" s="12">
+      <c r="O33" s="6">
+        <v>0</v>
+      </c>
+      <c r="P33" s="7">
         <f>P9/1000</f>
         <v>1.0059881419591901</v>
       </c>
-      <c r="Q33" s="12">
+      <c r="Q33" s="7">
         <f>Q9/1000</f>
         <v>0.70079319852844102</v>
       </c>
-      <c r="R33" s="12">
+      <c r="R33" s="7">
         <f>R9/1000</f>
         <v>0.64087292339114377</v>
       </c>
-      <c r="S33" s="12">
+      <c r="S33" s="7">
         <f>S9/1000</f>
         <v>0.71412149683434767</v>
       </c>
-      <c r="T33" s="12">
-        <f>T9/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U33" s="12">
+      <c r="T33" s="7"/>
+      <c r="U33" s="8">
         <f>U9/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V33" s="12">
+        <v>1.0244714055131809</v>
+      </c>
+      <c r="V33" s="8">
         <f>V9/1000</f>
-        <v>1.0244714055131809</v>
-      </c>
-      <c r="W33" s="12">
+        <v>0.72656998135595197</v>
+      </c>
+      <c r="W33" s="8">
         <f>W9/1000</f>
-        <v>0.72656998135595197</v>
-      </c>
-      <c r="X33" s="12">
+        <v>0.67274187858881462</v>
+      </c>
+      <c r="X33" s="8">
         <f>X9/1000</f>
-        <v>0.67274187858881462</v>
-      </c>
-      <c r="Y33" s="12">
+        <v>0.67856208479756042</v>
+      </c>
+      <c r="Y33" s="8">
         <f>Y9/1000</f>
+        <v>0.77759004986035485</v>
+      </c>
+      <c r="Z33" s="8">
+        <f>Z9/1000</f>
+        <v>0.80470481487888801</v>
+      </c>
+      <c r="AA33" s="8">
+        <f>AA9/1000</f>
+        <v>1.0800425048209241</v>
+      </c>
+      <c r="AB33" s="8"/>
+      <c r="AC33" s="8">
+        <f>AC9/1000</f>
+        <v>0.67275459643071378</v>
+      </c>
+      <c r="AD33" s="8">
+        <f>AD9/1000</f>
+        <v>0.65884192959465615</v>
+      </c>
+      <c r="AE33" s="8">
+        <f>AE9/1000</f>
+        <v>0.73771733283010843</v>
+      </c>
+      <c r="AF33" s="8">
+        <f>AF9/1000</f>
+        <v>0.72520134591293051</v>
+      </c>
+      <c r="AG33" s="8">
+        <f>AG9/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH33" s="8">
+        <f>AH9/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI33" s="8">
+        <f>AI9/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" ht="14.25">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B34">
         <v>2.9999999999999999e-02</v>
       </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="6">
+      <c r="C34" s="10"/>
+      <c r="D34" s="9">
         <f>D14/1000</f>
         <v>4.621207206710326e-02</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="9">
         <f>E14/1000</f>
         <v>3.6562164955427981e-02</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="9">
         <f>F14/1000</f>
         <v>2.8016753497552501e-02</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="9">
         <f>G14/1000</f>
         <v>2.941212902238563e-02</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="9">
         <f>H14/1000</f>
         <v>5.9589611248039076e-02</v>
       </c>
-      <c r="J34" s="8">
+      <c r="J34" s="9">
         <f>J14/1000</f>
         <v>4.8290297872142028e-02</v>
       </c>
-      <c r="K34" s="8">
+      <c r="K34" s="9">
         <f>K14/1000</f>
         <v>2.7056719483739302e-02</v>
       </c>
-      <c r="L34" s="8">
+      <c r="L34" s="9">
         <f>L14/1000</f>
         <v>3.3794892998491102e-02</v>
       </c>
-      <c r="N34" s="8">
+      <c r="N34" s="9">
         <f>N14/1000</f>
         <v>2.7056719483739302e-02</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
-      <c r="P34" s="8">
+      <c r="P34" s="9">
         <f>P14/1000</f>
         <v>4.2188342550647635e-02</v>
       </c>
-      <c r="Q34" s="8">
+      <c r="Q34" s="9">
         <f>Q14/1000</f>
         <v>3.2164074349346525e-02</v>
       </c>
-      <c r="R34" s="8">
+      <c r="R34" s="9">
         <f>R14/1000</f>
         <v>2.5807109992933012e-02</v>
       </c>
-      <c r="S34" s="8">
+      <c r="S34" s="9">
         <f>S14/1000</f>
         <v>3.3074541389620835e-02</v>
       </c>
-      <c r="T34" s="8">
-        <f>T14/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U34" s="8">
+      <c r="T34" s="9"/>
+      <c r="U34" s="11">
         <f>U14/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V34" s="8">
+        <v>4.4940613976118544e-02</v>
+      </c>
+      <c r="V34" s="11">
         <f>V14/1000</f>
-        <v>4.4940613976118544e-02</v>
-      </c>
-      <c r="W34" s="8">
+        <v>3.4900366947641349e-02</v>
+      </c>
+      <c r="W34" s="11">
         <f>W14/1000</f>
-        <v>3.4900366947641349e-02</v>
-      </c>
-      <c r="X34" s="8">
+        <v>2.918809934592842e-02</v>
+      </c>
+      <c r="X34" s="11">
         <f>X14/1000</f>
-        <v>2.918809934592842e-02</v>
-      </c>
-      <c r="Y34" s="8">
+        <v>2.9308103597655157e-02</v>
+      </c>
+      <c r="Y34" s="11">
         <f>Y14/1000</f>
+        <v>3.9810106116292182e-02</v>
+      </c>
+      <c r="Z34" s="11">
+        <f>Z14/1000</f>
+        <v>3.4090012150156009e-02</v>
+      </c>
+      <c r="AA34" s="11">
+        <f>AA14/1000</f>
+        <v>6.1198907395515159e-02</v>
+      </c>
+      <c r="AB34" s="11"/>
+      <c r="AC34" s="11">
+        <f>AC14/1000</f>
+        <v>2.6625943351861549e-02</v>
+      </c>
+      <c r="AD34" s="11">
+        <f>AD14/1000</f>
+        <v>3.1554270135409061e-02</v>
+      </c>
+      <c r="AE34" s="11">
+        <f>AE14/1000</f>
+        <v>3.607693037235904e-02</v>
+      </c>
+      <c r="AF34" s="11">
+        <f>AF14/1000</f>
+        <v>3.4486221839960009e-02</v>
+      </c>
+      <c r="AG34" s="11">
+        <f>AG14/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH34" s="11">
+        <f>AH14/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI34" s="11">
+        <f>AI14/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" ht="14.25">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B35">
         <v>0.22</v>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="6">
+      <c r="C35" s="10"/>
+      <c r="D35" s="9">
         <f>D16/1000</f>
         <v>0.28830227135991116</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="9">
         <f>E16/1000</f>
         <v>0.27429023135991337</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="9">
         <f>F16/1000</f>
         <v>0.22703761281613141</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="9">
         <f>G16/1000</f>
         <v>0.21825202108802291</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="9">
         <f>H16/1000</f>
         <v>0.43023048014211257</v>
       </c>
-      <c r="J35" s="8">
+      <c r="J35" s="9">
         <f>J16/1000</f>
         <v>0.34173291724526467</v>
       </c>
-      <c r="K35" s="8">
+      <c r="K35" s="9">
         <f>K16/1000</f>
         <v>0.2087249901591067</v>
       </c>
-      <c r="L35" s="8">
+      <c r="L35" s="9">
         <f>L16/1000</f>
         <v>0.2504208533599136</v>
       </c>
-      <c r="N35" s="8">
+      <c r="N35" s="9">
         <f>N16/1000</f>
         <v>0.2087249901591067</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
-      <c r="P35" s="8">
+      <c r="P35" s="9">
         <f>P16/1000</f>
         <v>0.2598566943213555</v>
       </c>
-      <c r="Q35" s="8">
+      <c r="Q35" s="9">
         <f>Q16/1000</f>
         <v>0.25570237149609182</v>
       </c>
-      <c r="R35" s="8">
+      <c r="R35" s="9">
         <f>R16/1000</f>
         <v>0.21583602108801922</v>
       </c>
-      <c r="S35" s="8">
+      <c r="S35" s="9">
         <f>S16/1000</f>
         <v>0.27129140108260452</v>
       </c>
-      <c r="T35" s="8">
-        <f>T16/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U35" s="8">
+      <c r="T35" s="9"/>
+      <c r="U35" s="11">
         <f>U16/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V35" s="8">
+        <v>0.28906321832135451</v>
+      </c>
+      <c r="V35" s="11">
         <f>V16/1000</f>
-        <v>0.28906321832135451</v>
-      </c>
-      <c r="W35" s="8">
+        <v>0.27274804135991099</v>
+      </c>
+      <c r="W35" s="11">
         <f>W16/1000</f>
-        <v>0.27274804135991099</v>
-      </c>
-      <c r="X35" s="8">
+        <v>0.24476081335991179</v>
+      </c>
+      <c r="X35" s="11">
         <f>X16/1000</f>
-        <v>0.24476081335991179</v>
-      </c>
-      <c r="Y35" s="8">
+        <v>0.22856775681613709</v>
+      </c>
+      <c r="Y35" s="11">
         <f>Y16/1000</f>
+        <v>0.2863672710825878</v>
+      </c>
+      <c r="Z35" s="11">
+        <f>Z16/1000</f>
+        <v>0.23518915591713541</v>
+      </c>
+      <c r="AA35" s="11">
+        <f>AA16/1000</f>
+        <v>0.42906939878270411</v>
+      </c>
+      <c r="AB35" s="11"/>
+      <c r="AC35" s="11">
+        <f>AC16/1000</f>
+        <v>0.22749568537045919</v>
+      </c>
+      <c r="AD35" s="11">
+        <f>AD16/1000</f>
+        <v>0.272448374993706</v>
+      </c>
+      <c r="AE35" s="11">
+        <f>AE16/1000</f>
+        <v>0.28264223135991406</v>
+      </c>
+      <c r="AF35" s="11">
+        <f>AF16/1000</f>
+        <v>0.22951373762586602</v>
+      </c>
+      <c r="AG35" s="11">
+        <f>AG16/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH35" s="11">
+        <f>AH16/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI35" s="11">
+        <f>AI16/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B36">
         <v>4.1799999999999997</v>
       </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="6">
+      <c r="C36" s="10"/>
+      <c r="D36" s="9">
         <f>D4/1000</f>
         <v>4.0609494800000006</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="9">
         <f>E4/1000</f>
         <v>4.0609494799999988</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="9">
         <f>F4/1000</f>
         <v>4.0609494799999784</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="9">
         <f>G4/1000</f>
         <v>4.0609494800000041</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="9">
         <f>H4/1000</f>
         <v>4.0609494800000006</v>
       </c>
-      <c r="J36" s="8">
+      <c r="J36" s="9">
         <f>J4/1000</f>
         <v>4.0609494799999863</v>
       </c>
-      <c r="K36" s="8">
+      <c r="K36" s="9">
         <f>K4/1000</f>
         <v>4.0609494800000139</v>
       </c>
-      <c r="L36" s="8">
+      <c r="L36" s="9">
         <f>L4/1000</f>
         <v>4.0609494799999961</v>
       </c>
-      <c r="N36" s="8">
+      <c r="N36" s="9">
         <f>N4/1000</f>
         <v>4.0609494800000139</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
-      <c r="P36" s="8">
+      <c r="P36" s="9">
         <f>P4/1000</f>
         <v>4.0609494800000006</v>
       </c>
-      <c r="Q36" s="8">
+      <c r="Q36" s="9">
         <f>Q4/1000</f>
         <v>4.0609494800000023</v>
       </c>
-      <c r="R36" s="8">
+      <c r="R36" s="9">
         <f>R4/1000</f>
         <v>4.0609494800000006</v>
       </c>
-      <c r="S36" s="8">
+      <c r="S36" s="9">
         <f>S4/1000</f>
         <v>4.0609494799999872</v>
       </c>
-      <c r="T36" s="8">
-        <f>T4/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U36" s="8">
+      <c r="T36" s="9"/>
+      <c r="U36" s="11">
         <f>U4/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V36" s="8">
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="V36" s="11">
         <f>V4/1000</f>
+        <v>4.0609494800000023</v>
+      </c>
+      <c r="W36" s="11">
+        <f>W4/1000</f>
         <v>4.0609494800000006</v>
       </c>
-      <c r="W36" s="8">
-        <f>W4/1000</f>
-        <v>4.0609494800000023</v>
-      </c>
-      <c r="X36" s="8">
+      <c r="X36" s="11">
         <f>X4/1000</f>
         <v>4.0609494800000006</v>
       </c>
-      <c r="Y36" s="8">
+      <c r="Y36" s="11">
         <f>Y4/1000</f>
+        <v>4.0609494799999935</v>
+      </c>
+      <c r="Z36" s="11">
+        <f>Z4/1000</f>
+        <v>4.060949479999989</v>
+      </c>
+      <c r="AA36" s="11">
+        <f>AA4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="AB36" s="11"/>
+      <c r="AC36" s="11">
+        <f>AC4/1000</f>
+        <v>4.0609494799999881</v>
+      </c>
+      <c r="AD36" s="11">
+        <f>AD4/1000</f>
+        <v>4.0609494799999952</v>
+      </c>
+      <c r="AE36" s="11">
+        <f>AE4/1000</f>
+        <v>4.0609494799999863</v>
+      </c>
+      <c r="AF36" s="11">
+        <f>AF4/1000</f>
+        <v>4.0609494800000014</v>
+      </c>
+      <c r="AG36" s="11">
+        <f>AG4/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH36" s="11">
+        <f>AH4/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI36" s="11">
+        <f>AI4/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="8"/>
-      <c r="S37" s="8"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="8"/>
-      <c r="V37" s="8"/>
-      <c r="W37" s="8"/>
-      <c r="X37" s="8"/>
-      <c r="Y37" s="8"/>
-    </row>
-    <row r="38" ht="14.25">
-      <c r="A38" t="s">
-        <v>53</v>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="9"/>
+      <c r="AA37" s="9"/>
+      <c r="AB37" s="9"/>
+      <c r="AC37" s="9"/>
+      <c r="AD37" s="9"/>
+      <c r="AE37" s="9"/>
+      <c r="AF37" s="9"/>
+      <c r="AG37" s="9"/>
+      <c r="AH37" s="9"/>
+      <c r="AI37" s="9"/>
+    </row>
+    <row r="38" s="6" customFormat="1" ht="14.25">
+      <c r="A38" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B38" s="7">
         <f>SUM(B26:B36)</f>
         <v>43.689999999999998</v>
       </c>
       <c r="C38" s="7"/>
-      <c r="D38" s="6">
+      <c r="D38" s="7">
         <f>SUM(D26:D36)</f>
         <v>44.666061701651401</v>
       </c>
@@ -3104,11 +4177,12 @@
         <f>SUM(L26:L36)</f>
         <v>44.483910255666878</v>
       </c>
+      <c r="M38" s="6"/>
       <c r="N38" s="7">
         <f>SUM(N26:N36)</f>
         <v>44.129231225941751</v>
       </c>
-      <c r="O38">
+      <c r="O38" s="6">
         <v>0</v>
       </c>
       <c r="P38" s="7">
@@ -3127,228 +4201,4579 @@
         <f>SUM(S26:S36)</f>
         <v>44.864374989779776</v>
       </c>
-      <c r="T38" s="7">
-        <f>SUM(T26:T36)</f>
-        <v>0</v>
-      </c>
+      <c r="T38" s="7"/>
       <c r="U38" s="7">
         <f>SUM(U26:U36)</f>
-        <v>0</v>
+        <v>45.208682799314971</v>
       </c>
       <c r="V38" s="7">
         <f>SUM(V26:V36)</f>
-        <v>45.208682799314971</v>
+        <v>44.368602955432053</v>
       </c>
       <c r="W38" s="7">
         <f>SUM(W26:W36)</f>
-        <v>44.368602955432053</v>
+        <v>44.589679215108305</v>
       </c>
       <c r="X38" s="7">
         <f>SUM(X26:X36)</f>
-        <v>44.589679215108305</v>
+        <v>44.367746173937341</v>
       </c>
       <c r="Y38" s="7">
         <f>SUM(Y26:Y36)</f>
+        <v>44.77214112019545</v>
+      </c>
+      <c r="Z38" s="7">
+        <f>SUM(Z26:Z36)</f>
+        <v>44.927835285515933</v>
+      </c>
+      <c r="AA38" s="7">
+        <f>SUM(AA26:AA36)</f>
+        <v>45.121117403751491</v>
+      </c>
+      <c r="AB38" s="7"/>
+      <c r="AC38" s="7">
+        <f>SUM(AC26:AC36)</f>
+        <v>44.181783148034718</v>
+      </c>
+      <c r="AD38" s="7">
+        <f>SUM(AD26:AD36)</f>
+        <v>44.073911743870163</v>
+      </c>
+      <c r="AE38" s="7">
+        <f>SUM(AE26:AE36)</f>
+        <v>44.105827773038925</v>
+      </c>
+      <c r="AF38" s="7">
+        <f>SUM(AF26:AF36)</f>
+        <v>44.148406079006463</v>
+      </c>
+      <c r="AG38" s="7">
+        <f>SUM(AG26:AG36)</f>
+        <v>0</v>
+      </c>
+      <c r="AH38" s="7">
+        <f>SUM(AH26:AH36)</f>
+        <v>0</v>
+      </c>
+      <c r="AI38" s="7">
+        <f>SUM(AI26:AI36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" ht="14.25">
       <c r="A39" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="8">
+        <v>62</v>
+      </c>
+      <c r="B39" s="9">
         <v>-30.59</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="6">
+      <c r="C39" s="10"/>
+      <c r="D39" s="9">
         <f>D19/1000</f>
         <v>-30.34348836729389</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="9">
         <f>E19/1000</f>
         <v>-30.34348836729394</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="9">
         <f>F19/1000</f>
         <v>-30.39376092033066</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="9">
         <f>G19/1000</f>
         <v>-30.393760920330688</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="9">
         <f>H19/1000</f>
         <v>-30.34348836729388</v>
       </c>
-      <c r="J39" s="8">
+      <c r="J39" s="9">
         <f>J19/1000</f>
         <v>-30.063153022915042</v>
       </c>
-      <c r="K39" s="8">
+      <c r="K39" s="9">
         <f>K19/1000</f>
         <v>-30.337633161895152</v>
       </c>
-      <c r="L39" s="8">
+      <c r="L39" s="9">
         <f>L19/1000</f>
         <v>-30.062161487294002</v>
       </c>
-      <c r="N39" s="8">
+      <c r="N39" s="9">
         <f>N19/1000</f>
         <v>-30.337633161895152</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
-      <c r="P39" s="8">
+      <c r="P39" s="9">
         <f>P19/1000</f>
         <v>-30.356844969999997</v>
       </c>
-      <c r="Q39" s="8">
+      <c r="Q39" s="9">
         <f>Q19/1000</f>
         <v>-30.363371910661282</v>
       </c>
-      <c r="R39" s="8">
+      <c r="R39" s="9">
         <f>R19/1000</f>
         <v>-30.393760920330728</v>
       </c>
-      <c r="S39" s="8">
+      <c r="S39" s="9">
         <f>S19/1000</f>
         <v>-30.393760920330688</v>
       </c>
-      <c r="T39" s="8">
-        <f>T19/1000</f>
-        <v>0</v>
-      </c>
-      <c r="U39" s="8">
+      <c r="T39" s="9"/>
+      <c r="U39" s="9">
         <f>U19/1000</f>
-        <v>0</v>
-      </c>
-      <c r="V39" s="8">
+        <v>-30.35684496999999</v>
+      </c>
+      <c r="V39" s="9">
         <f>V19/1000</f>
-        <v>-30.35684496999999</v>
-      </c>
-      <c r="W39" s="8">
+        <v>-30.343488367293869</v>
+      </c>
+      <c r="W39" s="9">
         <f>W19/1000</f>
-        <v>-30.343488367293869</v>
-      </c>
-      <c r="X39" s="8">
+        <v>-30.062161487293938</v>
+      </c>
+      <c r="X39" s="9">
         <f>X19/1000</f>
-        <v>-30.062161487293938</v>
-      </c>
-      <c r="Y39" s="8">
+        <v>-30.346329111751569</v>
+      </c>
+      <c r="Y39" s="9">
         <f>Y19/1000</f>
+        <v>-30.254103403117849</v>
+      </c>
+      <c r="Z39" s="9">
+        <f>Z19/1000</f>
+        <v>-30.351126258527838</v>
+      </c>
+      <c r="AA39" s="9">
+        <f>AA19/1000</f>
+        <v>-30.12616563613954</v>
+      </c>
+      <c r="AB39" s="9"/>
+      <c r="AC39" s="9">
+        <f>AC19/1000</f>
+        <v>-30.33763316189517</v>
+      </c>
+      <c r="AD39" s="9">
+        <f>AD19/1000</f>
+        <v>-30.08205433903402</v>
+      </c>
+      <c r="AE39" s="9">
+        <f>AE19/1000</f>
+        <v>-30.343488367294061</v>
+      </c>
+      <c r="AF39" s="9">
+        <f>AF19/1000</f>
+        <v>-30.39376092033066</v>
+      </c>
+      <c r="AG39" s="9">
+        <f>AG19/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AH39" s="9">
+        <f>AH19/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AI39" s="9">
+        <f>AI19/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" ht="14.25">
-      <c r="B40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="8"/>
-      <c r="N40" s="8"/>
-      <c r="P40" s="8"/>
-      <c r="Q40" s="8"/>
-      <c r="R40" s="8"/>
-      <c r="S40" s="8"/>
-      <c r="T40" s="8"/>
-      <c r="U40" s="8"/>
-      <c r="V40" s="8"/>
-      <c r="W40" s="8"/>
-      <c r="X40" s="8"/>
-      <c r="Y40" s="8"/>
+      <c r="B40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9"/>
+      <c r="Y40" s="9"/>
+      <c r="Z40" s="9"/>
+      <c r="AA40" s="9"/>
+      <c r="AB40" s="9"/>
+      <c r="AC40" s="9"/>
+      <c r="AD40" s="9"/>
+      <c r="AE40" s="9"/>
+      <c r="AF40" s="9"/>
+      <c r="AG40" s="9"/>
+      <c r="AH40" s="9"/>
+      <c r="AI40" s="9"/>
     </row>
     <row r="41" ht="14.25">
       <c r="A41" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" s="8">
+        <v>63</v>
+      </c>
+      <c r="B41" s="9">
         <f>SUM(B38:B39)</f>
         <v>13.099999999999998</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="6">
+      <c r="C41" s="10"/>
+      <c r="D41" s="9">
         <f>SUM(D38:D39)</f>
         <v>14.322573334357511</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="9">
         <f>SUM(E38:E39)</f>
         <v>14.65002130847758</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="9">
         <f>SUM(F38:F39)</f>
         <v>14.873106802933346</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="9">
         <f>SUM(G38:G39)</f>
         <v>15.416689472775243</v>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="9">
         <f>SUM(H38:H39)</f>
         <v>15.828442189177288</v>
       </c>
-      <c r="J41" s="8">
+      <c r="J41" s="9">
         <f>SUM(J38:J39)</f>
         <v>14.708514258267787</v>
       </c>
-      <c r="K41" s="8">
+      <c r="K41" s="9">
         <f>SUM(K38:K39)</f>
         <v>13.7915980640466</v>
       </c>
-      <c r="L41" s="8">
+      <c r="L41" s="9">
         <f>SUM(L38:L39)</f>
         <v>14.421748768372876</v>
       </c>
-      <c r="N41" s="8">
+      <c r="N41" s="9">
         <f>SUM(N38:N39)</f>
         <v>13.7915980640466</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
-      <c r="P41" s="8">
+      <c r="P41" s="9">
         <f>SUM(P38:P39)</f>
         <v>14.828621512587226</v>
       </c>
-      <c r="Q41" s="8">
+      <c r="Q41" s="9">
         <f>SUM(Q38:Q39)</f>
         <v>14.036757399575361</v>
       </c>
-      <c r="R41" s="8">
+      <c r="R41" s="9">
         <f>SUM(R38:R39)</f>
         <v>14.105560255005152</v>
       </c>
-      <c r="S41" s="8">
+      <c r="S41" s="9">
         <f>SUM(S38:S39)</f>
         <v>14.470614069449088</v>
       </c>
-      <c r="T41" s="8">
-        <f>SUM(T38:T39)</f>
-        <v>0</v>
-      </c>
-      <c r="U41" s="8">
+      <c r="T41" s="9"/>
+      <c r="U41" s="9">
         <f>SUM(U38:U39)</f>
-        <v>0</v>
-      </c>
-      <c r="V41" s="8">
+        <v>14.851837829314981</v>
+      </c>
+      <c r="V41" s="9">
         <f>SUM(V38:V39)</f>
+        <v>14.025114588138184</v>
+      </c>
+      <c r="W41" s="9">
+        <f>SUM(W38:W39)</f>
+        <v>14.527517727814367</v>
+      </c>
+      <c r="X41" s="9">
+        <f>SUM(X38:X39)</f>
+        <v>14.021417062185773</v>
+      </c>
+      <c r="Y41" s="9">
+        <f>SUM(Y38:Y39)</f>
+        <v>14.5180377170776</v>
+      </c>
+      <c r="Z41" s="9">
+        <f>SUM(Z38:Z39)</f>
+        <v>14.576709026988095</v>
+      </c>
+      <c r="AA41" s="9">
+        <f>SUM(AA38:AA39)</f>
+        <v>14.994951767611951</v>
+      </c>
+      <c r="AB41" s="9"/>
+      <c r="AC41" s="9">
+        <f>SUM(AC38:AC39)</f>
+        <v>13.844149986139549</v>
+      </c>
+      <c r="AD41" s="9">
+        <f>SUM(AD38:AD39)</f>
+        <v>13.991857404836143</v>
+      </c>
+      <c r="AE41" s="9">
+        <f>SUM(AE38:AE39)</f>
+        <v>13.762339405744864</v>
+      </c>
+      <c r="AF41" s="9">
+        <f>SUM(AF38:AF39)</f>
+        <v>13.754645158675803</v>
+      </c>
+      <c r="AG41" s="9">
+        <f>SUM(AG38:AG39)</f>
+        <v>0</v>
+      </c>
+      <c r="AH41" s="9">
+        <f>SUM(AH38:AH39)</f>
+        <v>0</v>
+      </c>
+      <c r="AI41" s="9">
+        <f>SUM(AI38:AI39)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="U42" s="1" t="str">
+        <f>U1</f>
+        <v>noins</v>
+      </c>
+      <c r="V42" s="1" t="str">
+        <f>V1</f>
+        <v>ins20%</v>
+      </c>
+      <c r="W42" s="1" t="str">
+        <f>W1</f>
+        <v>ins40%</v>
+      </c>
+      <c r="X42" s="1" t="str">
+        <f>X1</f>
+        <v>ins60%</v>
+      </c>
+      <c r="Y42" s="1" t="str">
+        <f>Y1</f>
+        <v>ins80%</v>
+      </c>
+      <c r="Z42" s="1" t="str">
+        <f>Z1</f>
+        <v>ins100%</v>
+      </c>
+      <c r="AA42" s="1" t="str">
+        <f>AA1</f>
+        <v>ins150%</v>
+      </c>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1" t="str">
+        <f>AC1</f>
+        <v xml:space="preserve">liq noins</v>
+      </c>
+      <c r="AD42" s="1" t="str">
+        <f>AD1</f>
+        <v xml:space="preserve">liq ins20%</v>
+      </c>
+      <c r="AE42" s="1" t="str">
+        <f>AE1</f>
+        <v xml:space="preserve">liq ins40%</v>
+      </c>
+      <c r="AF42" s="1" t="str">
+        <f>AF1</f>
+        <v xml:space="preserve">liq ins60%</v>
+      </c>
+      <c r="AG42" s="1" t="str">
+        <f>AG1</f>
+        <v xml:space="preserve">liq ins80%</v>
+      </c>
+      <c r="AH42" s="1" t="str">
+        <f>AH1</f>
+        <v xml:space="preserve">liq ins100%</v>
+      </c>
+      <c r="AI42" s="1" t="str">
+        <f>AI1</f>
+        <v xml:space="preserve">liq ins150%</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="1" max="1" width="37.140625"/>
+    <col bestFit="1" min="2" max="2" width="6.8515625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="10.421875"/>
+    <col customWidth="1" min="4" max="4" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5">
+        <v>69607.316630000118</v>
+      </c>
+      <c r="D3" s="5">
+        <v>69593.258801737393</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4060.9494799999879</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5">
+        <v>3011.7763737611531</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2542.3794783902758</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="D7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5">
+        <v>23819.947670000001</v>
+      </c>
+      <c r="D8" s="5">
+        <v>23774.429339999999</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5">
+        <v>1024.471405513181</v>
+      </c>
+      <c r="D9" s="5">
+        <v>672.75459643071383</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5">
+        <v>808.72542709314394</v>
+      </c>
+      <c r="D10" s="5">
+        <v>735.50880075495002</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="D12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5">
+        <v>1611.9264000000001</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1606.8459499999999</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5">
+        <v>44.940613976118541</v>
+      </c>
+      <c r="D14" s="5">
+        <v>26.625943351861551</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5">
+        <v>10340.940661000021</v>
+      </c>
+      <c r="D15" s="5">
+        <v>10338.852324086471</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5">
+        <v>289.0632183213545</v>
+      </c>
+      <c r="D16" s="5">
+        <v>227.4956853704592</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5">
+        <v>92584.832120000006</v>
+      </c>
+      <c r="D18" s="5">
+        <v>92639.804190406896</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5">
+        <v>-30356.844969999991</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-30337.63316189517</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5">
+        <v>177043.9865793151</v>
+      </c>
+      <c r="D20" s="5">
+        <v>176077.21297828379</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="6">
+        <v>0</v>
+      </c>
+      <c r="C23" s="8">
+        <f>C6</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="8">
+        <f>D6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="9">
+        <f>B11/1000</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="11">
+        <f>C11</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="11">
+        <f>D11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="6">
+        <v>2.1499999999999999</v>
+      </c>
+      <c r="C26" s="8">
+        <f>C5/1000</f>
+        <v>3.0117763737611529</v>
+      </c>
+      <c r="D26" s="8">
+        <f>D5/1000</f>
+        <v>2.5423794783902758</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="C27" s="11">
+        <f>C10/1000</f>
+        <v>0.80872542709314399</v>
+      </c>
+      <c r="D27" s="11">
+        <f>D10/1000</f>
+        <v>0.73550880075495007</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C28" s="11">
+        <f>C7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="D28" s="11">
+        <f>D7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="5">
+        <v>5.0000000000000003e-02</v>
+      </c>
+      <c r="C29" s="11">
+        <f>C12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="D29" s="11">
+        <f>D12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="5">
+        <v>23.57</v>
+      </c>
+      <c r="C30" s="11">
+        <f>C8/1000</f>
+        <v>23.819947670000001</v>
+      </c>
+      <c r="D30" s="11">
+        <f>D8/1000</f>
+        <v>23.774429339999998</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="5">
+        <v>1.5800000000000001</v>
+      </c>
+      <c r="C31" s="11">
+        <f>C13/1000</f>
+        <v>1.6119264</v>
+      </c>
+      <c r="D31" s="11">
+        <f>D13/1000</f>
+        <v>1.6068459499999999</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="5">
+        <v>10.57</v>
+      </c>
+      <c r="C32" s="11">
+        <f>C15/1000</f>
+        <v>10.340940661000021</v>
+      </c>
+      <c r="D32" s="11">
+        <f>D15/1000</f>
+        <v>10.338852324086471</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="6">
+        <v>0.62</v>
+      </c>
+      <c r="C33" s="8">
+        <f>C9/1000</f>
+        <v>1.0244714055131809</v>
+      </c>
+      <c r="D33" s="8">
+        <f>D9/1000</f>
+        <v>0.67275459643071378</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="5">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="C34" s="11">
+        <f>C14/1000</f>
+        <v>4.4940613976118544e-02</v>
+      </c>
+      <c r="D34" s="11">
+        <f>D14/1000</f>
+        <v>2.6625943351861549e-02</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="C35" s="11">
+        <f>C16/1000</f>
+        <v>0.28906321832135451</v>
+      </c>
+      <c r="D35" s="11">
+        <f>D16/1000</f>
+        <v>0.22749568537045919</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="5">
+        <v>4.1799999999999997</v>
+      </c>
+      <c r="C36" s="11">
+        <f>C4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="D36" s="11">
+        <f>D4/1000</f>
+        <v>4.0609494799999881</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="7">
+        <f>SUM(B26:B36)</f>
+        <v>43.689999999999998</v>
+      </c>
+      <c r="C38" s="7">
+        <f>SUM(C26:C36)</f>
+        <v>45.208682799314971</v>
+      </c>
+      <c r="D38" s="7">
+        <f>SUM(D26:D36)</f>
+        <v>44.181783148034718</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="9">
+        <v>-30.59</v>
+      </c>
+      <c r="C39" s="9">
+        <f>C19/1000</f>
+        <v>-30.35684496999999</v>
+      </c>
+      <c r="D39" s="9">
+        <f>D19/1000</f>
+        <v>-30.33763316189517</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="9">
+        <f>SUM(B38:B39)</f>
+        <v>13.099999999999998</v>
+      </c>
+      <c r="C41" s="9">
+        <f>SUM(C38:C39)</f>
         <v>14.851837829314981</v>
       </c>
-      <c r="W41" s="8">
-        <f>SUM(W38:W39)</f>
+      <c r="D41" s="9">
+        <f>SUM(D38:D39)</f>
+        <v>13.844149986139549</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="C42" s="1" t="str">
+        <f>C1</f>
+        <v xml:space="preserve">sCO2 noins</v>
+      </c>
+      <c r="D42" s="1" t="str">
+        <f>D1</f>
+        <v xml:space="preserve">liq noins</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="37.140625"/>
+    <col customWidth="1" min="2" max="2" width="9.140625"/>
+    <col customWidth="1" min="3" max="8" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="5">
+        <v>69607.316630000118</v>
+      </c>
+      <c r="C3" s="5">
+        <v>69597.543222625274</v>
+      </c>
+      <c r="D3" s="5">
+        <v>69391.693142625401</v>
+      </c>
+      <c r="E3" s="5">
+        <v>69599.622444599387</v>
+      </c>
+      <c r="F3" s="5">
+        <v>69532.139366398915</v>
+      </c>
+      <c r="G3" s="5">
+        <v>69603.132085613208</v>
+      </c>
+      <c r="H3" s="5">
+        <v>69438.499605969642</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4060.949480000002</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4060.9494799999939</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4060.9494799999889</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3011.7763737611531</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2491.3570058783462</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2940.315261938953</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2699.1899078522679</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3004.409742667825</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3033.681652187734</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2958.4751029840372</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>203.41004422359791</v>
+      </c>
+      <c r="D6" s="5">
+        <v>440.69461639348378</v>
+      </c>
+      <c r="E6" s="5">
+        <v>261.30101500166052</v>
+      </c>
+      <c r="F6" s="5">
+        <v>492.09113817889602</v>
+      </c>
+      <c r="G6" s="5">
+        <v>234.26697045616001</v>
+      </c>
+      <c r="H6" s="5">
+        <v>165.67485359931001</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="C7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="D7" s="5">
+        <v>165.10938333999999</v>
+      </c>
+      <c r="E7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="F7" s="5">
+        <v>148.9714454999984</v>
+      </c>
+      <c r="G7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="H7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="5">
+        <v>23819.947670000001</v>
+      </c>
+      <c r="C8" s="5">
+        <v>23926.322779999999</v>
+      </c>
+      <c r="D8" s="5">
+        <v>23679.195970000001</v>
+      </c>
+      <c r="E8" s="5">
+        <v>23826.562910000001</v>
+      </c>
+      <c r="F8" s="5">
+        <v>23631.474620000001</v>
+      </c>
+      <c r="G8" s="5">
+        <v>23774.429339999999</v>
+      </c>
+      <c r="H8" s="5">
+        <v>23606.99826</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1024.471405513181</v>
+      </c>
+      <c r="C9" s="5">
+        <v>726.569981355952</v>
+      </c>
+      <c r="D9" s="5">
+        <v>672.74187858881464</v>
+      </c>
+      <c r="E9" s="5">
+        <v>678.56208479756037</v>
+      </c>
+      <c r="F9" s="5">
+        <v>777.59004986035484</v>
+      </c>
+      <c r="G9" s="5">
+        <v>804.70481487888799</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1080.042504820924</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5">
+        <v>808.72542709314394</v>
+      </c>
+      <c r="C10" s="5">
+        <v>696.5245112513079</v>
+      </c>
+      <c r="D10" s="5">
+        <v>836.65331059579796</v>
+      </c>
+      <c r="E10" s="5">
+        <v>696.20053983729599</v>
+      </c>
+      <c r="F10" s="5">
+        <v>854.95436631219593</v>
+      </c>
+      <c r="G10" s="5">
+        <v>841.68429764965992</v>
+      </c>
+      <c r="H10" s="5">
+        <v>824.41561571600096</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>63.142957502529988</v>
+      </c>
+      <c r="D11" s="5">
+        <v>128.79124610002</v>
+      </c>
+      <c r="E11" s="5">
+        <v>39.618204026112011</v>
+      </c>
+      <c r="F11" s="5">
+        <v>123.06288941384</v>
+      </c>
+      <c r="G11" s="5">
+        <v>46.122297555099998</v>
+      </c>
+      <c r="H11" s="5">
+        <v>34.749922530525012</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="C12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="D12" s="5">
+        <v>55.639340949999998</v>
+      </c>
+      <c r="E12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="F12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="G12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="H12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1611.9264000000001</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1623.80045</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1596.2213999999999</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1612.66696</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1590.8734099999999</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1606.8459499999999</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1588.16291</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="5">
+        <v>44.940613976118541</v>
+      </c>
+      <c r="C14" s="5">
+        <v>34.900366947641352</v>
+      </c>
+      <c r="D14" s="5">
+        <v>29.188099345928421</v>
+      </c>
+      <c r="E14" s="5">
+        <v>29.308103597655158</v>
+      </c>
+      <c r="F14" s="5">
+        <v>39.810106116292182</v>
+      </c>
+      <c r="G14" s="5">
+        <v>34.090012150156006</v>
+      </c>
+      <c r="H14" s="5">
+        <v>61.198907395515157</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="5">
+        <v>10340.940661000021</v>
+      </c>
+      <c r="C15" s="5">
+        <v>10339.488788988891</v>
+      </c>
+      <c r="D15" s="5">
+        <v>10308.9042769889</v>
+      </c>
+      <c r="E15" s="5">
+        <v>10339.796881386421</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10329.770524506201</v>
+      </c>
+      <c r="G15" s="5">
+        <v>10340.319033082371</v>
+      </c>
+      <c r="H15" s="5">
+        <v>10315.86367440231</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="5">
+        <v>289.0632183213545</v>
+      </c>
+      <c r="C16" s="5">
+        <v>272.74804135991099</v>
+      </c>
+      <c r="D16" s="5">
+        <v>244.76081335991179</v>
+      </c>
+      <c r="E16" s="5">
+        <v>228.56775681613709</v>
+      </c>
+      <c r="F16" s="5">
+        <v>286.36727108258782</v>
+      </c>
+      <c r="G16" s="5">
+        <v>235.18915591713539</v>
+      </c>
+      <c r="H16" s="5">
+        <v>429.06939878270413</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="5">
+        <v>92584.832120000006</v>
+      </c>
+      <c r="C18" s="5">
+        <v>92623.050287719991</v>
+      </c>
+      <c r="D18" s="5">
+        <v>92922.050927719858</v>
+      </c>
+      <c r="E18" s="5">
+        <v>92522.56579599141</v>
+      </c>
+      <c r="F18" s="5">
+        <v>92606.881784256359</v>
+      </c>
+      <c r="G18" s="5">
+        <v>92601.195463209151</v>
+      </c>
+      <c r="H18" s="5">
+        <v>92828.863940102048</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="5">
+        <v>-30356.844969999991</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-30343.48836729387</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-30062.161487293939</v>
+      </c>
+      <c r="E19" s="5">
+        <v>-30346.329111751569</v>
+      </c>
+      <c r="F19" s="5">
+        <v>-30254.10340311785</v>
+      </c>
+      <c r="G19" s="5">
+        <v>-30351.126258527838</v>
+      </c>
+      <c r="H19" s="5">
+        <v>-30126.16563613954</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="5">
+        <v>177043.9865793151</v>
+      </c>
+      <c r="C20" s="5">
+        <v>176245.70809848339</v>
+      </c>
+      <c r="D20" s="5">
+        <v>176841.2617981596</v>
+      </c>
+      <c r="E20" s="5">
+        <v>176143.60530277659</v>
+      </c>
+      <c r="F20" s="5">
+        <v>176657.05886773291</v>
+      </c>
+      <c r="G20" s="5">
+        <v>176781.03657581049</v>
+      </c>
+      <c r="H20" s="5">
+        <v>177262.31531368359</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="8">
+        <f>B6</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="8">
+        <f>C6</f>
+        <v>203.41004422359791</v>
+      </c>
+      <c r="D23" s="8">
+        <f>D6</f>
+        <v>440.69461639348378</v>
+      </c>
+      <c r="E23" s="8">
+        <f>E6</f>
+        <v>261.30101500166052</v>
+      </c>
+      <c r="F23" s="8">
+        <f>F6</f>
+        <v>492.09113817889602</v>
+      </c>
+      <c r="G23" s="8">
+        <f>G6</f>
+        <v>234.26697045616001</v>
+      </c>
+      <c r="H23" s="8">
+        <f>H6</f>
+        <v>165.67485359931001</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="11">
+        <f>B11</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="11">
+        <f>C11</f>
+        <v>63.142957502529988</v>
+      </c>
+      <c r="D24" s="11">
+        <f>D11</f>
+        <v>128.79124610002</v>
+      </c>
+      <c r="E24" s="11">
+        <f>E11</f>
+        <v>39.618204026112011</v>
+      </c>
+      <c r="F24" s="11">
+        <f>F11</f>
+        <v>123.06288941384</v>
+      </c>
+      <c r="G24" s="11">
+        <f>G11</f>
+        <v>46.122297555099998</v>
+      </c>
+      <c r="H24" s="11">
+        <f>H11</f>
+        <v>34.749922530525012</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="8">
+        <f>B5/1000</f>
+        <v>3.0117763737611529</v>
+      </c>
+      <c r="C26" s="8">
+        <f>C5/1000</f>
+        <v>2.4913570058783461</v>
+      </c>
+      <c r="D26" s="8">
+        <f>D5/1000</f>
+        <v>2.9403152619389528</v>
+      </c>
+      <c r="E26" s="8">
+        <f>E5/1000</f>
+        <v>2.6991899078522681</v>
+      </c>
+      <c r="F26" s="8">
+        <f>F5/1000</f>
+        <v>3.0044097426678249</v>
+      </c>
+      <c r="G26" s="8">
+        <f>G5/1000</f>
+        <v>3.0336816521877341</v>
+      </c>
+      <c r="H26" s="8">
+        <f>H5/1000</f>
+        <v>2.9584751029840373</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="11">
+        <f>B10/1000</f>
+        <v>0.80872542709314399</v>
+      </c>
+      <c r="C27" s="11">
+        <f>C10/1000</f>
+        <v>0.69652451125130788</v>
+      </c>
+      <c r="D27" s="11">
+        <f>D10/1000</f>
+        <v>0.83665331059579795</v>
+      </c>
+      <c r="E27" s="11">
+        <f>E10/1000</f>
+        <v>0.69620053983729602</v>
+      </c>
+      <c r="F27" s="11">
+        <f>F10/1000</f>
+        <v>0.8549543663121959</v>
+      </c>
+      <c r="G27" s="11">
+        <f>G10/1000</f>
+        <v>0.84168429764965991</v>
+      </c>
+      <c r="H27" s="11">
+        <f>H10/1000</f>
+        <v>0.82441561571600097</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="11">
+        <f>B7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="C28" s="11">
+        <f>C7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="D28" s="11">
+        <f>D7/1000</f>
+        <v>0.16510938334</v>
+      </c>
+      <c r="E28" s="11">
+        <f>E7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="F28" s="11">
+        <f>F7/1000</f>
+        <v>0.14897144549999838</v>
+      </c>
+      <c r="G28" s="11">
+        <f>G7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="H28" s="11">
+        <f>H7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="11">
+        <f>B12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="C29" s="11">
+        <f>C12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="D29" s="11">
+        <f>D12/1000</f>
+        <v>5.5639340949999998e-02</v>
+      </c>
+      <c r="E29" s="11">
+        <f>E12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="F29" s="11">
+        <f>F12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="G29" s="11">
+        <f>G12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="H29" s="11">
+        <f>H12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="11">
+        <f>B8/1000</f>
+        <v>23.819947670000001</v>
+      </c>
+      <c r="C30" s="11">
+        <f>C8/1000</f>
+        <v>23.92632278</v>
+      </c>
+      <c r="D30" s="11">
+        <f>D8/1000</f>
+        <v>23.679195970000002</v>
+      </c>
+      <c r="E30" s="11">
+        <f>E8/1000</f>
+        <v>23.82656291</v>
+      </c>
+      <c r="F30" s="11">
+        <f>F8/1000</f>
+        <v>23.631474620000002</v>
+      </c>
+      <c r="G30" s="11">
+        <f>G8/1000</f>
+        <v>23.774429339999998</v>
+      </c>
+      <c r="H30" s="11">
+        <f>H8/1000</f>
+        <v>23.606998260000001</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="11">
+        <f>B13/1000</f>
+        <v>1.6119264</v>
+      </c>
+      <c r="C31" s="11">
+        <f>C13/1000</f>
+        <v>1.6238004500000001</v>
+      </c>
+      <c r="D31" s="11">
+        <f>D13/1000</f>
+        <v>1.5962213999999999</v>
+      </c>
+      <c r="E31" s="11">
+        <f>E13/1000</f>
+        <v>1.6126669600000001</v>
+      </c>
+      <c r="F31" s="11">
+        <f>F13/1000</f>
+        <v>1.5908734099999999</v>
+      </c>
+      <c r="G31" s="11">
+        <f>G13/1000</f>
+        <v>1.6068459499999999</v>
+      </c>
+      <c r="H31" s="11">
+        <f>H13/1000</f>
+        <v>1.5881629100000001</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="11">
+        <f>B15/1000</f>
+        <v>10.340940661000021</v>
+      </c>
+      <c r="C32" s="11">
+        <f>C15/1000</f>
+        <v>10.339488788988891</v>
+      </c>
+      <c r="D32" s="11">
+        <f>D15/1000</f>
+        <v>10.308904276988899</v>
+      </c>
+      <c r="E32" s="11">
+        <f>E15/1000</f>
+        <v>10.339796881386421</v>
+      </c>
+      <c r="F32" s="11">
+        <f>F15/1000</f>
+        <v>10.3297705245062</v>
+      </c>
+      <c r="G32" s="11">
+        <f>G15/1000</f>
+        <v>10.340319033082372</v>
+      </c>
+      <c r="H32" s="11">
+        <f>H15/1000</f>
+        <v>10.31586367440231</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="8">
+        <f>B9/1000</f>
+        <v>1.0244714055131809</v>
+      </c>
+      <c r="C33" s="8">
+        <f>C9/1000</f>
+        <v>0.72656998135595197</v>
+      </c>
+      <c r="D33" s="8">
+        <f>D9/1000</f>
+        <v>0.67274187858881462</v>
+      </c>
+      <c r="E33" s="8">
+        <f>E9/1000</f>
+        <v>0.67856208479756042</v>
+      </c>
+      <c r="F33" s="8">
+        <f>F9/1000</f>
+        <v>0.77759004986035485</v>
+      </c>
+      <c r="G33" s="8">
+        <f>G9/1000</f>
+        <v>0.80470481487888801</v>
+      </c>
+      <c r="H33" s="8">
+        <f>H9/1000</f>
+        <v>1.0800425048209241</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="11">
+        <f>B14/1000</f>
+        <v>4.4940613976118544e-02</v>
+      </c>
+      <c r="C34" s="11">
+        <f>C14/1000</f>
+        <v>3.4900366947641349e-02</v>
+      </c>
+      <c r="D34" s="11">
+        <f>D14/1000</f>
+        <v>2.918809934592842e-02</v>
+      </c>
+      <c r="E34" s="11">
+        <f>E14/1000</f>
+        <v>2.9308103597655157e-02</v>
+      </c>
+      <c r="F34" s="11">
+        <f>F14/1000</f>
+        <v>3.9810106116292182e-02</v>
+      </c>
+      <c r="G34" s="11">
+        <f>G14/1000</f>
+        <v>3.4090012150156009e-02</v>
+      </c>
+      <c r="H34" s="11">
+        <f>H14/1000</f>
+        <v>6.1198907395515159e-02</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="11">
+        <f>B16/1000</f>
+        <v>0.28906321832135451</v>
+      </c>
+      <c r="C35" s="11">
+        <f>C16/1000</f>
+        <v>0.27274804135991099</v>
+      </c>
+      <c r="D35" s="11">
+        <f>D16/1000</f>
+        <v>0.24476081335991179</v>
+      </c>
+      <c r="E35" s="11">
+        <f>E16/1000</f>
+        <v>0.22856775681613709</v>
+      </c>
+      <c r="F35" s="11">
+        <f>F16/1000</f>
+        <v>0.2863672710825878</v>
+      </c>
+      <c r="G35" s="11">
+        <f>G16/1000</f>
+        <v>0.23518915591713541</v>
+      </c>
+      <c r="H35" s="11">
+        <f>H16/1000</f>
+        <v>0.42906939878270411</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="11">
+        <f>B4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="C36" s="11">
+        <f>C4/1000</f>
+        <v>4.0609494800000023</v>
+      </c>
+      <c r="D36" s="11">
+        <f>D4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="E36" s="11">
+        <f>E4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="F36" s="11">
+        <f>F4/1000</f>
+        <v>4.0609494799999935</v>
+      </c>
+      <c r="G36" s="11">
+        <f>G4/1000</f>
+        <v>4.060949479999989</v>
+      </c>
+      <c r="H36" s="11">
+        <f>H4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="7">
+        <f>SUM(B26:B36)</f>
+        <v>45.208682799314971</v>
+      </c>
+      <c r="C38" s="7">
+        <f>SUM(C26:C36)</f>
+        <v>44.368602955432053</v>
+      </c>
+      <c r="D38" s="7">
+        <f>SUM(D26:D36)</f>
+        <v>44.589679215108305</v>
+      </c>
+      <c r="E38" s="7">
+        <f>SUM(E26:E36)</f>
+        <v>44.367746173937341</v>
+      </c>
+      <c r="F38" s="7">
+        <f>SUM(F26:F36)</f>
+        <v>44.77214112019545</v>
+      </c>
+      <c r="G38" s="7">
+        <f>SUM(G26:G36)</f>
+        <v>44.927835285515933</v>
+      </c>
+      <c r="H38" s="7">
+        <f>SUM(H26:H36)</f>
+        <v>45.121117403751491</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="9">
+        <f>B19/1000</f>
+        <v>-30.35684496999999</v>
+      </c>
+      <c r="C39" s="9">
+        <f>C19/1000</f>
+        <v>-30.343488367293869</v>
+      </c>
+      <c r="D39" s="9">
+        <f>D19/1000</f>
+        <v>-30.062161487293938</v>
+      </c>
+      <c r="E39" s="9">
+        <f>E19/1000</f>
+        <v>-30.346329111751569</v>
+      </c>
+      <c r="F39" s="9">
+        <f>F19/1000</f>
+        <v>-30.254103403117849</v>
+      </c>
+      <c r="G39" s="9">
+        <f>G19/1000</f>
+        <v>-30.351126258527838</v>
+      </c>
+      <c r="H39" s="9">
+        <f>H19/1000</f>
+        <v>-30.12616563613954</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="9">
+        <f>SUM(B38:B39)</f>
+        <v>14.851837829314981</v>
+      </c>
+      <c r="C41" s="9">
+        <f>SUM(C38:C39)</f>
         <v>14.025114588138184</v>
       </c>
-      <c r="X41" s="8">
-        <f>SUM(X38:X39)</f>
+      <c r="D41" s="9">
+        <f>SUM(D38:D39)</f>
         <v>14.527517727814367</v>
       </c>
-      <c r="Y41" s="8">
-        <f>SUM(Y38:Y39)</f>
-        <v>0</v>
+      <c r="E41" s="9">
+        <f>SUM(E38:E39)</f>
+        <v>14.021417062185773</v>
+      </c>
+      <c r="F41" s="9">
+        <f>SUM(F38:F39)</f>
+        <v>14.5180377170776</v>
+      </c>
+      <c r="G41" s="9">
+        <f>SUM(G38:G39)</f>
+        <v>14.576709026988095</v>
+      </c>
+      <c r="H41" s="9">
+        <f>SUM(H38:H39)</f>
+        <v>14.994951767611951</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="B42" s="1" t="str">
+        <f>B1</f>
+        <v>noins</v>
+      </c>
+      <c r="C42" s="1" t="str">
+        <f>C1</f>
+        <v>ins20%</v>
+      </c>
+      <c r="D42" s="1" t="str">
+        <f>D1</f>
+        <v>ins40%</v>
+      </c>
+      <c r="E42" s="1" t="str">
+        <f>E1</f>
+        <v>ins60%</v>
+      </c>
+      <c r="F42" s="1" t="str">
+        <f>F1</f>
+        <v>ins80%</v>
+      </c>
+      <c r="G42" s="1" t="str">
+        <f>G1</f>
+        <v>ins100%</v>
+      </c>
+      <c r="H42" s="1" t="str">
+        <f>H1</f>
+        <v>ins150%</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="37.140625"/>
+    <col customWidth="1" min="2" max="5" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="5">
+        <v>69593.258801737393</v>
+      </c>
+      <c r="C3" s="5">
+        <v>69406.223870696296</v>
+      </c>
+      <c r="D3" s="5">
+        <v>69597.54322262507</v>
+      </c>
+      <c r="E3" s="5">
+        <v>69634.329084374709</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4060.9494799999879</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4060.9494799999952</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4060.9494799999861</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4060.9494800000011</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2542.3794783902758</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2494.4157891952582</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2513.7389663880131</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2435.1492104371969</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>96.841142582021973</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>30.554145623040011</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="C7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="D7" s="5">
+        <v>165.10938333999931</v>
+      </c>
+      <c r="E7" s="5">
+        <v>148.9714454999999</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="5">
+        <v>23774.429339999999</v>
+      </c>
+      <c r="C8" s="5">
+        <v>23723.679469999999</v>
+      </c>
+      <c r="D8" s="5">
+        <v>23586.962899999999</v>
+      </c>
+      <c r="E8" s="5">
+        <v>23826.562910000001</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="5">
+        <v>672.75459643071383</v>
+      </c>
+      <c r="C9" s="5">
+        <v>658.84192959465611</v>
+      </c>
+      <c r="D9" s="5">
+        <v>737.71733283010838</v>
+      </c>
+      <c r="E9" s="5">
+        <v>725.20134591293049</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5">
+        <v>735.50880075495002</v>
+      </c>
+      <c r="C10" s="5">
+        <v>723.82196580906998</v>
+      </c>
+      <c r="D10" s="5">
+        <v>741.58780880969596</v>
+      </c>
+      <c r="E10" s="5">
+        <v>682.981213044024</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>39.004466488049992</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>12.306343296</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="C12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="D12" s="5">
+        <v>55.639340949999998</v>
+      </c>
+      <c r="E12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1606.8459499999999</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1601.1893399999999</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1585.91461</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1612.66696</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="5">
+        <v>26.625943351861551</v>
+      </c>
+      <c r="C14" s="5">
+        <v>31.554270135409059</v>
+      </c>
+      <c r="D14" s="5">
+        <v>36.076930372359037</v>
+      </c>
+      <c r="E14" s="5">
+        <v>34.48622183996001</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="5">
+        <v>10338.852324086471</v>
+      </c>
+      <c r="C15" s="5">
+        <v>10311.069574492059</v>
+      </c>
+      <c r="D15" s="5">
+        <v>10339.488788988851</v>
+      </c>
+      <c r="E15" s="5">
+        <v>10344.95345049649</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="5">
+        <v>227.4956853704592</v>
+      </c>
+      <c r="C16" s="5">
+        <v>272.44837499370601</v>
+      </c>
+      <c r="D16" s="5">
+        <v>282.64223135991409</v>
+      </c>
+      <c r="E16" s="5">
+        <v>229.51373762586601</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="5">
+        <v>92639.804190406896</v>
+      </c>
+      <c r="C18" s="5">
+        <v>93080.28297062905</v>
+      </c>
+      <c r="D18" s="5">
+        <v>92623.050287719743</v>
+      </c>
+      <c r="E18" s="5">
+        <v>92479.201967458706</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="5">
+        <v>-30337.63316189517</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-30082.054339034021</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-30343.48836729406</v>
+      </c>
+      <c r="E19" s="5">
+        <v>-30393.76092033066</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="5">
+        <v>176077.21297828379</v>
+      </c>
+      <c r="C20" s="5">
+        <v>176478.36424616151</v>
+      </c>
+      <c r="D20" s="5">
+        <v>175982.93291608969</v>
+      </c>
+      <c r="E20" s="5">
+        <v>175868.17621050921</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="8">
+        <f>B6</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="8">
+        <f>C6</f>
+        <v>96.841142582021973</v>
+      </c>
+      <c r="D23" s="8">
+        <f>D6</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <f>E6</f>
+        <v>30.554145623040011</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="11">
+        <f>B11</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="11">
+        <f>C11</f>
+        <v>39.004466488049992</v>
+      </c>
+      <c r="D24" s="11">
+        <f>D11</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="11">
+        <f>E11</f>
+        <v>12.306343296</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="8">
+        <f>B5/1000</f>
+        <v>2.5423794783902758</v>
+      </c>
+      <c r="C26" s="8">
+        <f>C5/1000</f>
+        <v>2.4944157891952581</v>
+      </c>
+      <c r="D26" s="8">
+        <f>D5/1000</f>
+        <v>2.5137389663880132</v>
+      </c>
+      <c r="E26" s="8">
+        <f>E5/1000</f>
+        <v>2.435149210437197</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="11">
+        <f>B10/1000</f>
+        <v>0.73550880075495007</v>
+      </c>
+      <c r="C27" s="11">
+        <f>C10/1000</f>
+        <v>0.72382196580906999</v>
+      </c>
+      <c r="D27" s="11">
+        <f>D10/1000</f>
+        <v>0.74158780880969599</v>
+      </c>
+      <c r="E27" s="11">
+        <f>E10/1000</f>
+        <v>0.68298121304402404</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="11">
+        <f>B7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="C28" s="11">
+        <f>C7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="D28" s="11">
+        <f>D7/1000</f>
+        <v>0.1651093833399993</v>
+      </c>
+      <c r="E28" s="11">
+        <f>E7/1000</f>
+        <v>0.14897144549999991</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="11">
+        <f>B12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="C29" s="11">
+        <f>C12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="D29" s="11">
+        <f>D12/1000</f>
+        <v>5.5639340949999998e-02</v>
+      </c>
+      <c r="E29" s="11">
+        <f>E12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="11">
+        <f>B8/1000</f>
+        <v>23.774429339999998</v>
+      </c>
+      <c r="C30" s="11">
+        <f>C8/1000</f>
+        <v>23.72367947</v>
+      </c>
+      <c r="D30" s="11">
+        <f>D8/1000</f>
+        <v>23.5869629</v>
+      </c>
+      <c r="E30" s="11">
+        <f>E8/1000</f>
+        <v>23.82656291</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="11">
+        <f>B13/1000</f>
+        <v>1.6068459499999999</v>
+      </c>
+      <c r="C31" s="11">
+        <f>C13/1000</f>
+        <v>1.6011893399999999</v>
+      </c>
+      <c r="D31" s="11">
+        <f>D13/1000</f>
+        <v>1.5859146100000001</v>
+      </c>
+      <c r="E31" s="11">
+        <f>E13/1000</f>
+        <v>1.6126669600000001</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="11">
+        <f>B15/1000</f>
+        <v>10.338852324086471</v>
+      </c>
+      <c r="C32" s="11">
+        <f>C15/1000</f>
+        <v>10.311069574492059</v>
+      </c>
+      <c r="D32" s="11">
+        <f>D15/1000</f>
+        <v>10.33948878898885</v>
+      </c>
+      <c r="E32" s="11">
+        <f>E15/1000</f>
+        <v>10.34495345049649</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="8">
+        <f>B9/1000</f>
+        <v>0.67275459643071378</v>
+      </c>
+      <c r="C33" s="8">
+        <f>C9/1000</f>
+        <v>0.65884192959465615</v>
+      </c>
+      <c r="D33" s="8">
+        <f>D9/1000</f>
+        <v>0.73771733283010843</v>
+      </c>
+      <c r="E33" s="8">
+        <f>E9/1000</f>
+        <v>0.72520134591293051</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="11">
+        <f>B14/1000</f>
+        <v>2.6625943351861549e-02</v>
+      </c>
+      <c r="C34" s="11">
+        <f>C14/1000</f>
+        <v>3.1554270135409061e-02</v>
+      </c>
+      <c r="D34" s="11">
+        <f>D14/1000</f>
+        <v>3.607693037235904e-02</v>
+      </c>
+      <c r="E34" s="11">
+        <f>E14/1000</f>
+        <v>3.4486221839960009e-02</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="11">
+        <f>B16/1000</f>
+        <v>0.22749568537045919</v>
+      </c>
+      <c r="C35" s="11">
+        <f>C16/1000</f>
+        <v>0.272448374993706</v>
+      </c>
+      <c r="D35" s="11">
+        <f>D16/1000</f>
+        <v>0.28264223135991406</v>
+      </c>
+      <c r="E35" s="11">
+        <f>E16/1000</f>
+        <v>0.22951373762586602</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="11">
+        <f>B4/1000</f>
+        <v>4.0609494799999881</v>
+      </c>
+      <c r="C36" s="11">
+        <f>C4/1000</f>
+        <v>4.0609494799999952</v>
+      </c>
+      <c r="D36" s="11">
+        <f>D4/1000</f>
+        <v>4.0609494799999863</v>
+      </c>
+      <c r="E36" s="11">
+        <f>E4/1000</f>
+        <v>4.0609494800000014</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="7">
+        <f>SUM(B26:B36)</f>
+        <v>44.181783148034718</v>
+      </c>
+      <c r="C38" s="7">
+        <f>SUM(C26:C36)</f>
+        <v>44.073911743870163</v>
+      </c>
+      <c r="D38" s="7">
+        <f>SUM(D26:D36)</f>
+        <v>44.105827773038925</v>
+      </c>
+      <c r="E38" s="7">
+        <f>SUM(E26:E36)</f>
+        <v>44.148406079006463</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="9">
+        <f>B19/1000</f>
+        <v>-30.33763316189517</v>
+      </c>
+      <c r="C39" s="9">
+        <f>C19/1000</f>
+        <v>-30.08205433903402</v>
+      </c>
+      <c r="D39" s="9">
+        <f>D19/1000</f>
+        <v>-30.343488367294061</v>
+      </c>
+      <c r="E39" s="9">
+        <f>E19/1000</f>
+        <v>-30.39376092033066</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="9">
+        <f>SUM(B38:B39)</f>
+        <v>13.844149986139549</v>
+      </c>
+      <c r="C41" s="9">
+        <f>SUM(C38:C39)</f>
+        <v>13.991857404836143</v>
+      </c>
+      <c r="D41" s="9">
+        <f>SUM(D38:D39)</f>
+        <v>13.762339405744864</v>
+      </c>
+      <c r="E41" s="9">
+        <f>SUM(E38:E39)</f>
+        <v>13.754645158675803</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="B42" s="1" t="str">
+        <f>B1</f>
+        <v xml:space="preserve">liq noins</v>
+      </c>
+      <c r="C42" s="1" t="str">
+        <f>C1</f>
+        <v xml:space="preserve">liq ins20%</v>
+      </c>
+      <c r="D42" s="1" t="str">
+        <f>D1</f>
+        <v xml:space="preserve">liq ins40%</v>
+      </c>
+      <c r="E42" s="1" t="str">
+        <f>E1</f>
+        <v xml:space="preserve">liq ins60%</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="36.921875"/>
+    <col customWidth="1" min="2" max="2" width="9.140625"/>
+    <col customWidth="1" min="3" max="8" width="9.140625"/>
+    <col customWidth="1" min="9" max="9" width="3.421875"/>
+    <col customWidth="1" min="10" max="13" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="5"/>
+      <c r="J1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="14"/>
+      <c r="J2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="5">
+        <v>69607.316630000118</v>
+      </c>
+      <c r="C3" s="5">
+        <v>69597.543222625274</v>
+      </c>
+      <c r="D3" s="5">
+        <v>69391.693142625401</v>
+      </c>
+      <c r="E3" s="5">
+        <v>69599.622444599387</v>
+      </c>
+      <c r="F3" s="5">
+        <v>69532.139366398915</v>
+      </c>
+      <c r="G3" s="5">
+        <v>69603.132085613208</v>
+      </c>
+      <c r="H3" s="5">
+        <v>69438.499605969642</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5">
+        <v>69593.258801737393</v>
+      </c>
+      <c r="K3" s="5">
+        <v>69406.223870696296</v>
+      </c>
+      <c r="L3" s="5">
+        <v>69597.54322262507</v>
+      </c>
+      <c r="M3" s="5">
+        <v>69634.329084374709</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4060.949480000002</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4060.9494799999939</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4060.9494799999889</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4060.9494800000002</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5">
+        <v>4060.9494799999879</v>
+      </c>
+      <c r="K4" s="5">
+        <v>4060.9494799999952</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4060.9494799999861</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4060.9494800000011</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3011.7763737611531</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2491.3570058783462</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2940.315261938953</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2699.1899078522679</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3004.409742667825</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3033.681652187734</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2958.4751029840372</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5">
+        <v>2542.3794783902758</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2494.4157891952582</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2513.7389663880131</v>
+      </c>
+      <c r="M5" s="5">
+        <v>2435.1492104371969</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>203.41004422359791</v>
+      </c>
+      <c r="D6" s="5">
+        <v>440.69461639348378</v>
+      </c>
+      <c r="E6" s="5">
+        <v>261.30101500166052</v>
+      </c>
+      <c r="F6" s="5">
+        <v>492.09113817889602</v>
+      </c>
+      <c r="G6" s="5">
+        <v>234.26697045616001</v>
+      </c>
+      <c r="H6" s="5">
+        <v>165.67485359931001</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>96.841142582021973</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>30.554145623040011</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="C7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="D7" s="5">
+        <v>165.10938333999999</v>
+      </c>
+      <c r="E7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="F7" s="5">
+        <v>148.9714454999984</v>
+      </c>
+      <c r="G7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="H7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="K7" s="5">
+        <v>148.97144549999999</v>
+      </c>
+      <c r="L7" s="5">
+        <v>165.10938333999931</v>
+      </c>
+      <c r="M7" s="5">
+        <v>148.9714454999999</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="5">
+        <v>23819.947670000001</v>
+      </c>
+      <c r="C8" s="5">
+        <v>23926.322779999999</v>
+      </c>
+      <c r="D8" s="5">
+        <v>23679.195970000001</v>
+      </c>
+      <c r="E8" s="5">
+        <v>23826.562910000001</v>
+      </c>
+      <c r="F8" s="5">
+        <v>23631.474620000001</v>
+      </c>
+      <c r="G8" s="5">
+        <v>23774.429339999999</v>
+      </c>
+      <c r="H8" s="5">
+        <v>23606.99826</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5">
+        <v>23774.429339999999</v>
+      </c>
+      <c r="K8" s="5">
+        <v>23723.679469999999</v>
+      </c>
+      <c r="L8" s="5">
+        <v>23586.962899999999</v>
+      </c>
+      <c r="M8" s="5">
+        <v>23826.562910000001</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1024.471405513181</v>
+      </c>
+      <c r="C9" s="5">
+        <v>726.569981355952</v>
+      </c>
+      <c r="D9" s="5">
+        <v>672.74187858881464</v>
+      </c>
+      <c r="E9" s="5">
+        <v>678.56208479756037</v>
+      </c>
+      <c r="F9" s="5">
+        <v>777.59004986035484</v>
+      </c>
+      <c r="G9" s="5">
+        <v>804.70481487888799</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1080.042504820924</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5">
+        <v>672.75459643071383</v>
+      </c>
+      <c r="K9" s="5">
+        <v>658.84192959465611</v>
+      </c>
+      <c r="L9" s="5">
+        <v>737.71733283010838</v>
+      </c>
+      <c r="M9" s="5">
+        <v>725.20134591293049</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5">
+        <v>808.72542709314394</v>
+      </c>
+      <c r="C10" s="5">
+        <v>696.5245112513079</v>
+      </c>
+      <c r="D10" s="5">
+        <v>836.65331059579796</v>
+      </c>
+      <c r="E10" s="5">
+        <v>696.20053983729599</v>
+      </c>
+      <c r="F10" s="5">
+        <v>854.95436631219593</v>
+      </c>
+      <c r="G10" s="5">
+        <v>841.68429764965992</v>
+      </c>
+      <c r="H10" s="5">
+        <v>824.41561571600096</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5">
+        <v>735.50880075495002</v>
+      </c>
+      <c r="K10" s="5">
+        <v>723.82196580906998</v>
+      </c>
+      <c r="L10" s="5">
+        <v>741.58780880969596</v>
+      </c>
+      <c r="M10" s="5">
+        <v>682.981213044024</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>63.142957502529988</v>
+      </c>
+      <c r="D11" s="5">
+        <v>128.79124610002</v>
+      </c>
+      <c r="E11" s="5">
+        <v>39.618204026112011</v>
+      </c>
+      <c r="F11" s="5">
+        <v>123.06288941384</v>
+      </c>
+      <c r="G11" s="5">
+        <v>46.122297555099998</v>
+      </c>
+      <c r="H11" s="5">
+        <v>34.749922530525012</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>39.004466488049992</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>12.306343296</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="C12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="D12" s="5">
+        <v>55.639340949999998</v>
+      </c>
+      <c r="E12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="F12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="G12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="H12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="K12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+      <c r="L12" s="5">
+        <v>55.639340949999998</v>
+      </c>
+      <c r="M12" s="5">
+        <v>46.970104149999997</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1611.9264000000001</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1623.80045</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1596.2213999999999</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1612.66696</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1590.8734099999999</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1606.8459499999999</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1588.16291</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5">
+        <v>1606.8459499999999</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1601.1893399999999</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1585.91461</v>
+      </c>
+      <c r="M13" s="5">
+        <v>1612.66696</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="5">
+        <v>44.940613976118541</v>
+      </c>
+      <c r="C14" s="5">
+        <v>34.900366947641352</v>
+      </c>
+      <c r="D14" s="5">
+        <v>29.188099345928421</v>
+      </c>
+      <c r="E14" s="5">
+        <v>29.308103597655158</v>
+      </c>
+      <c r="F14" s="5">
+        <v>39.810106116292182</v>
+      </c>
+      <c r="G14" s="5">
+        <v>34.090012150156006</v>
+      </c>
+      <c r="H14" s="5">
+        <v>61.198907395515157</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5">
+        <v>26.625943351861551</v>
+      </c>
+      <c r="K14" s="5">
+        <v>31.554270135409059</v>
+      </c>
+      <c r="L14" s="5">
+        <v>36.076930372359037</v>
+      </c>
+      <c r="M14" s="5">
+        <v>34.48622183996001</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="5">
+        <v>10340.940661000021</v>
+      </c>
+      <c r="C15" s="5">
+        <v>10339.488788988891</v>
+      </c>
+      <c r="D15" s="5">
+        <v>10308.9042769889</v>
+      </c>
+      <c r="E15" s="5">
+        <v>10339.796881386421</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10329.770524506201</v>
+      </c>
+      <c r="G15" s="5">
+        <v>10340.319033082371</v>
+      </c>
+      <c r="H15" s="5">
+        <v>10315.86367440231</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5">
+        <v>10338.852324086471</v>
+      </c>
+      <c r="K15" s="5">
+        <v>10311.069574492059</v>
+      </c>
+      <c r="L15" s="5">
+        <v>10339.488788988851</v>
+      </c>
+      <c r="M15" s="5">
+        <v>10344.95345049649</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="5">
+        <v>289.0632183213545</v>
+      </c>
+      <c r="C16" s="5">
+        <v>272.74804135991099</v>
+      </c>
+      <c r="D16" s="5">
+        <v>244.76081335991179</v>
+      </c>
+      <c r="E16" s="5">
+        <v>228.56775681613709</v>
+      </c>
+      <c r="F16" s="5">
+        <v>286.36727108258782</v>
+      </c>
+      <c r="G16" s="5">
+        <v>235.18915591713539</v>
+      </c>
+      <c r="H16" s="5">
+        <v>429.06939878270413</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5">
+        <v>227.4956853704592</v>
+      </c>
+      <c r="K16" s="5">
+        <v>272.44837499370601</v>
+      </c>
+      <c r="L16" s="5">
+        <v>282.64223135991409</v>
+      </c>
+      <c r="M16" s="5">
+        <v>229.51373762586601</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="5">
+        <v>92584.832120000006</v>
+      </c>
+      <c r="C18" s="5">
+        <v>92623.050287719991</v>
+      </c>
+      <c r="D18" s="5">
+        <v>92922.050927719858</v>
+      </c>
+      <c r="E18" s="5">
+        <v>92522.56579599141</v>
+      </c>
+      <c r="F18" s="5">
+        <v>92606.881784256359</v>
+      </c>
+      <c r="G18" s="5">
+        <v>92601.195463209151</v>
+      </c>
+      <c r="H18" s="5">
+        <v>92828.863940102048</v>
+      </c>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5">
+        <v>92639.804190406896</v>
+      </c>
+      <c r="K18" s="5">
+        <v>93080.28297062905</v>
+      </c>
+      <c r="L18" s="5">
+        <v>92623.050287719743</v>
+      </c>
+      <c r="M18" s="5">
+        <v>92479.201967458706</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="5">
+        <v>-30356.844969999991</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-30343.48836729387</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-30062.161487293939</v>
+      </c>
+      <c r="E19" s="5">
+        <v>-30346.329111751569</v>
+      </c>
+      <c r="F19" s="5">
+        <v>-30254.10340311785</v>
+      </c>
+      <c r="G19" s="5">
+        <v>-30351.126258527838</v>
+      </c>
+      <c r="H19" s="5">
+        <v>-30126.16563613954</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5">
+        <v>-30337.63316189517</v>
+      </c>
+      <c r="K19" s="5">
+        <v>-30082.054339034021</v>
+      </c>
+      <c r="L19" s="5">
+        <v>-30343.48836729406</v>
+      </c>
+      <c r="M19" s="5">
+        <v>-30393.76092033066</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="5">
+        <v>177043.9865793151</v>
+      </c>
+      <c r="C20" s="5">
+        <v>176245.70809848339</v>
+      </c>
+      <c r="D20" s="5">
+        <v>176841.2617981596</v>
+      </c>
+      <c r="E20" s="5">
+        <v>176143.60530277659</v>
+      </c>
+      <c r="F20" s="5">
+        <v>176657.05886773291</v>
+      </c>
+      <c r="G20" s="5">
+        <v>176781.03657581049</v>
+      </c>
+      <c r="H20" s="5">
+        <v>177262.31531368359</v>
+      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5">
+        <v>176077.21297828379</v>
+      </c>
+      <c r="K20" s="5">
+        <v>176478.36424616151</v>
+      </c>
+      <c r="L20" s="5">
+        <v>175982.93291608969</v>
+      </c>
+      <c r="M20" s="5">
+        <v>175868.17621050921</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="8">
+        <f>B6</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="8">
+        <f>C6</f>
+        <v>203.41004422359791</v>
+      </c>
+      <c r="D23" s="8">
+        <f>D6</f>
+        <v>440.69461639348378</v>
+      </c>
+      <c r="E23" s="8">
+        <f>E6</f>
+        <v>261.30101500166052</v>
+      </c>
+      <c r="F23" s="8">
+        <f>F6</f>
+        <v>492.09113817889602</v>
+      </c>
+      <c r="G23" s="8">
+        <f>G6</f>
+        <v>234.26697045616001</v>
+      </c>
+      <c r="H23" s="8">
+        <f>H6</f>
+        <v>165.67485359931001</v>
+      </c>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8">
+        <f>J6</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="8">
+        <f>K6</f>
+        <v>96.841142582021973</v>
+      </c>
+      <c r="L23" s="8">
+        <f>L6</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="8">
+        <f>M6</f>
+        <v>30.554145623040011</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="11">
+        <f>B11</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="11">
+        <f>C11</f>
+        <v>63.142957502529988</v>
+      </c>
+      <c r="D24" s="11">
+        <f>D11</f>
+        <v>128.79124610002</v>
+      </c>
+      <c r="E24" s="11">
+        <f>E11</f>
+        <v>39.618204026112011</v>
+      </c>
+      <c r="F24" s="11">
+        <f>F11</f>
+        <v>123.06288941384</v>
+      </c>
+      <c r="G24" s="11">
+        <f>G11</f>
+        <v>46.122297555099998</v>
+      </c>
+      <c r="H24" s="11">
+        <f>H11</f>
+        <v>34.749922530525012</v>
+      </c>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11">
+        <f>J11</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="11">
+        <f>K11</f>
+        <v>39.004466488049992</v>
+      </c>
+      <c r="L24" s="11">
+        <f>L11</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="11">
+        <f>M11</f>
+        <v>12.306343296</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="8">
+        <f>B5/1000</f>
+        <v>3.0117763737611529</v>
+      </c>
+      <c r="C26" s="8">
+        <f>C5/1000</f>
+        <v>2.4913570058783461</v>
+      </c>
+      <c r="D26" s="8">
+        <f>D5/1000</f>
+        <v>2.9403152619389528</v>
+      </c>
+      <c r="E26" s="8">
+        <f>E5/1000</f>
+        <v>2.6991899078522681</v>
+      </c>
+      <c r="F26" s="8">
+        <f>F5/1000</f>
+        <v>3.0044097426678249</v>
+      </c>
+      <c r="G26" s="8">
+        <f>G5/1000</f>
+        <v>3.0336816521877341</v>
+      </c>
+      <c r="H26" s="8">
+        <f>H5/1000</f>
+        <v>2.9584751029840373</v>
+      </c>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8">
+        <f>J5/1000</f>
+        <v>2.5423794783902758</v>
+      </c>
+      <c r="K26" s="8">
+        <f>K5/1000</f>
+        <v>2.4944157891952581</v>
+      </c>
+      <c r="L26" s="8">
+        <f>L5/1000</f>
+        <v>2.5137389663880132</v>
+      </c>
+      <c r="M26" s="8">
+        <f>M5/1000</f>
+        <v>2.435149210437197</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="11">
+        <f>B10/1000</f>
+        <v>0.80872542709314399</v>
+      </c>
+      <c r="C27" s="11">
+        <f>C10/1000</f>
+        <v>0.69652451125130788</v>
+      </c>
+      <c r="D27" s="11">
+        <f>D10/1000</f>
+        <v>0.83665331059579795</v>
+      </c>
+      <c r="E27" s="11">
+        <f>E10/1000</f>
+        <v>0.69620053983729602</v>
+      </c>
+      <c r="F27" s="11">
+        <f>F10/1000</f>
+        <v>0.8549543663121959</v>
+      </c>
+      <c r="G27" s="11">
+        <f>G10/1000</f>
+        <v>0.84168429764965991</v>
+      </c>
+      <c r="H27" s="11">
+        <f>H10/1000</f>
+        <v>0.82441561571600097</v>
+      </c>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11">
+        <f>J10/1000</f>
+        <v>0.73550880075495007</v>
+      </c>
+      <c r="K27" s="11">
+        <f>K10/1000</f>
+        <v>0.72382196580906999</v>
+      </c>
+      <c r="L27" s="11">
+        <f>L10/1000</f>
+        <v>0.74158780880969599</v>
+      </c>
+      <c r="M27" s="11">
+        <f>M10/1000</f>
+        <v>0.68298121304402404</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="11">
+        <f>B7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="C28" s="11">
+        <f>C7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="D28" s="11">
+        <f>D7/1000</f>
+        <v>0.16510938334</v>
+      </c>
+      <c r="E28" s="11">
+        <f>E7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="F28" s="11">
+        <f>F7/1000</f>
+        <v>0.14897144549999838</v>
+      </c>
+      <c r="G28" s="11">
+        <f>G7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="H28" s="11">
+        <f>H7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11">
+        <f>J7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="K28" s="11">
+        <f>K7/1000</f>
+        <v>0.14897144549999999</v>
+      </c>
+      <c r="L28" s="11">
+        <f>L7/1000</f>
+        <v>0.1651093833399993</v>
+      </c>
+      <c r="M28" s="11">
+        <f>M7/1000</f>
+        <v>0.14897144549999991</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="11">
+        <f>B12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="C29" s="11">
+        <f>C12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="D29" s="11">
+        <f>D12/1000</f>
+        <v>5.5639340949999998e-02</v>
+      </c>
+      <c r="E29" s="11">
+        <f>E12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="F29" s="11">
+        <f>F12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="G29" s="11">
+        <f>G12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="H29" s="11">
+        <f>H12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11">
+        <f>J12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="K29" s="11">
+        <f>K12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+      <c r="L29" s="11">
+        <f>L12/1000</f>
+        <v>5.5639340949999998e-02</v>
+      </c>
+      <c r="M29" s="11">
+        <f>M12/1000</f>
+        <v>4.6970104149999997e-02</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="11">
+        <f>B8/1000</f>
+        <v>23.819947670000001</v>
+      </c>
+      <c r="C30" s="11">
+        <f>C8/1000</f>
+        <v>23.92632278</v>
+      </c>
+      <c r="D30" s="11">
+        <f>D8/1000</f>
+        <v>23.679195970000002</v>
+      </c>
+      <c r="E30" s="11">
+        <f>E8/1000</f>
+        <v>23.82656291</v>
+      </c>
+      <c r="F30" s="11">
+        <f>F8/1000</f>
+        <v>23.631474620000002</v>
+      </c>
+      <c r="G30" s="11">
+        <f>G8/1000</f>
+        <v>23.774429339999998</v>
+      </c>
+      <c r="H30" s="11">
+        <f>H8/1000</f>
+        <v>23.606998260000001</v>
+      </c>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11">
+        <f>J8/1000</f>
+        <v>23.774429339999998</v>
+      </c>
+      <c r="K30" s="11">
+        <f>K8/1000</f>
+        <v>23.72367947</v>
+      </c>
+      <c r="L30" s="11">
+        <f>L8/1000</f>
+        <v>23.5869629</v>
+      </c>
+      <c r="M30" s="11">
+        <f>M8/1000</f>
+        <v>23.82656291</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="11">
+        <f>B13/1000</f>
+        <v>1.6119264</v>
+      </c>
+      <c r="C31" s="11">
+        <f>C13/1000</f>
+        <v>1.6238004500000001</v>
+      </c>
+      <c r="D31" s="11">
+        <f>D13/1000</f>
+        <v>1.5962213999999999</v>
+      </c>
+      <c r="E31" s="11">
+        <f>E13/1000</f>
+        <v>1.6126669600000001</v>
+      </c>
+      <c r="F31" s="11">
+        <f>F13/1000</f>
+        <v>1.5908734099999999</v>
+      </c>
+      <c r="G31" s="11">
+        <f>G13/1000</f>
+        <v>1.6068459499999999</v>
+      </c>
+      <c r="H31" s="11">
+        <f>H13/1000</f>
+        <v>1.5881629100000001</v>
+      </c>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11">
+        <f>J13/1000</f>
+        <v>1.6068459499999999</v>
+      </c>
+      <c r="K31" s="11">
+        <f>K13/1000</f>
+        <v>1.6011893399999999</v>
+      </c>
+      <c r="L31" s="11">
+        <f>L13/1000</f>
+        <v>1.5859146100000001</v>
+      </c>
+      <c r="M31" s="11">
+        <f>M13/1000</f>
+        <v>1.6126669600000001</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="11">
+        <f>B15/1000</f>
+        <v>10.340940661000021</v>
+      </c>
+      <c r="C32" s="11">
+        <f>C15/1000</f>
+        <v>10.339488788988891</v>
+      </c>
+      <c r="D32" s="11">
+        <f>D15/1000</f>
+        <v>10.308904276988899</v>
+      </c>
+      <c r="E32" s="11">
+        <f>E15/1000</f>
+        <v>10.339796881386421</v>
+      </c>
+      <c r="F32" s="11">
+        <f>F15/1000</f>
+        <v>10.3297705245062</v>
+      </c>
+      <c r="G32" s="11">
+        <f>G15/1000</f>
+        <v>10.340319033082372</v>
+      </c>
+      <c r="H32" s="11">
+        <f>H15/1000</f>
+        <v>10.31586367440231</v>
+      </c>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11">
+        <f>J15/1000</f>
+        <v>10.338852324086471</v>
+      </c>
+      <c r="K32" s="11">
+        <f>K15/1000</f>
+        <v>10.311069574492059</v>
+      </c>
+      <c r="L32" s="11">
+        <f>L15/1000</f>
+        <v>10.33948878898885</v>
+      </c>
+      <c r="M32" s="11">
+        <f>M15/1000</f>
+        <v>10.34495345049649</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="8">
+        <f>B9/1000</f>
+        <v>1.0244714055131809</v>
+      </c>
+      <c r="C33" s="8">
+        <f>C9/1000</f>
+        <v>0.72656998135595197</v>
+      </c>
+      <c r="D33" s="8">
+        <f>D9/1000</f>
+        <v>0.67274187858881462</v>
+      </c>
+      <c r="E33" s="8">
+        <f>E9/1000</f>
+        <v>0.67856208479756042</v>
+      </c>
+      <c r="F33" s="8">
+        <f>F9/1000</f>
+        <v>0.77759004986035485</v>
+      </c>
+      <c r="G33" s="8">
+        <f>G9/1000</f>
+        <v>0.80470481487888801</v>
+      </c>
+      <c r="H33" s="8">
+        <f>H9/1000</f>
+        <v>1.0800425048209241</v>
+      </c>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8">
+        <f>J9/1000</f>
+        <v>0.67275459643071378</v>
+      </c>
+      <c r="K33" s="8">
+        <f>K9/1000</f>
+        <v>0.65884192959465615</v>
+      </c>
+      <c r="L33" s="8">
+        <f>L9/1000</f>
+        <v>0.73771733283010843</v>
+      </c>
+      <c r="M33" s="8">
+        <f>M9/1000</f>
+        <v>0.72520134591293051</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="11">
+        <f>B14/1000</f>
+        <v>4.4940613976118544e-02</v>
+      </c>
+      <c r="C34" s="11">
+        <f>C14/1000</f>
+        <v>3.4900366947641349e-02</v>
+      </c>
+      <c r="D34" s="11">
+        <f>D14/1000</f>
+        <v>2.918809934592842e-02</v>
+      </c>
+      <c r="E34" s="11">
+        <f>E14/1000</f>
+        <v>2.9308103597655157e-02</v>
+      </c>
+      <c r="F34" s="11">
+        <f>F14/1000</f>
+        <v>3.9810106116292182e-02</v>
+      </c>
+      <c r="G34" s="11">
+        <f>G14/1000</f>
+        <v>3.4090012150156009e-02</v>
+      </c>
+      <c r="H34" s="11">
+        <f>H14/1000</f>
+        <v>6.1198907395515159e-02</v>
+      </c>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11">
+        <f>J14/1000</f>
+        <v>2.6625943351861549e-02</v>
+      </c>
+      <c r="K34" s="11">
+        <f>K14/1000</f>
+        <v>3.1554270135409061e-02</v>
+      </c>
+      <c r="L34" s="11">
+        <f>L14/1000</f>
+        <v>3.607693037235904e-02</v>
+      </c>
+      <c r="M34" s="11">
+        <f>M14/1000</f>
+        <v>3.4486221839960009e-02</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="11">
+        <f>B16/1000</f>
+        <v>0.28906321832135451</v>
+      </c>
+      <c r="C35" s="11">
+        <f>C16/1000</f>
+        <v>0.27274804135991099</v>
+      </c>
+      <c r="D35" s="11">
+        <f>D16/1000</f>
+        <v>0.24476081335991179</v>
+      </c>
+      <c r="E35" s="11">
+        <f>E16/1000</f>
+        <v>0.22856775681613709</v>
+      </c>
+      <c r="F35" s="11">
+        <f>F16/1000</f>
+        <v>0.2863672710825878</v>
+      </c>
+      <c r="G35" s="11">
+        <f>G16/1000</f>
+        <v>0.23518915591713541</v>
+      </c>
+      <c r="H35" s="11">
+        <f>H16/1000</f>
+        <v>0.42906939878270411</v>
+      </c>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11">
+        <f>J16/1000</f>
+        <v>0.22749568537045919</v>
+      </c>
+      <c r="K35" s="11">
+        <f>K16/1000</f>
+        <v>0.272448374993706</v>
+      </c>
+      <c r="L35" s="11">
+        <f>L16/1000</f>
+        <v>0.28264223135991406</v>
+      </c>
+      <c r="M35" s="11">
+        <f>M16/1000</f>
+        <v>0.22951373762586602</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="11">
+        <f>B4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="C36" s="11">
+        <f>C4/1000</f>
+        <v>4.0609494800000023</v>
+      </c>
+      <c r="D36" s="11">
+        <f>D4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="E36" s="11">
+        <f>E4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="F36" s="11">
+        <f>F4/1000</f>
+        <v>4.0609494799999935</v>
+      </c>
+      <c r="G36" s="11">
+        <f>G4/1000</f>
+        <v>4.060949479999989</v>
+      </c>
+      <c r="H36" s="11">
+        <f>H4/1000</f>
+        <v>4.0609494800000006</v>
+      </c>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11">
+        <f>J4/1000</f>
+        <v>4.0609494799999881</v>
+      </c>
+      <c r="K36" s="11">
+        <f>K4/1000</f>
+        <v>4.0609494799999952</v>
+      </c>
+      <c r="L36" s="11">
+        <f>L4/1000</f>
+        <v>4.0609494799999863</v>
+      </c>
+      <c r="M36" s="11">
+        <f>M4/1000</f>
+        <v>4.0609494800000014</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="7">
+        <f>SUM(B26:B36)</f>
+        <v>45.208682799314971</v>
+      </c>
+      <c r="C38" s="7">
+        <f>SUM(C26:C36)</f>
+        <v>44.368602955432053</v>
+      </c>
+      <c r="D38" s="7">
+        <f>SUM(D26:D36)</f>
+        <v>44.589679215108305</v>
+      </c>
+      <c r="E38" s="7">
+        <f>SUM(E26:E36)</f>
+        <v>44.367746173937341</v>
+      </c>
+      <c r="F38" s="7">
+        <f>SUM(F26:F36)</f>
+        <v>44.77214112019545</v>
+      </c>
+      <c r="G38" s="7">
+        <f>SUM(G26:G36)</f>
+        <v>44.927835285515933</v>
+      </c>
+      <c r="H38" s="7">
+        <f>SUM(H26:H36)</f>
+        <v>45.121117403751491</v>
+      </c>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7">
+        <f>SUM(J26:J36)</f>
+        <v>44.181783148034718</v>
+      </c>
+      <c r="K38" s="7">
+        <f>SUM(K26:K36)</f>
+        <v>44.073911743870163</v>
+      </c>
+      <c r="L38" s="7">
+        <f>SUM(L26:L36)</f>
+        <v>44.105827773038925</v>
+      </c>
+      <c r="M38" s="7">
+        <f>SUM(M26:M36)</f>
+        <v>44.148406079006463</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="9">
+        <f>B19/1000</f>
+        <v>-30.35684496999999</v>
+      </c>
+      <c r="C39" s="9">
+        <f>C19/1000</f>
+        <v>-30.343488367293869</v>
+      </c>
+      <c r="D39" s="9">
+        <f>D19/1000</f>
+        <v>-30.062161487293938</v>
+      </c>
+      <c r="E39" s="9">
+        <f>E19/1000</f>
+        <v>-30.346329111751569</v>
+      </c>
+      <c r="F39" s="9">
+        <f>F19/1000</f>
+        <v>-30.254103403117849</v>
+      </c>
+      <c r="G39" s="9">
+        <f>G19/1000</f>
+        <v>-30.351126258527838</v>
+      </c>
+      <c r="H39" s="9">
+        <f>H19/1000</f>
+        <v>-30.12616563613954</v>
+      </c>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9">
+        <f>J19/1000</f>
+        <v>-30.33763316189517</v>
+      </c>
+      <c r="K39" s="9">
+        <f>K19/1000</f>
+        <v>-30.08205433903402</v>
+      </c>
+      <c r="L39" s="9">
+        <f>L19/1000</f>
+        <v>-30.343488367294061</v>
+      </c>
+      <c r="M39" s="9">
+        <f>M19/1000</f>
+        <v>-30.39376092033066</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="9">
+        <f>SUM(B38:B39)</f>
+        <v>14.851837829314981</v>
+      </c>
+      <c r="C41" s="9">
+        <f>SUM(C38:C39)</f>
+        <v>14.025114588138184</v>
+      </c>
+      <c r="D41" s="9">
+        <f>SUM(D38:D39)</f>
+        <v>14.527517727814367</v>
+      </c>
+      <c r="E41" s="9">
+        <f>SUM(E38:E39)</f>
+        <v>14.021417062185773</v>
+      </c>
+      <c r="F41" s="9">
+        <f>SUM(F38:F39)</f>
+        <v>14.5180377170776</v>
+      </c>
+      <c r="G41" s="9">
+        <f>SUM(G38:G39)</f>
+        <v>14.576709026988095</v>
+      </c>
+      <c r="H41" s="9">
+        <f>SUM(H38:H39)</f>
+        <v>14.994951767611951</v>
+      </c>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9">
+        <f>SUM(J38:J39)</f>
+        <v>13.844149986139549</v>
+      </c>
+      <c r="K41" s="9">
+        <f>SUM(K38:K39)</f>
+        <v>13.991857404836143</v>
+      </c>
+      <c r="L41" s="9">
+        <f>SUM(L38:L39)</f>
+        <v>13.762339405744864</v>
+      </c>
+      <c r="M41" s="9">
+        <f>SUM(M38:M39)</f>
+        <v>13.754645158675803</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="B42" s="1" t="str">
+        <f>B1</f>
+        <v>noins</v>
+      </c>
+      <c r="C42" s="1" t="str">
+        <f>C1</f>
+        <v>ins20%</v>
+      </c>
+      <c r="D42" s="1" t="str">
+        <f>D1</f>
+        <v>ins40%</v>
+      </c>
+      <c r="E42" s="1" t="str">
+        <f>E1</f>
+        <v>ins60%</v>
+      </c>
+      <c r="F42" s="1" t="str">
+        <f>F1</f>
+        <v>ins80%</v>
+      </c>
+      <c r="G42" s="1" t="str">
+        <f>G1</f>
+        <v>ins100%</v>
+      </c>
+      <c r="H42" s="1" t="str">
+        <f>H1</f>
+        <v>ins150%</v>
+      </c>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1" t="str">
+        <f>J1</f>
+        <v xml:space="preserve">liq noins</v>
+      </c>
+      <c r="K42" s="1" t="str">
+        <f>K1</f>
+        <v xml:space="preserve">liq ins20%</v>
+      </c>
+      <c r="L42" s="1" t="str">
+        <f>L1</f>
+        <v xml:space="preserve">liq ins40%</v>
+      </c>
+      <c r="M42" s="1" t="str">
+        <f>M1</f>
+        <v xml:space="preserve">liq ins60%</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="A44" t="s">
+        <v>65</v>
+      </c>
+      <c r="M44">
+        <v>2540.54</v>
       </c>
     </row>
   </sheetData>
